--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>876003</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>9.63000011444092</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>8.82999992370605</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>832416</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>8.98999977111816</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>8.44999980926514</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>8.61999988555908</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>497678</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>8.53999996185303</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>8.6899995803833</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>8.64999961853027</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>242064</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>8.78999996185303</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>8.64999961853027</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>8.71000003814697</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>418675</v>
+        <v>152176</v>
       </c>
       <c r="C2715" t="n">
-        <v>9.92000007629395</v>
+        <v>9.89999961853027</v>
       </c>
       <c r="D2715" t="n">
-        <v>9.76000022888184</v>
+        <v>9.77999973297119</v>
       </c>
       <c r="E2715" t="n">
+        <v>9.85999965667725</v>
+      </c>
+      <c r="F2715" t="n">
         <v>9.85000038146973</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>9.88000011444092</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>192010</v>
+        <v>418675</v>
       </c>
       <c r="C2716" t="n">
         <v>9.92000007629395</v>
       </c>
       <c r="D2716" t="n">
-        <v>9.72000026702881</v>
+        <v>9.76000022888184</v>
       </c>
       <c r="E2716" t="n">
-        <v>9.92000007629395</v>
+        <v>9.85000038146973</v>
       </c>
       <c r="F2716" t="n">
-        <v>9.72000026702881</v>
+        <v>9.88000011444092</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>247307</v>
+        <v>192010</v>
       </c>
       <c r="C2717" t="n">
-        <v>9.85000038146973</v>
+        <v>9.92000007629395</v>
       </c>
       <c r="D2717" t="n">
-        <v>9.61999988555908</v>
+        <v>9.72000026702881</v>
       </c>
       <c r="E2717" t="n">
-        <v>9.69999980926514</v>
+        <v>9.92000007629395</v>
       </c>
       <c r="F2717" t="n">
-        <v>9.68000030517578</v>
+        <v>9.72000026702881</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>330775</v>
+        <v>247307</v>
       </c>
       <c r="C2718" t="n">
-        <v>9.75</v>
+        <v>9.85000038146973</v>
       </c>
       <c r="D2718" t="n">
-        <v>9.60000038146973</v>
+        <v>9.61999988555908</v>
       </c>
       <c r="E2718" t="n">
-        <v>9.60000038146973</v>
+        <v>9.69999980926514</v>
       </c>
       <c r="F2718" t="n">
-        <v>9.67000007629395</v>
+        <v>9.68000030517578</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>876003</v>
+        <v>330775</v>
       </c>
       <c r="C2719" t="n">
-        <v>9.63000011444092</v>
+        <v>9.75</v>
       </c>
       <c r="D2719" t="n">
-        <v>8.82999992370605</v>
+        <v>9.60000038146973</v>
       </c>
       <c r="E2719" t="n">
-        <v>9.61999988555908</v>
+        <v>9.60000038146973</v>
       </c>
       <c r="F2719" t="n">
-        <v>8.84000015258789</v>
+        <v>9.67000007629395</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>832416</v>
+        <v>876003</v>
       </c>
       <c r="C2720" t="n">
-        <v>8.98999977111816</v>
+        <v>9.63000011444092</v>
       </c>
       <c r="D2720" t="n">
-        <v>8.44999980926514</v>
+        <v>8.82999992370605</v>
       </c>
       <c r="E2720" t="n">
-        <v>8.89999961853027</v>
+        <v>9.61999988555908</v>
       </c>
       <c r="F2720" t="n">
-        <v>8.61999988555908</v>
+        <v>8.84000015258789</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>497678</v>
+        <v>832416</v>
       </c>
       <c r="C2721" t="n">
-        <v>8.76000022888184</v>
+        <v>8.98999977111816</v>
       </c>
       <c r="D2721" t="n">
-        <v>8.53999996185303</v>
+        <v>8.44999980926514</v>
       </c>
       <c r="E2721" t="n">
-        <v>8.6899995803833</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="F2721" t="n">
-        <v>8.64999961853027</v>
+        <v>8.61999988555908</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>242064</v>
+        <v>497678</v>
       </c>
       <c r="C2722" t="n">
-        <v>8.78999996185303</v>
+        <v>8.76000022888184</v>
       </c>
       <c r="D2722" t="n">
+        <v>8.53999996185303</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>8.6899995803833</v>
+      </c>
+      <c r="F2722" t="n">
         <v>8.64999961853027</v>
       </c>
-      <c r="E2722" t="n">
-        <v>8.65999984741211</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>8.71000003814697</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>420408</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>8.60999965667725</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>8.63000011444092</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>8.52000045776367</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>8.65999984741211</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>239534</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>8.86999988555908</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>8.78999996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>8.78999996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>8.85000038146973</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>185854</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>8.80000019073486</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>8.68000030517578</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>219246</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>8.52999973297119</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>8.60000038146973</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>8.57999992370605</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>241025</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>8.59000015258789</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>8.64999961853027</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>164876</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>8.61999988555908</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>8.61999988555908</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G2" t="n">
-        <v>2.77823328971863</v>
+        <v>2.77823376655579</v>
       </c>
       <c r="H2" t="n">
         <v>152343</v>
@@ -485,7 +485,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G4" t="n">
-        <v>2.72616267204285</v>
+        <v>2.72616243362427</v>
       </c>
       <c r="H4" t="n">
         <v>62746</v>
@@ -514,7 +514,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>2.67409157752991</v>
+        <v>2.67409181594849</v>
       </c>
       <c r="H5" t="n">
         <v>221162</v>
@@ -543,7 +543,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66233372688293</v>
+        <v>2.66233348846436</v>
       </c>
       <c r="H6" t="n">
         <v>101924</v>
@@ -572,7 +572,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64553689956665</v>
+        <v>2.64553666114807</v>
       </c>
       <c r="H7" t="n">
         <v>94529</v>
@@ -601,7 +601,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66233372688293</v>
+        <v>2.66233348846436</v>
       </c>
       <c r="H8" t="n">
         <v>67534</v>
@@ -630,7 +630,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68248987197876</v>
+        <v>2.68249011039734</v>
       </c>
       <c r="H9" t="n">
         <v>47799</v>
@@ -688,7 +688,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64217734336853</v>
+        <v>2.64217710494995</v>
       </c>
       <c r="H11" t="n">
         <v>143921</v>
@@ -717,7 +717,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G12" t="n">
-        <v>2.50444149971008</v>
+        <v>2.5044412612915</v>
       </c>
       <c r="H12" t="n">
         <v>233084</v>
@@ -804,7 +804,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G15" t="n">
-        <v>2.49604272842407</v>
+        <v>2.49604249000549</v>
       </c>
       <c r="H15" t="n">
         <v>236506</v>
@@ -862,7 +862,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G17" t="n">
-        <v>2.55483245849609</v>
+        <v>2.55483222007751</v>
       </c>
       <c r="H17" t="n">
         <v>111221</v>
@@ -920,7 +920,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G19" t="n">
-        <v>2.54475426673889</v>
+        <v>2.54475402832031</v>
       </c>
       <c r="H19" t="n">
         <v>36810</v>
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51955842971802</v>
+        <v>2.51955890655518</v>
       </c>
       <c r="H20" t="n">
         <v>71539</v>
@@ -978,7 +978,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52963709831238</v>
+        <v>2.5296368598938</v>
       </c>
       <c r="H21" t="n">
         <v>56267</v>
@@ -1036,7 +1036,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48764419555664</v>
+        <v>2.48764443397522</v>
       </c>
       <c r="H23" t="n">
         <v>72870</v>
@@ -1152,7 +1152,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22561025619507</v>
+        <v>2.22560977935791</v>
       </c>
       <c r="H27" t="n">
         <v>529181</v>
@@ -1210,7 +1210,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20041441917419</v>
+        <v>2.20041418075562</v>
       </c>
       <c r="H29" t="n">
         <v>154588</v>
@@ -1239,7 +1239,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G30" t="n">
-        <v>2.17689871788025</v>
+        <v>2.17689847946167</v>
       </c>
       <c r="H30" t="n">
         <v>105462</v>
@@ -1268,7 +1268,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G31" t="n">
-        <v>2.21049284934998</v>
+        <v>2.21049308776855</v>
       </c>
       <c r="H31" t="n">
         <v>93450</v>
@@ -1297,7 +1297,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G32" t="n">
-        <v>2.31463479995728</v>
+        <v>2.31463432312012</v>
       </c>
       <c r="H32" t="n">
         <v>95609</v>
@@ -1355,7 +1355,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45237016677856</v>
+        <v>2.45237040519714</v>
       </c>
       <c r="H34" t="n">
         <v>111775</v>
@@ -1384,7 +1384,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G35" t="n">
-        <v>2.49100375175476</v>
+        <v>2.49100351333618</v>
       </c>
       <c r="H35" t="n">
         <v>110175</v>
@@ -1500,7 +1500,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>2.41205716133118</v>
+        <v>2.41205739974976</v>
       </c>
       <c r="H39" t="n">
         <v>479838</v>
@@ -1529,7 +1529,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G40" t="n">
-        <v>2.56827020645142</v>
+        <v>2.56827044487</v>
       </c>
       <c r="H40" t="n">
         <v>281502</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51955842971802</v>
+        <v>2.51955890655518</v>
       </c>
       <c r="H41" t="n">
         <v>243349</v>
@@ -1587,7 +1587,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G42" t="n">
-        <v>2.539715051651</v>
+        <v>2.53971529006958</v>
       </c>
       <c r="H42" t="n">
         <v>123602</v>
@@ -1616,7 +1616,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G43" t="n">
-        <v>2.59178590774536</v>
+        <v>2.59178638458252</v>
       </c>
       <c r="H43" t="n">
         <v>130900</v>
@@ -1674,7 +1674,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G45" t="n">
-        <v>2.59178590774536</v>
+        <v>2.59178638458252</v>
       </c>
       <c r="H45" t="n">
         <v>107783</v>
@@ -1732,7 +1732,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G47" t="n">
-        <v>2.56659030914307</v>
+        <v>2.56659078598022</v>
       </c>
       <c r="H47" t="n">
         <v>91697</v>
@@ -1761,7 +1761,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G48" t="n">
-        <v>2.539715051651</v>
+        <v>2.53971529006958</v>
       </c>
       <c r="H48" t="n">
         <v>18221</v>
@@ -1819,7 +1819,7 @@
         <v>2.98200011253357</v>
       </c>
       <c r="G50" t="n">
-        <v>2.50444149971008</v>
+        <v>2.5044412612915</v>
       </c>
       <c r="H50" t="n">
         <v>104942</v>
@@ -1848,7 +1848,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.57666873931885</v>
+        <v>2.57666850090027</v>
       </c>
       <c r="H51" t="n">
         <v>72645</v>
@@ -1877,7 +1877,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G52" t="n">
-        <v>2.63545775413513</v>
+        <v>2.63545823097229</v>
       </c>
       <c r="H52" t="n">
         <v>192821</v>
@@ -1935,7 +1935,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G54" t="n">
-        <v>2.63713836669922</v>
+        <v>2.63713788986206</v>
       </c>
       <c r="H54" t="n">
         <v>77417</v>
@@ -1964,7 +1964,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G55" t="n">
-        <v>2.63713836669922</v>
+        <v>2.63713788986206</v>
       </c>
       <c r="H55" t="n">
         <v>165084</v>
@@ -1993,7 +1993,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>2.61194252967834</v>
+        <v>2.61194205284119</v>
       </c>
       <c r="H56" t="n">
         <v>79540</v>
@@ -2022,7 +2022,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G57" t="n">
-        <v>2.63881778717041</v>
+        <v>2.63881731033325</v>
       </c>
       <c r="H57" t="n">
         <v>56554</v>
@@ -2051,7 +2051,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G58" t="n">
-        <v>2.62370014190674</v>
+        <v>2.62370038032532</v>
       </c>
       <c r="H58" t="n">
         <v>66398</v>
@@ -2109,7 +2109,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56323146820068</v>
+        <v>2.5632312297821</v>
       </c>
       <c r="H60" t="n">
         <v>42243</v>
@@ -2138,7 +2138,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>2.56323146820068</v>
+        <v>2.5632312297821</v>
       </c>
       <c r="H61" t="n">
         <v>22329</v>
@@ -2167,7 +2167,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>2.57498908042908</v>
+        <v>2.5749888420105</v>
       </c>
       <c r="H62" t="n">
         <v>63758</v>
@@ -2196,7 +2196,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G63" t="n">
-        <v>2.63209867477417</v>
+        <v>2.63209891319275</v>
       </c>
       <c r="H63" t="n">
         <v>31651</v>
@@ -2225,7 +2225,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G64" t="n">
-        <v>2.64553689956665</v>
+        <v>2.64553666114807</v>
       </c>
       <c r="H64" t="n">
         <v>86631</v>
@@ -2283,7 +2283,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G66" t="n">
-        <v>2.58506727218628</v>
+        <v>2.5850670337677</v>
       </c>
       <c r="H66" t="n">
         <v>94314</v>
@@ -2341,7 +2341,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G68" t="n">
-        <v>2.59010624885559</v>
+        <v>2.59010648727417</v>
       </c>
       <c r="H68" t="n">
         <v>75467</v>
@@ -2370,7 +2370,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G69" t="n">
-        <v>2.56827020645142</v>
+        <v>2.56827044487</v>
       </c>
       <c r="H69" t="n">
         <v>60387</v>
@@ -2399,7 +2399,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G70" t="n">
-        <v>2.63545775413513</v>
+        <v>2.63545823097229</v>
       </c>
       <c r="H70" t="n">
         <v>82625</v>
@@ -2428,7 +2428,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G71" t="n">
-        <v>2.65729427337646</v>
+        <v>2.65729451179504</v>
       </c>
       <c r="H71" t="n">
         <v>90621</v>
@@ -2486,7 +2486,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.66737270355225</v>
+        <v>2.66737294197083</v>
       </c>
       <c r="H73" t="n">
         <v>66614</v>
@@ -2515,7 +2515,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G74" t="n">
-        <v>2.66065382957458</v>
+        <v>2.66065359115601</v>
       </c>
       <c r="H74" t="n">
         <v>20828</v>
@@ -2544,7 +2544,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G75" t="n">
-        <v>2.63209867477417</v>
+        <v>2.63209891319275</v>
       </c>
       <c r="H75" t="n">
         <v>52279</v>
@@ -2573,7 +2573,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>2.64553689956665</v>
+        <v>2.64553666114807</v>
       </c>
       <c r="H76" t="n">
         <v>87034</v>
@@ -2602,7 +2602,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.67913055419922</v>
+        <v>2.67913103103638</v>
       </c>
       <c r="H77" t="n">
         <v>80578</v>
@@ -2631,7 +2631,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G78" t="n">
-        <v>2.63713836669922</v>
+        <v>2.63713788986206</v>
       </c>
       <c r="H78" t="n">
         <v>62187</v>
@@ -2660,7 +2660,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.60354351997375</v>
+        <v>2.60354328155518</v>
       </c>
       <c r="H79" t="n">
         <v>67023</v>
@@ -2689,7 +2689,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>2.60354351997375</v>
+        <v>2.60354328155518</v>
       </c>
       <c r="H80" t="n">
         <v>25508</v>
@@ -2718,7 +2718,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G81" t="n">
-        <v>2.62537980079651</v>
+        <v>2.62538003921509</v>
       </c>
       <c r="H81" t="n">
         <v>105903</v>
@@ -2747,7 +2747,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G82" t="n">
-        <v>2.61194252967834</v>
+        <v>2.61194205284119</v>
       </c>
       <c r="H82" t="n">
         <v>47197</v>
@@ -2805,7 +2805,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G84" t="n">
-        <v>2.63377857208252</v>
+        <v>2.63377809524536</v>
       </c>
       <c r="H84" t="n">
         <v>80921</v>
@@ -2921,7 +2921,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59010624885559</v>
+        <v>2.59010648727417</v>
       </c>
       <c r="H88" t="n">
         <v>31696</v>
@@ -2950,7 +2950,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G89" t="n">
-        <v>2.56491041183472</v>
+        <v>2.56491088867188</v>
       </c>
       <c r="H89" t="n">
         <v>41649</v>
@@ -2979,7 +2979,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>2.64553689956665</v>
+        <v>2.64553666114807</v>
       </c>
       <c r="H90" t="n">
         <v>52351</v>
@@ -3008,7 +3008,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59682536125183</v>
+        <v>2.59682559967041</v>
       </c>
       <c r="H91" t="n">
         <v>56203</v>
@@ -3037,7 +3037,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G92" t="n">
-        <v>2.61194252967834</v>
+        <v>2.61194205284119</v>
       </c>
       <c r="H92" t="n">
         <v>177199</v>
@@ -3066,7 +3066,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G93" t="n">
-        <v>2.61194252967834</v>
+        <v>2.61194205284119</v>
       </c>
       <c r="H93" t="n">
         <v>159194</v>
@@ -3095,7 +3095,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G94" t="n">
-        <v>2.65393543243408</v>
+        <v>2.65393495559692</v>
       </c>
       <c r="H94" t="n">
         <v>160303</v>
@@ -3124,7 +3124,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>2.68752956390381</v>
+        <v>2.68752932548523</v>
       </c>
       <c r="H95" t="n">
         <v>75303</v>
@@ -3182,7 +3182,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G97" t="n">
-        <v>2.71272468566895</v>
+        <v>2.71272444725037</v>
       </c>
       <c r="H97" t="n">
         <v>185551</v>
@@ -3211,7 +3211,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G98" t="n">
-        <v>2.71272468566895</v>
+        <v>2.71272444725037</v>
       </c>
       <c r="H98" t="n">
         <v>83766</v>
@@ -3240,7 +3240,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>2.71272468566895</v>
+        <v>2.71272444725037</v>
       </c>
       <c r="H99" t="n">
         <v>89690</v>
@@ -3298,7 +3298,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G101" t="n">
-        <v>2.83030438423157</v>
+        <v>2.83030390739441</v>
       </c>
       <c r="H101" t="n">
         <v>133246</v>
@@ -3327,7 +3327,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>2.89581251144409</v>
+        <v>2.89581274986267</v>
       </c>
       <c r="H102" t="n">
         <v>232119</v>
@@ -3385,7 +3385,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G104" t="n">
-        <v>2.95460247993469</v>
+        <v>2.95460224151611</v>
       </c>
       <c r="H104" t="n">
         <v>202295</v>
@@ -3414,7 +3414,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>2.97425746917725</v>
+        <v>2.97425723075867</v>
       </c>
       <c r="H105" t="n">
         <v>77690</v>
@@ -3443,7 +3443,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G106" t="n">
-        <v>2.96571063995361</v>
+        <v>2.96571040153503</v>
       </c>
       <c r="H106" t="n">
         <v>150398</v>
@@ -3472,7 +3472,7 @@
         <v>3.5</v>
       </c>
       <c r="G107" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H107" t="n">
         <v>138310</v>
@@ -3501,7 +3501,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01699090003967</v>
+        <v>3.01699113845825</v>
       </c>
       <c r="H108" t="n">
         <v>89579</v>
@@ -3530,7 +3530,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G109" t="n">
-        <v>2.97938585281372</v>
+        <v>2.97938561439514</v>
       </c>
       <c r="H109" t="n">
         <v>62868</v>
@@ -3559,7 +3559,7 @@
         <v>3.5</v>
       </c>
       <c r="G110" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H110" t="n">
         <v>61822</v>
@@ -3588,7 +3588,7 @@
         <v>3.5</v>
       </c>
       <c r="G111" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H111" t="n">
         <v>108157</v>
@@ -3617,7 +3617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>2.97425746917725</v>
+        <v>2.97425723075867</v>
       </c>
       <c r="H112" t="n">
         <v>75910</v>
@@ -3675,7 +3675,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>2.92297720909119</v>
+        <v>2.92297697067261</v>
       </c>
       <c r="H114" t="n">
         <v>205314</v>
@@ -3733,7 +3733,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G116" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H116" t="n">
         <v>111280</v>
@@ -3762,7 +3762,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G117" t="n">
-        <v>2.9058837890625</v>
+        <v>2.90588355064392</v>
       </c>
       <c r="H117" t="n">
         <v>61653</v>
@@ -3791,7 +3791,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>2.81186938285828</v>
+        <v>2.81186962127686</v>
       </c>
       <c r="H118" t="n">
         <v>99749</v>
@@ -3820,7 +3820,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G119" t="n">
-        <v>2.86315035820007</v>
+        <v>2.86314988136292</v>
       </c>
       <c r="H119" t="n">
         <v>181130</v>
@@ -3878,7 +3878,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G121" t="n">
-        <v>2.99476933479309</v>
+        <v>2.99476957321167</v>
       </c>
       <c r="H121" t="n">
         <v>63908</v>
@@ -3907,7 +3907,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.02553772926331</v>
+        <v>3.02553725242615</v>
       </c>
       <c r="H122" t="n">
         <v>240472</v>
@@ -3936,7 +3936,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>3.03921222686768</v>
+        <v>3.03921270370483</v>
       </c>
       <c r="H123" t="n">
         <v>125877</v>
@@ -3994,7 +3994,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>2.75546145439148</v>
+        <v>2.7554612159729</v>
       </c>
       <c r="H125" t="n">
         <v>151935</v>
@@ -4023,7 +4023,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G126" t="n">
-        <v>2.88195300102234</v>
+        <v>2.88195276260376</v>
       </c>
       <c r="H126" t="n">
         <v>123491</v>
@@ -4052,7 +4052,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G127" t="n">
-        <v>2.88879036903381</v>
+        <v>2.88878989219666</v>
       </c>
       <c r="H127" t="n">
         <v>47357</v>
@@ -4081,7 +4081,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G128" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H128" t="n">
         <v>47325</v>
@@ -4110,7 +4110,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G129" t="n">
-        <v>2.89220905303955</v>
+        <v>2.89220881462097</v>
       </c>
       <c r="H129" t="n">
         <v>68529</v>
@@ -4139,7 +4139,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H130" t="n">
         <v>8471</v>
@@ -4168,7 +4168,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G131" t="n">
-        <v>2.84605622291565</v>
+        <v>2.84605669975281</v>
       </c>
       <c r="H131" t="n">
         <v>18015</v>
@@ -4197,7 +4197,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G132" t="n">
-        <v>2.71785593032837</v>
+        <v>2.71785616874695</v>
       </c>
       <c r="H132" t="n">
         <v>69786</v>
@@ -4284,7 +4284,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G135" t="n">
-        <v>2.86315035820007</v>
+        <v>2.86314988136292</v>
       </c>
       <c r="H135" t="n">
         <v>188961</v>
@@ -4342,7 +4342,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G137" t="n">
-        <v>2.86315035820007</v>
+        <v>2.86314988136292</v>
       </c>
       <c r="H137" t="n">
         <v>143728</v>
@@ -4371,7 +4371,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G138" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H138" t="n">
         <v>110344</v>
@@ -4400,7 +4400,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G139" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H139" t="n">
         <v>72008</v>
@@ -4429,7 +4429,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89220905303955</v>
+        <v>2.89220881462097</v>
       </c>
       <c r="H140" t="n">
         <v>44705</v>
@@ -4458,7 +4458,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>2.87169694900513</v>
+        <v>2.87169671058655</v>
       </c>
       <c r="H141" t="n">
         <v>131250</v>
@@ -4487,7 +4487,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G142" t="n">
-        <v>2.98793196678162</v>
+        <v>2.9879322052002</v>
       </c>
       <c r="H142" t="n">
         <v>157097</v>
@@ -4516,7 +4516,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G143" t="n">
-        <v>2.98793196678162</v>
+        <v>2.9879322052002</v>
       </c>
       <c r="H143" t="n">
         <v>99267</v>
@@ -4545,7 +4545,7 @@
         <v>3.5</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H144" t="n">
         <v>111137</v>
@@ -4574,7 +4574,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G145" t="n">
-        <v>2.9828040599823</v>
+        <v>2.98280429840088</v>
       </c>
       <c r="H145" t="n">
         <v>14696</v>
@@ -4603,7 +4603,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G146" t="n">
-        <v>2.9828040599823</v>
+        <v>2.98280429840088</v>
       </c>
       <c r="H146" t="n">
         <v>58293</v>
@@ -4632,7 +4632,7 @@
         <v>3.5</v>
       </c>
       <c r="G147" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H147" t="n">
         <v>88477</v>
@@ -4661,7 +4661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>3.01699090003967</v>
+        <v>3.01699113845825</v>
       </c>
       <c r="H148" t="n">
         <v>229996</v>
@@ -4748,7 +4748,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G151" t="n">
-        <v>2.9759669303894</v>
+        <v>2.97596669197083</v>
       </c>
       <c r="H151" t="n">
         <v>153244</v>
@@ -4806,7 +4806,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>3.03408455848694</v>
+        <v>3.03408408164978</v>
       </c>
       <c r="H153" t="n">
         <v>70270</v>
@@ -4835,7 +4835,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08707427978516</v>
+        <v>3.08707404136658</v>
       </c>
       <c r="H154" t="n">
         <v>78818</v>
@@ -4864,7 +4864,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G155" t="n">
-        <v>3.128098487854</v>
+        <v>3.12809872627258</v>
       </c>
       <c r="H155" t="n">
         <v>153076</v>
@@ -4893,7 +4893,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>3.17766904830933</v>
+        <v>3.17766880989075</v>
       </c>
       <c r="H156" t="n">
         <v>125694</v>
@@ -4922,7 +4922,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G157" t="n">
-        <v>3.17766904830933</v>
+        <v>3.17766880989075</v>
       </c>
       <c r="H157" t="n">
         <v>74677</v>
@@ -4951,7 +4951,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G158" t="n">
-        <v>3.16228532791138</v>
+        <v>3.16228556632996</v>
       </c>
       <c r="H158" t="n">
         <v>141495</v>
@@ -4980,7 +4980,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.16228532791138</v>
+        <v>3.16228556632996</v>
       </c>
       <c r="H159" t="n">
         <v>92789</v>
@@ -5009,7 +5009,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G160" t="n">
-        <v>3.15373826026917</v>
+        <v>3.15373873710632</v>
       </c>
       <c r="H160" t="n">
         <v>54552</v>
@@ -5038,7 +5038,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G161" t="n">
-        <v>3.128098487854</v>
+        <v>3.12809872627258</v>
       </c>
       <c r="H161" t="n">
         <v>44019</v>
@@ -5067,7 +5067,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G162" t="n">
-        <v>3.17766904830933</v>
+        <v>3.17766880989075</v>
       </c>
       <c r="H162" t="n">
         <v>40904</v>
@@ -5096,7 +5096,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G163" t="n">
-        <v>3.16228532791138</v>
+        <v>3.16228556632996</v>
       </c>
       <c r="H163" t="n">
         <v>108272</v>
@@ -5183,7 +5183,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.17425060272217</v>
+        <v>3.17425012588501</v>
       </c>
       <c r="H166" t="n">
         <v>53864</v>
@@ -5212,7 +5212,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G167" t="n">
-        <v>3.14348268508911</v>
+        <v>3.14348220825195</v>
       </c>
       <c r="H167" t="n">
         <v>26131</v>
@@ -5241,7 +5241,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>3.17937874794006</v>
+        <v>3.17937850952148</v>
       </c>
       <c r="H168" t="n">
         <v>10423</v>
@@ -5270,7 +5270,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16228532791138</v>
+        <v>3.16228556632996</v>
       </c>
       <c r="H169" t="n">
         <v>60929</v>
@@ -5299,7 +5299,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G170" t="n">
-        <v>3.15373826026917</v>
+        <v>3.15373873710632</v>
       </c>
       <c r="H170" t="n">
         <v>91808</v>
@@ -5328,7 +5328,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G171" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H171" t="n">
         <v>47454</v>
@@ -5357,7 +5357,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G172" t="n">
-        <v>3.14348268508911</v>
+        <v>3.14348220825195</v>
       </c>
       <c r="H172" t="n">
         <v>83572</v>
@@ -5415,7 +5415,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H174" t="n">
         <v>87725</v>
@@ -5473,7 +5473,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G176" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H176" t="n">
         <v>91479</v>
@@ -5502,7 +5502,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>3.16228532791138</v>
+        <v>3.16228556632996</v>
       </c>
       <c r="H177" t="n">
         <v>92758</v>
@@ -5531,7 +5531,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G178" t="n">
-        <v>3.13322591781616</v>
+        <v>3.13322639465332</v>
       </c>
       <c r="H178" t="n">
         <v>32351</v>
@@ -5560,7 +5560,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H179" t="n">
         <v>75390</v>
@@ -5589,7 +5589,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H180" t="n">
         <v>50226</v>
@@ -5618,7 +5618,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G181" t="n">
-        <v>3.08707427978516</v>
+        <v>3.08707404136658</v>
       </c>
       <c r="H181" t="n">
         <v>81429</v>
@@ -5734,7 +5734,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08194589614868</v>
+        <v>3.08194613456726</v>
       </c>
       <c r="H185" t="n">
         <v>38222</v>
@@ -5792,7 +5792,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G187" t="n">
-        <v>3.107586145401</v>
+        <v>3.10758638381958</v>
       </c>
       <c r="H187" t="n">
         <v>53535</v>
@@ -5821,7 +5821,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G188" t="n">
-        <v>3.10587692260742</v>
+        <v>3.105877161026</v>
       </c>
       <c r="H188" t="n">
         <v>34306</v>
@@ -5850,7 +5850,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G189" t="n">
-        <v>3.07168984413147</v>
+        <v>3.07168960571289</v>
       </c>
       <c r="H189" t="n">
         <v>13448</v>
@@ -5879,7 +5879,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G190" t="n">
-        <v>3.0528872013092</v>
+        <v>3.05288743972778</v>
       </c>
       <c r="H190" t="n">
         <v>53980</v>
@@ -5908,7 +5908,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G191" t="n">
-        <v>3.10245823860168</v>
+        <v>3.10245847702026</v>
       </c>
       <c r="H191" t="n">
         <v>52101</v>
@@ -5966,7 +5966,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G193" t="n">
-        <v>3.07168984413147</v>
+        <v>3.07168960571289</v>
       </c>
       <c r="H193" t="n">
         <v>70631</v>
@@ -6053,7 +6053,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.15373826026917</v>
+        <v>3.15373873710632</v>
       </c>
       <c r="H196" t="n">
         <v>133023</v>
@@ -6082,7 +6082,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G197" t="n">
-        <v>3.15202903747559</v>
+        <v>3.15202879905701</v>
       </c>
       <c r="H197" t="n">
         <v>54450</v>
@@ -6111,7 +6111,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G198" t="n">
-        <v>3.19647216796875</v>
+        <v>3.19647240638733</v>
       </c>
       <c r="H198" t="n">
         <v>214245</v>
@@ -6140,7 +6140,7 @@
         <v>3.75</v>
       </c>
       <c r="G199" t="n">
-        <v>3.20501923561096</v>
+        <v>3.2050187587738</v>
       </c>
       <c r="H199" t="n">
         <v>160447</v>
@@ -6169,7 +6169,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G200" t="n">
-        <v>3.20330953598022</v>
+        <v>3.20330929756165</v>
       </c>
       <c r="H200" t="n">
         <v>78395</v>
@@ -6198,7 +6198,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G201" t="n">
-        <v>3.11442399024963</v>
+        <v>3.11442351341248</v>
       </c>
       <c r="H201" t="n">
         <v>81316</v>
@@ -6256,7 +6256,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G203" t="n">
-        <v>3.13493585586548</v>
+        <v>3.1349356174469</v>
       </c>
       <c r="H203" t="n">
         <v>81760</v>
@@ -6343,7 +6343,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G206" t="n">
-        <v>3.14348268508911</v>
+        <v>3.14348220825195</v>
       </c>
       <c r="H206" t="n">
         <v>62561</v>
@@ -6372,7 +6372,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H207" t="n">
         <v>58958</v>
@@ -6430,7 +6430,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G209" t="n">
-        <v>3.14348268508911</v>
+        <v>3.14348220825195</v>
       </c>
       <c r="H209" t="n">
         <v>79922</v>
@@ -6459,7 +6459,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G210" t="n">
-        <v>3.11784219741821</v>
+        <v>3.11784195899963</v>
       </c>
       <c r="H210" t="n">
         <v>130183</v>
@@ -6488,7 +6488,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.128098487854</v>
+        <v>3.12809872627258</v>
       </c>
       <c r="H211" t="n">
         <v>65236</v>
@@ -6517,7 +6517,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G212" t="n">
-        <v>3.14519166946411</v>
+        <v>3.14519190788269</v>
       </c>
       <c r="H212" t="n">
         <v>166561</v>
@@ -6546,7 +6546,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G213" t="n">
-        <v>3.15373826026917</v>
+        <v>3.15373873710632</v>
       </c>
       <c r="H213" t="n">
         <v>78310</v>
@@ -6575,7 +6575,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.128098487854</v>
+        <v>3.12809872627258</v>
       </c>
       <c r="H214" t="n">
         <v>116511</v>
@@ -6604,7 +6604,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G215" t="n">
-        <v>3.15032005310059</v>
+        <v>3.15031957626343</v>
       </c>
       <c r="H215" t="n">
         <v>37592</v>
@@ -6633,7 +6633,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G216" t="n">
-        <v>3.07339906692505</v>
+        <v>3.07339930534363</v>
       </c>
       <c r="H216" t="n">
         <v>100487</v>
@@ -6691,7 +6691,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G218" t="n">
-        <v>3.02211904525757</v>
+        <v>3.02211928367615</v>
       </c>
       <c r="H218" t="n">
         <v>98671</v>
@@ -6720,7 +6720,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G219" t="n">
-        <v>3.05459666252136</v>
+        <v>3.05459642410278</v>
       </c>
       <c r="H219" t="n">
         <v>107982</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>2.97425746917725</v>
+        <v>2.97425723075867</v>
       </c>
       <c r="H220" t="n">
         <v>74403</v>
@@ -6865,7 +6865,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G224" t="n">
-        <v>3.05117750167847</v>
+        <v>3.05117774009705</v>
       </c>
       <c r="H224" t="n">
         <v>86249</v>
@@ -6894,7 +6894,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G225" t="n">
-        <v>3.04946827888489</v>
+        <v>3.04946875572205</v>
       </c>
       <c r="H225" t="n">
         <v>86643</v>
@@ -6923,7 +6923,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>3.03408455848694</v>
+        <v>3.03408408164978</v>
       </c>
       <c r="H226" t="n">
         <v>68454</v>
@@ -6952,7 +6952,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G227" t="n">
-        <v>3.0375030040741</v>
+        <v>3.03750276565552</v>
       </c>
       <c r="H227" t="n">
         <v>61249</v>
@@ -6981,7 +6981,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G228" t="n">
-        <v>3.02382850646973</v>
+        <v>3.02382826805115</v>
       </c>
       <c r="H228" t="n">
         <v>492149</v>
@@ -7010,7 +7010,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G229" t="n">
-        <v>3.02382850646973</v>
+        <v>3.02382826805115</v>
       </c>
       <c r="H229" t="n">
         <v>60528</v>
@@ -7039,7 +7039,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>3.02553772926331</v>
+        <v>3.02553725242615</v>
       </c>
       <c r="H230" t="n">
         <v>82568</v>
@@ -7068,7 +7068,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.99989795684814</v>
+        <v>2.99989748001099</v>
       </c>
       <c r="H231" t="n">
         <v>75544</v>
@@ -7097,7 +7097,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G232" t="n">
-        <v>3.01357245445251</v>
+        <v>3.01357269287109</v>
       </c>
       <c r="H232" t="n">
         <v>19834</v>
@@ -7126,7 +7126,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G233" t="n">
-        <v>3.00502562522888</v>
+        <v>3.0050253868103</v>
       </c>
       <c r="H233" t="n">
         <v>37168</v>
@@ -7184,7 +7184,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.96571063995361</v>
+        <v>2.96571040153503</v>
       </c>
       <c r="H235" t="n">
         <v>54912</v>
@@ -7213,7 +7213,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G236" t="n">
-        <v>3.0375030040741</v>
+        <v>3.03750276565552</v>
       </c>
       <c r="H236" t="n">
         <v>129585</v>
@@ -7242,7 +7242,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>3.01699090003967</v>
+        <v>3.01699113845825</v>
       </c>
       <c r="H237" t="n">
         <v>103881</v>
@@ -7271,7 +7271,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G238" t="n">
-        <v>2.99476933479309</v>
+        <v>2.99476957321167</v>
       </c>
       <c r="H238" t="n">
         <v>81090</v>
@@ -7300,7 +7300,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G239" t="n">
-        <v>3.03408455848694</v>
+        <v>3.03408408164978</v>
       </c>
       <c r="H239" t="n">
         <v>118074</v>
@@ -7329,7 +7329,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G240" t="n">
-        <v>3.03921222686768</v>
+        <v>3.03921270370483</v>
       </c>
       <c r="H240" t="n">
         <v>109816</v>
@@ -7358,7 +7358,7 @@
         <v>3.5</v>
       </c>
       <c r="G241" t="n">
-        <v>2.99135112762451</v>
+        <v>2.99135065078735</v>
       </c>
       <c r="H241" t="n">
         <v>377862</v>
@@ -7474,7 +7474,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G245" t="n">
-        <v>3.128098487854</v>
+        <v>3.12809872627258</v>
       </c>
       <c r="H245" t="n">
         <v>161129</v>
@@ -7503,7 +7503,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G246" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H246" t="n">
         <v>286401</v>
@@ -7619,7 +7619,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G250" t="n">
-        <v>3.08707427978516</v>
+        <v>3.08707404136658</v>
       </c>
       <c r="H250" t="n">
         <v>207332</v>
@@ -7648,7 +7648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H251" t="n">
         <v>385619</v>
@@ -7677,7 +7677,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G252" t="n">
-        <v>3.07339906692505</v>
+        <v>3.07339930534363</v>
       </c>
       <c r="H252" t="n">
         <v>192710</v>
@@ -7735,7 +7735,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G254" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H254" t="n">
         <v>208908</v>
@@ -7764,7 +7764,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H255" t="n">
         <v>176587</v>
@@ -7793,7 +7793,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G256" t="n">
-        <v>3.06143426895142</v>
+        <v>3.06143403053284</v>
       </c>
       <c r="H256" t="n">
         <v>109911</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H257" t="n">
         <v>123713</v>
@@ -7851,7 +7851,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G258" t="n">
-        <v>3.12297081947327</v>
+        <v>3.12297034263611</v>
       </c>
       <c r="H258" t="n">
         <v>207540</v>
@@ -7880,7 +7880,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G259" t="n">
-        <v>3.15373826026917</v>
+        <v>3.15373873710632</v>
       </c>
       <c r="H259" t="n">
         <v>263684</v>
@@ -7967,7 +7967,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G262" t="n">
-        <v>3.09733009338379</v>
+        <v>3.09733033180237</v>
       </c>
       <c r="H262" t="n">
         <v>78644</v>
@@ -7996,7 +7996,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G263" t="n">
-        <v>3.07510876655579</v>
+        <v>3.07510900497437</v>
       </c>
       <c r="H263" t="n">
         <v>104543</v>
@@ -8054,7 +8054,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>3.06485271453857</v>
+        <v>3.06485247612</v>
       </c>
       <c r="H265" t="n">
         <v>127492</v>
@@ -8083,7 +8083,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>3.0802366733551</v>
+        <v>3.08023691177368</v>
       </c>
       <c r="H266" t="n">
         <v>158916</v>
@@ -8112,7 +8112,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>3.07681775093079</v>
+        <v>3.07681822776794</v>
       </c>
       <c r="H267" t="n">
         <v>125273</v>
@@ -8141,7 +8141,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G268" t="n">
-        <v>3.05630612373352</v>
+        <v>3.05630564689636</v>
       </c>
       <c r="H268" t="n">
         <v>94444</v>
@@ -8199,7 +8199,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G270" t="n">
-        <v>3.04946827888489</v>
+        <v>3.04946875572205</v>
       </c>
       <c r="H270" t="n">
         <v>126994</v>
@@ -8257,7 +8257,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.22211194038391</v>
+        <v>3.22211265563965</v>
       </c>
       <c r="H272" t="n">
         <v>187201</v>
@@ -8286,7 +8286,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G273" t="n">
-        <v>3.34689426422119</v>
+        <v>3.34689378738403</v>
       </c>
       <c r="H273" t="n">
         <v>449364</v>
@@ -8315,7 +8315,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G274" t="n">
-        <v>3.3315098285675</v>
+        <v>3.33151006698608</v>
       </c>
       <c r="H274" t="n">
         <v>254945</v>
@@ -8373,7 +8373,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G276" t="n">
-        <v>3.35885953903198</v>
+        <v>3.35885977745056</v>
       </c>
       <c r="H276" t="n">
         <v>342113</v>
@@ -8489,7 +8489,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>3.38449931144714</v>
+        <v>3.38450002670288</v>
       </c>
       <c r="H280" t="n">
         <v>93708</v>
@@ -8576,7 +8576,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G283" t="n">
-        <v>3.34176659584045</v>
+        <v>3.34176635742188</v>
       </c>
       <c r="H283" t="n">
         <v>130360</v>
@@ -8605,7 +8605,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G284" t="n">
-        <v>3.3862087726593</v>
+        <v>3.38620901107788</v>
       </c>
       <c r="H284" t="n">
         <v>98208</v>
@@ -8721,7 +8721,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G288" t="n">
-        <v>3.34860372543335</v>
+        <v>3.34860348701477</v>
       </c>
       <c r="H288" t="n">
         <v>99309</v>
@@ -8808,7 +8808,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.37595319747925</v>
+        <v>3.37595295906067</v>
       </c>
       <c r="H291" t="n">
         <v>127566</v>
@@ -8837,7 +8837,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.37595319747925</v>
+        <v>3.37595295906067</v>
       </c>
       <c r="H292" t="n">
         <v>113666</v>
@@ -8866,7 +8866,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.37595319747925</v>
+        <v>3.37595295906067</v>
       </c>
       <c r="H293" t="n">
         <v>158578</v>
@@ -8924,7 +8924,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G295" t="n">
-        <v>3.45458245277405</v>
+        <v>3.45458269119263</v>
       </c>
       <c r="H295" t="n">
         <v>264871</v>
@@ -8982,7 +8982,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G297" t="n">
-        <v>3.45116424560547</v>
+        <v>3.45116448402405</v>
       </c>
       <c r="H297" t="n">
         <v>239070</v>
@@ -9011,7 +9011,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G298" t="n">
-        <v>3.43919897079468</v>
+        <v>3.4391987323761</v>
       </c>
       <c r="H298" t="n">
         <v>122801</v>
@@ -9040,7 +9040,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G299" t="n">
-        <v>3.48535108566284</v>
+        <v>3.48535084724426</v>
       </c>
       <c r="H299" t="n">
         <v>178480</v>
@@ -9098,7 +9098,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G301" t="n">
-        <v>3.5844931602478</v>
+        <v>3.58449292182922</v>
       </c>
       <c r="H301" t="n">
         <v>285880</v>
@@ -9127,7 +9127,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>3.54688739776611</v>
+        <v>3.54688787460327</v>
       </c>
       <c r="H302" t="n">
         <v>281445</v>
@@ -9156,7 +9156,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G303" t="n">
-        <v>3.52637529373169</v>
+        <v>3.52637505531311</v>
       </c>
       <c r="H303" t="n">
         <v>224923</v>
@@ -9185,7 +9185,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53834056854248</v>
+        <v>3.53834080696106</v>
       </c>
       <c r="H304" t="n">
         <v>178128</v>
@@ -9243,7 +9243,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>3.52124691009521</v>
+        <v>3.52124714851379</v>
       </c>
       <c r="H306" t="n">
         <v>284296</v>
@@ -9272,7 +9272,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G307" t="n">
-        <v>3.60329580307007</v>
+        <v>3.60329604148865</v>
       </c>
       <c r="H307" t="n">
         <v>348389</v>
@@ -9301,7 +9301,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G308" t="n">
-        <v>3.70243716239929</v>
+        <v>3.70243740081787</v>
       </c>
       <c r="H308" t="n">
         <v>311354</v>
@@ -9330,7 +9330,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>3.67508792877197</v>
+        <v>3.67508840560913</v>
       </c>
       <c r="H309" t="n">
         <v>234969</v>
@@ -9359,7 +9359,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.67508792877197</v>
+        <v>3.67508840560913</v>
       </c>
       <c r="H310" t="n">
         <v>376882</v>
@@ -9475,7 +9475,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>3.84089422225952</v>
+        <v>3.84089469909668</v>
       </c>
       <c r="H314" t="n">
         <v>389841</v>
@@ -9504,7 +9504,7 @@
         <v>4.53800010681152</v>
       </c>
       <c r="G315" t="n">
-        <v>3.87850046157837</v>
+        <v>3.87849974632263</v>
       </c>
       <c r="H315" t="n">
         <v>708378</v>
@@ -9562,7 +9562,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>3.95713019371033</v>
+        <v>3.95712971687317</v>
       </c>
       <c r="H317" t="n">
         <v>403814</v>
@@ -9649,7 +9649,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G320" t="n">
-        <v>3.98447871208191</v>
+        <v>3.98447918891907</v>
       </c>
       <c r="H320" t="n">
         <v>380294</v>
@@ -9678,7 +9678,7 @@
         <v>4.64400005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>3.96909499168396</v>
+        <v>3.96909546852112</v>
       </c>
       <c r="H321" t="n">
         <v>219480</v>
@@ -9736,7 +9736,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G323" t="n">
-        <v>3.99815368652344</v>
+        <v>3.9981541633606</v>
       </c>
       <c r="H323" t="n">
         <v>269524</v>
@@ -9794,7 +9794,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G325" t="n">
-        <v>4.07336521148682</v>
+        <v>4.07336473464966</v>
       </c>
       <c r="H325" t="n">
         <v>309394</v>
@@ -9852,7 +9852,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G327" t="n">
-        <v>4.02208471298218</v>
+        <v>4.02208518981934</v>
       </c>
       <c r="H327" t="n">
         <v>123388</v>
@@ -9881,7 +9881,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>4.00841093063354</v>
+        <v>4.00841045379639</v>
       </c>
       <c r="H328" t="n">
         <v>291725</v>
@@ -9939,7 +9939,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>4.02550315856934</v>
+        <v>4.02550363540649</v>
       </c>
       <c r="H330" t="n">
         <v>506896</v>
@@ -9997,7 +9997,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G332" t="n">
-        <v>3.99302506446838</v>
+        <v>3.99302554130554</v>
       </c>
       <c r="H332" t="n">
         <v>556368</v>
@@ -10026,7 +10026,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G333" t="n">
-        <v>4.06823778152466</v>
+        <v>4.0682373046875</v>
       </c>
       <c r="H333" t="n">
         <v>339562</v>
@@ -10142,7 +10142,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.2220778465271</v>
+        <v>4.22207832336426</v>
       </c>
       <c r="H337" t="n">
         <v>265017</v>
@@ -10171,7 +10171,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33318662643433</v>
+        <v>4.33318567276001</v>
       </c>
       <c r="H338" t="n">
         <v>397358</v>
@@ -10258,7 +10258,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.4442925453186</v>
+        <v>4.44429206848145</v>
       </c>
       <c r="H341" t="n">
         <v>510342</v>
@@ -10287,7 +10287,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>4.36737203598022</v>
+        <v>4.36737251281738</v>
       </c>
       <c r="H342" t="n">
         <v>409995</v>
@@ -10316,7 +10316,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.4442925453186</v>
+        <v>4.44429206848145</v>
       </c>
       <c r="H343" t="n">
         <v>316502</v>
@@ -10345,7 +10345,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.4442925453186</v>
+        <v>4.44429206848145</v>
       </c>
       <c r="H344" t="n">
         <v>380014</v>
@@ -10374,7 +10374,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G345" t="n">
-        <v>4.43574571609497</v>
+        <v>4.43574523925781</v>
       </c>
       <c r="H345" t="n">
         <v>221235</v>
@@ -10403,7 +10403,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G346" t="n">
-        <v>4.46138572692871</v>
+        <v>4.46138525009155</v>
       </c>
       <c r="H346" t="n">
         <v>324637</v>
@@ -10432,7 +10432,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>4.40155982971191</v>
+        <v>4.40155935287476</v>
       </c>
       <c r="H347" t="n">
         <v>342562</v>
@@ -10461,7 +10461,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>4.35455226898193</v>
+        <v>4.35455179214478</v>
       </c>
       <c r="H348" t="n">
         <v>1219966</v>
@@ -10490,7 +10490,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>4.46565914154053</v>
+        <v>4.46565961837769</v>
       </c>
       <c r="H349" t="n">
         <v>327373</v>
@@ -10519,7 +10519,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G350" t="n">
-        <v>4.51266717910767</v>
+        <v>4.51266670227051</v>
       </c>
       <c r="H350" t="n">
         <v>467077</v>
@@ -10548,7 +10548,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G351" t="n">
-        <v>4.67505407333374</v>
+        <v>4.67505359649658</v>
       </c>
       <c r="H351" t="n">
         <v>642036</v>
@@ -10577,7 +10577,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G352" t="n">
-        <v>4.57676601409912</v>
+        <v>4.57676649093628</v>
       </c>
       <c r="H352" t="n">
         <v>707468</v>
@@ -10606,7 +10606,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>4.67078161239624</v>
+        <v>4.67078113555908</v>
       </c>
       <c r="H353" t="n">
         <v>658370</v>
@@ -10635,7 +10635,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>4.72206115722656</v>
+        <v>4.72206163406372</v>
       </c>
       <c r="H354" t="n">
         <v>446009</v>
@@ -10664,7 +10664,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G355" t="n">
-        <v>4.79470825195312</v>
+        <v>4.79470777511597</v>
       </c>
       <c r="H355" t="n">
         <v>451947</v>
@@ -10780,7 +10780,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G359" t="n">
-        <v>4.97418928146362</v>
+        <v>4.97418832778931</v>
       </c>
       <c r="H359" t="n">
         <v>377192</v>
@@ -10838,7 +10838,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G361" t="n">
-        <v>4.91277551651001</v>
+        <v>4.91277599334717</v>
       </c>
       <c r="H361" t="n">
         <v>376356</v>
@@ -10867,7 +10867,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G362" t="n">
-        <v>4.9516978263855</v>
+        <v>4.95169734954834</v>
       </c>
       <c r="H362" t="n">
         <v>528310</v>
@@ -10925,7 +10925,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G364" t="n">
-        <v>5.01656675338745</v>
+        <v>5.01656723022461</v>
       </c>
       <c r="H364" t="n">
         <v>344747</v>
@@ -10983,7 +10983,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G366" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H366" t="n">
         <v>493739</v>
@@ -11012,7 +11012,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G367" t="n">
-        <v>4.92142486572266</v>
+        <v>4.92142534255981</v>
       </c>
       <c r="H367" t="n">
         <v>452657</v>
@@ -11070,7 +11070,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G369" t="n">
-        <v>4.8479061126709</v>
+        <v>4.84790658950806</v>
       </c>
       <c r="H369" t="n">
         <v>306807</v>
@@ -11099,7 +11099,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>4.52356004714966</v>
+        <v>4.52355909347534</v>
       </c>
       <c r="H370" t="n">
         <v>1242963</v>
@@ -11186,7 +11186,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>4.46301460266113</v>
+        <v>4.46301507949829</v>
       </c>
       <c r="H373" t="n">
         <v>627722</v>
@@ -11215,7 +11215,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G374" t="n">
-        <v>4.48031330108643</v>
+        <v>4.48031234741211</v>
       </c>
       <c r="H374" t="n">
         <v>293039</v>
@@ -11360,7 +11360,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>4.44571590423584</v>
+        <v>4.445716381073</v>
       </c>
       <c r="H379" t="n">
         <v>145570</v>
@@ -11389,7 +11389,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G380" t="n">
-        <v>4.59275341033936</v>
+        <v>4.59275388717651</v>
       </c>
       <c r="H380" t="n">
         <v>260836</v>
@@ -11418,7 +11418,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>4.51058578491211</v>
+        <v>4.51058626174927</v>
       </c>
       <c r="H381" t="n">
         <v>268402</v>
@@ -11447,7 +11447,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>4.55815696716309</v>
+        <v>4.55815649032593</v>
       </c>
       <c r="H382" t="n">
         <v>212506</v>
@@ -11563,7 +11563,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G386" t="n">
-        <v>4.31597805023193</v>
+        <v>4.31597661972046</v>
       </c>
       <c r="H386" t="n">
         <v>270746</v>
@@ -11621,7 +11621,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36354827880859</v>
+        <v>4.36354875564575</v>
       </c>
       <c r="H388" t="n">
         <v>158333</v>
@@ -11679,7 +11679,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G390" t="n">
-        <v>4.46301460266113</v>
+        <v>4.46301507949829</v>
       </c>
       <c r="H390" t="n">
         <v>278617</v>
@@ -11708,7 +11708,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>4.415442943573</v>
+        <v>4.41544389724731</v>
       </c>
       <c r="H391" t="n">
         <v>285596</v>
@@ -11737,7 +11737,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G392" t="n">
-        <v>4.55815696716309</v>
+        <v>4.55815649032593</v>
       </c>
       <c r="H392" t="n">
         <v>285504</v>
@@ -11766,7 +11766,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G393" t="n">
-        <v>4.60140323638916</v>
+        <v>4.601402759552</v>
       </c>
       <c r="H393" t="n">
         <v>198710</v>
@@ -11911,7 +11911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G398" t="n">
-        <v>4.65329837799072</v>
+        <v>4.65329790115356</v>
       </c>
       <c r="H398" t="n">
         <v>188616</v>
@@ -11940,7 +11940,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.63167476654053</v>
+        <v>4.63167572021484</v>
       </c>
       <c r="H399" t="n">
         <v>100820</v>
@@ -11969,7 +11969,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>4.65329837799072</v>
+        <v>4.65329790115356</v>
       </c>
       <c r="H400" t="n">
         <v>91142</v>
@@ -12085,7 +12085,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G404" t="n">
-        <v>4.74411630630493</v>
+        <v>4.74411582946777</v>
       </c>
       <c r="H404" t="n">
         <v>211993</v>
@@ -12143,7 +12143,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G406" t="n">
-        <v>4.81763458251953</v>
+        <v>4.81763410568237</v>
       </c>
       <c r="H406" t="n">
         <v>155403</v>
@@ -12172,7 +12172,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>4.84358167648315</v>
+        <v>4.84358215332031</v>
       </c>
       <c r="H407" t="n">
         <v>173795</v>
@@ -12230,7 +12230,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>4.83060789108276</v>
+        <v>4.83060884475708</v>
       </c>
       <c r="H409" t="n">
         <v>259833</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.99926805496216</v>
+        <v>4.99926853179932</v>
       </c>
       <c r="H412" t="n">
         <v>293363</v>
@@ -12375,7 +12375,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>4.8479061126709</v>
+        <v>4.84790658950806</v>
       </c>
       <c r="H414" t="n">
         <v>166900</v>
@@ -12404,7 +12404,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.84358167648315</v>
+        <v>4.84358215332031</v>
       </c>
       <c r="H415" t="n">
         <v>109312</v>
@@ -12462,7 +12462,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>4.99061918258667</v>
+        <v>4.99061870574951</v>
       </c>
       <c r="H417" t="n">
         <v>218175</v>
@@ -12520,7 +12520,7 @@
         <v>5.71500015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>4.94304847717285</v>
+        <v>4.94304895401001</v>
       </c>
       <c r="H419" t="n">
         <v>113305</v>
@@ -12549,7 +12549,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G420" t="n">
-        <v>4.99061918258667</v>
+        <v>4.99061870574951</v>
       </c>
       <c r="H420" t="n">
         <v>97531</v>
@@ -12578,7 +12578,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G421" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H421" t="n">
         <v>117409</v>
@@ -12636,7 +12636,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G423" t="n">
-        <v>4.89547729492188</v>
+        <v>4.89547777175903</v>
       </c>
       <c r="H423" t="n">
         <v>58924</v>
@@ -12665,7 +12665,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86088037490845</v>
+        <v>4.86087989807129</v>
       </c>
       <c r="H424" t="n">
         <v>75493</v>
@@ -12694,7 +12694,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G425" t="n">
-        <v>4.89547729492188</v>
+        <v>4.89547777175903</v>
       </c>
       <c r="H425" t="n">
         <v>162576</v>
@@ -12752,7 +12752,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>5.01224327087402</v>
+        <v>5.01224231719971</v>
       </c>
       <c r="H427" t="n">
         <v>264895</v>
@@ -12781,7 +12781,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G428" t="n">
-        <v>5.02089166641235</v>
+        <v>5.02089214324951</v>
       </c>
       <c r="H428" t="n">
         <v>198478</v>
@@ -12810,7 +12810,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G429" t="n">
-        <v>5.00791835784912</v>
+        <v>5.0079174041748</v>
       </c>
       <c r="H429" t="n">
         <v>116387</v>
@@ -12839,7 +12839,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G430" t="n">
-        <v>5.00359392166138</v>
+        <v>5.00359296798706</v>
       </c>
       <c r="H430" t="n">
         <v>149517</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.01656675338745</v>
+        <v>5.01656723022461</v>
       </c>
       <c r="H432" t="n">
         <v>103229</v>
@@ -12955,7 +12955,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>5.09873533248901</v>
+        <v>5.09873485565186</v>
       </c>
       <c r="H434" t="n">
         <v>469929</v>
@@ -13042,7 +13042,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G437" t="n">
-        <v>5.215500831604</v>
+        <v>5.21549940109253</v>
       </c>
       <c r="H437" t="n">
         <v>223600</v>
@@ -13071,7 +13071,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G438" t="n">
-        <v>5.16360473632812</v>
+        <v>5.16360425949097</v>
       </c>
       <c r="H438" t="n">
         <v>901306</v>
@@ -13187,7 +13187,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>5.13765716552734</v>
+        <v>5.13765668869019</v>
       </c>
       <c r="H442" t="n">
         <v>396834</v>
@@ -13274,7 +13274,7 @@
         <v>5.83500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.04683971405029</v>
+        <v>5.04683923721313</v>
       </c>
       <c r="H445" t="n">
         <v>301985</v>
@@ -13390,7 +13390,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G449" t="n">
-        <v>5.20252513885498</v>
+        <v>5.20252561569214</v>
       </c>
       <c r="H449" t="n">
         <v>307624</v>
@@ -13448,7 +13448,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.15062999725342</v>
+        <v>5.15063047409058</v>
       </c>
       <c r="H451" t="n">
         <v>258487</v>
@@ -13477,7 +13477,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>5.13765716552734</v>
+        <v>5.13765668869019</v>
       </c>
       <c r="H452" t="n">
         <v>150154</v>
@@ -13535,7 +13535,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>5.1073842048645</v>
+        <v>5.10738515853882</v>
       </c>
       <c r="H454" t="n">
         <v>174661</v>
@@ -13564,7 +13564,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>5.12035846710205</v>
+        <v>5.12035799026489</v>
       </c>
       <c r="H455" t="n">
         <v>137091</v>
@@ -13593,7 +13593,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.12468290328979</v>
+        <v>5.12468338012695</v>
       </c>
       <c r="H456" t="n">
         <v>391635</v>
@@ -13622,7 +13622,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G457" t="n">
-        <v>5.14198160171509</v>
+        <v>5.14198112487793</v>
       </c>
       <c r="H457" t="n">
         <v>276363</v>
@@ -13680,7 +13680,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G459" t="n">
-        <v>5.13765716552734</v>
+        <v>5.13765668869019</v>
       </c>
       <c r="H459" t="n">
         <v>199816</v>
@@ -13825,7 +13825,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G464" t="n">
-        <v>5.19387769699097</v>
+        <v>5.19387626647949</v>
       </c>
       <c r="H464" t="n">
         <v>368120</v>
@@ -13854,7 +13854,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G465" t="n">
-        <v>5.19820213317871</v>
+        <v>5.19820165634155</v>
       </c>
       <c r="H465" t="n">
         <v>247241</v>
@@ -13912,7 +13912,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G467" t="n">
-        <v>5.26739549636841</v>
+        <v>5.26739501953125</v>
       </c>
       <c r="H467" t="n">
         <v>280279</v>
@@ -13941,7 +13941,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G468" t="n">
-        <v>5.25009679794312</v>
+        <v>5.25009727478027</v>
       </c>
       <c r="H468" t="n">
         <v>285951</v>
@@ -13970,7 +13970,7 @@
         <v>6.02500009536743</v>
       </c>
       <c r="G469" t="n">
-        <v>5.21117496490479</v>
+        <v>5.21117544174194</v>
       </c>
       <c r="H469" t="n">
         <v>214701</v>
@@ -13999,7 +13999,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>5.27172088623047</v>
+        <v>5.27171945571899</v>
       </c>
       <c r="H470" t="n">
         <v>292493</v>
@@ -14028,7 +14028,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G471" t="n">
-        <v>5.32794046401978</v>
+        <v>5.32793998718262</v>
       </c>
       <c r="H471" t="n">
         <v>238584</v>
@@ -14057,7 +14057,7 @@
         <v>6.125</v>
       </c>
       <c r="G472" t="n">
-        <v>5.29766654968262</v>
+        <v>5.29766750335693</v>
       </c>
       <c r="H472" t="n">
         <v>320585</v>
@@ -14086,7 +14086,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H473" t="n">
         <v>294814</v>
@@ -14173,7 +14173,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>5.25874614715576</v>
+        <v>5.2587456703186</v>
       </c>
       <c r="H476" t="n">
         <v>379252</v>
@@ -14202,7 +14202,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>5.01656675338745</v>
+        <v>5.01656723022461</v>
       </c>
       <c r="H477" t="n">
         <v>522773</v>
@@ -14231,7 +14231,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>4.99061918258667</v>
+        <v>4.99061870574951</v>
       </c>
       <c r="H478" t="n">
         <v>529854</v>
@@ -14289,7 +14289,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.78303813934326</v>
+        <v>4.78303718566895</v>
       </c>
       <c r="H480" t="n">
         <v>389197</v>
@@ -14318,7 +14318,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G481" t="n">
-        <v>4.73979091644287</v>
+        <v>4.73979043960571</v>
       </c>
       <c r="H481" t="n">
         <v>747857</v>
@@ -14347,7 +14347,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>4.90845203399658</v>
+        <v>4.90845108032227</v>
       </c>
       <c r="H482" t="n">
         <v>446975</v>
@@ -14405,7 +14405,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>4.76573944091797</v>
+        <v>4.76573896408081</v>
       </c>
       <c r="H484" t="n">
         <v>287179</v>
@@ -14434,7 +14434,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G485" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H485" t="n">
         <v>263441</v>
@@ -14463,7 +14463,7 @@
         <v>5.7649998664856</v>
       </c>
       <c r="G486" t="n">
-        <v>4.98629474639893</v>
+        <v>4.98629426956177</v>
       </c>
       <c r="H486" t="n">
         <v>333879</v>
@@ -14492,7 +14492,7 @@
         <v>5.72499990463257</v>
       </c>
       <c r="G487" t="n">
-        <v>4.9516978263855</v>
+        <v>4.95169734954834</v>
       </c>
       <c r="H487" t="n">
         <v>252838</v>
@@ -14521,7 +14521,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>5.00359392166138</v>
+        <v>5.00359296798706</v>
       </c>
       <c r="H488" t="n">
         <v>143604</v>
@@ -14550,7 +14550,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G489" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H489" t="n">
         <v>185613</v>
@@ -14579,7 +14579,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G490" t="n">
-        <v>4.96467161178589</v>
+        <v>4.96467065811157</v>
       </c>
       <c r="H490" t="n">
         <v>159744</v>
@@ -14637,7 +14637,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G492" t="n">
-        <v>4.9300742149353</v>
+        <v>4.93007373809814</v>
       </c>
       <c r="H492" t="n">
         <v>270903</v>
@@ -14666,7 +14666,7 @@
         <v>5.625</v>
       </c>
       <c r="G493" t="n">
-        <v>4.86520385742188</v>
+        <v>4.86520433425903</v>
       </c>
       <c r="H493" t="n">
         <v>154327</v>
@@ -14695,7 +14695,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>4.86088037490845</v>
+        <v>4.86087989807129</v>
       </c>
       <c r="H494" t="n">
         <v>196034</v>
@@ -14724,7 +14724,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.90845203399658</v>
+        <v>4.90845108032227</v>
       </c>
       <c r="H495" t="n">
         <v>317223</v>
@@ -14753,7 +14753,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G496" t="n">
-        <v>4.873854637146</v>
+        <v>4.87385511398315</v>
       </c>
       <c r="H496" t="n">
         <v>203739</v>
@@ -14782,7 +14782,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G497" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H497" t="n">
         <v>100297</v>
@@ -14811,7 +14811,7 @@
         <v>5.625</v>
       </c>
       <c r="G498" t="n">
-        <v>4.86520385742188</v>
+        <v>4.86520433425903</v>
       </c>
       <c r="H498" t="n">
         <v>144169</v>
@@ -14840,7 +14840,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G499" t="n">
-        <v>4.92575025558472</v>
+        <v>4.92574977874756</v>
       </c>
       <c r="H499" t="n">
         <v>214562</v>
@@ -14898,7 +14898,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83060789108276</v>
+        <v>4.83060884475708</v>
       </c>
       <c r="H501" t="n">
         <v>212118</v>
@@ -14927,7 +14927,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>4.82628297805786</v>
+        <v>4.82628345489502</v>
       </c>
       <c r="H502" t="n">
         <v>188491</v>
@@ -14956,7 +14956,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.89980220794678</v>
+        <v>4.89980268478394</v>
       </c>
       <c r="H503" t="n">
         <v>344279</v>
@@ -14985,7 +14985,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G504" t="n">
-        <v>4.9300742149353</v>
+        <v>4.93007373809814</v>
       </c>
       <c r="H504" t="n">
         <v>198960</v>
@@ -15014,7 +15014,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.83060789108276</v>
+        <v>4.83060884475708</v>
       </c>
       <c r="H505" t="n">
         <v>188563</v>
@@ -15043,7 +15043,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G506" t="n">
-        <v>4.86088037490845</v>
+        <v>4.86087989807129</v>
       </c>
       <c r="H506" t="n">
         <v>155510</v>
@@ -15072,7 +15072,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.90845203399658</v>
+        <v>4.90845108032227</v>
       </c>
       <c r="H507" t="n">
         <v>101198</v>
@@ -15101,7 +15101,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G508" t="n">
-        <v>4.84358167648315</v>
+        <v>4.84358215332031</v>
       </c>
       <c r="H508" t="n">
         <v>115157</v>
@@ -15159,7 +15159,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>4.82628297805786</v>
+        <v>4.82628345489502</v>
       </c>
       <c r="H510" t="n">
         <v>133582</v>
@@ -15188,7 +15188,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G511" t="n">
-        <v>4.80466032028198</v>
+        <v>4.80466079711914</v>
       </c>
       <c r="H511" t="n">
         <v>148244</v>
@@ -15217,7 +15217,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>4.80898475646973</v>
+        <v>4.80898380279541</v>
       </c>
       <c r="H512" t="n">
         <v>181953</v>
@@ -15304,7 +15304,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.96467161178589</v>
+        <v>4.96467065811157</v>
       </c>
       <c r="H515" t="n">
         <v>264465</v>
@@ -15362,7 +15362,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G517" t="n">
-        <v>5.25009679794312</v>
+        <v>5.25009727478027</v>
       </c>
       <c r="H517" t="n">
         <v>434448</v>
@@ -15478,7 +15478,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>5.30199241638184</v>
+        <v>5.30199289321899</v>
       </c>
       <c r="H521" t="n">
         <v>435702</v>
@@ -15536,7 +15536,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G523" t="n">
-        <v>5.215500831604</v>
+        <v>5.21549940109253</v>
       </c>
       <c r="H523" t="n">
         <v>273338</v>
@@ -15565,7 +15565,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G524" t="n">
-        <v>5.25009679794312</v>
+        <v>5.25009727478027</v>
       </c>
       <c r="H524" t="n">
         <v>185841</v>
@@ -15594,7 +15594,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G525" t="n">
-        <v>5.33658885955811</v>
+        <v>5.33658933639526</v>
       </c>
       <c r="H525" t="n">
         <v>479599</v>
@@ -15652,7 +15652,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G527" t="n">
-        <v>5.44902944564819</v>
+        <v>5.44902992248535</v>
       </c>
       <c r="H527" t="n">
         <v>507337</v>
@@ -15681,7 +15681,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H528" t="n">
         <v>230837</v>
@@ -15710,7 +15710,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H529" t="n">
         <v>218110</v>
@@ -15739,7 +15739,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>5.44038057327271</v>
+        <v>5.44037961959839</v>
       </c>
       <c r="H530" t="n">
         <v>126571</v>
@@ -15797,7 +15797,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H532" t="n">
         <v>486411</v>
@@ -15826,7 +15826,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G533" t="n">
-        <v>5.32794046401978</v>
+        <v>5.32793998718262</v>
       </c>
       <c r="H533" t="n">
         <v>206920</v>
@@ -15942,7 +15942,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>5.00791835784912</v>
+        <v>5.0079174041748</v>
       </c>
       <c r="H537" t="n">
         <v>604507</v>
@@ -16000,7 +16000,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G539" t="n">
-        <v>5.01656675338745</v>
+        <v>5.01656723022461</v>
       </c>
       <c r="H539" t="n">
         <v>361915</v>
@@ -16029,7 +16029,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G540" t="n">
-        <v>4.91277551651001</v>
+        <v>4.91277599334717</v>
       </c>
       <c r="H540" t="n">
         <v>331497</v>
@@ -16087,7 +16087,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G542" t="n">
-        <v>4.99926805496216</v>
+        <v>4.99926853179932</v>
       </c>
       <c r="H542" t="n">
         <v>469641</v>
@@ -16145,7 +16145,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>5.16360473632812</v>
+        <v>5.16360425949097</v>
       </c>
       <c r="H544" t="n">
         <v>297803</v>
@@ -16174,7 +16174,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G545" t="n">
-        <v>5.215500831604</v>
+        <v>5.21549940109253</v>
       </c>
       <c r="H545" t="n">
         <v>194987</v>
@@ -16261,7 +16261,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G548" t="n">
-        <v>5.13765716552734</v>
+        <v>5.13765668869019</v>
       </c>
       <c r="H548" t="n">
         <v>161745</v>
@@ -16319,7 +16319,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G550" t="n">
-        <v>5.01656675338745</v>
+        <v>5.01656723022461</v>
       </c>
       <c r="H550" t="n">
         <v>208904</v>
@@ -16348,7 +16348,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G551" t="n">
-        <v>5.06846332550049</v>
+        <v>5.06846284866333</v>
       </c>
       <c r="H551" t="n">
         <v>207351</v>
@@ -16435,7 +16435,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G554" t="n">
-        <v>4.9300742149353</v>
+        <v>4.93007373809814</v>
       </c>
       <c r="H554" t="n">
         <v>252907</v>
@@ -16464,7 +16464,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G555" t="n">
-        <v>4.8781795501709</v>
+        <v>4.87817907333374</v>
       </c>
       <c r="H555" t="n">
         <v>460820</v>
@@ -16551,7 +16551,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>5.04251527786255</v>
+        <v>5.04251432418823</v>
       </c>
       <c r="H558" t="n">
         <v>231109</v>
@@ -16609,7 +16609,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G560" t="n">
-        <v>5.16360473632812</v>
+        <v>5.16360425949097</v>
       </c>
       <c r="H560" t="n">
         <v>189270</v>
@@ -16638,7 +16638,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>5.29334354400635</v>
+        <v>5.29334306716919</v>
       </c>
       <c r="H561" t="n">
         <v>400906</v>
@@ -16696,7 +16696,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>5.30199241638184</v>
+        <v>5.30199289321899</v>
       </c>
       <c r="H563" t="n">
         <v>280196</v>
@@ -16725,7 +16725,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H564" t="n">
         <v>256807</v>
@@ -16754,7 +16754,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G565" t="n">
-        <v>5.34523773193359</v>
+        <v>5.34523868560791</v>
       </c>
       <c r="H565" t="n">
         <v>193583</v>
@@ -16783,7 +16783,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.23279905319214</v>
+        <v>5.23279857635498</v>
       </c>
       <c r="H566" t="n">
         <v>294812</v>
@@ -16812,7 +16812,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G567" t="n">
-        <v>5.33658885955811</v>
+        <v>5.33658933639526</v>
       </c>
       <c r="H567" t="n">
         <v>264739</v>
@@ -16928,7 +16928,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G571" t="n">
-        <v>5.16360473632812</v>
+        <v>5.16360425949097</v>
       </c>
       <c r="H571" t="n">
         <v>189194</v>
@@ -17015,7 +17015,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>5.29334354400635</v>
+        <v>5.29334306716919</v>
       </c>
       <c r="H574" t="n">
         <v>254433</v>
@@ -17044,7 +17044,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>5.27604532241821</v>
+        <v>5.27604484558105</v>
       </c>
       <c r="H575" t="n">
         <v>188121</v>
@@ -17102,7 +17102,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>5.26739549636841</v>
+        <v>5.26739501953125</v>
       </c>
       <c r="H577" t="n">
         <v>184600</v>
@@ -17131,7 +17131,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G578" t="n">
-        <v>5.27604532241821</v>
+        <v>5.27604484558105</v>
       </c>
       <c r="H578" t="n">
         <v>147386</v>
@@ -17160,7 +17160,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G579" t="n">
-        <v>5.32794046401978</v>
+        <v>5.32793998718262</v>
       </c>
       <c r="H579" t="n">
         <v>157062</v>
@@ -17189,7 +17189,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H580" t="n">
         <v>241429</v>
@@ -17218,7 +17218,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G581" t="n">
-        <v>5.29334354400635</v>
+        <v>5.29334306716919</v>
       </c>
       <c r="H581" t="n">
         <v>116988</v>
@@ -17247,7 +17247,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G582" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H582" t="n">
         <v>152528</v>
@@ -17276,7 +17276,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G583" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H583" t="n">
         <v>134082</v>
@@ -17305,7 +17305,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.31929063796997</v>
+        <v>5.31929016113281</v>
       </c>
       <c r="H584" t="n">
         <v>211164</v>
@@ -17334,7 +17334,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G585" t="n">
-        <v>5.3884859085083</v>
+        <v>5.38848495483398</v>
       </c>
       <c r="H585" t="n">
         <v>150381</v>
@@ -17392,7 +17392,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G587" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H587" t="n">
         <v>102963</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.27604532241821</v>
+        <v>5.27604484558105</v>
       </c>
       <c r="H588" t="n">
         <v>205665</v>
@@ -17450,7 +17450,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>5.26739549636841</v>
+        <v>5.26739501953125</v>
       </c>
       <c r="H589" t="n">
         <v>171564</v>
@@ -17479,7 +17479,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>5.26739549636841</v>
+        <v>5.26739501953125</v>
       </c>
       <c r="H590" t="n">
         <v>107170</v>
@@ -17508,7 +17508,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G591" t="n">
-        <v>5.25009679794312</v>
+        <v>5.25009727478027</v>
       </c>
       <c r="H591" t="n">
         <v>82268</v>
@@ -17537,7 +17537,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G592" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H592" t="n">
         <v>51217</v>
@@ -17566,7 +17566,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G593" t="n">
-        <v>5.32794046401978</v>
+        <v>5.32793998718262</v>
       </c>
       <c r="H593" t="n">
         <v>145565</v>
@@ -17595,7 +17595,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G594" t="n">
-        <v>5.31064176559448</v>
+        <v>5.31064081192017</v>
       </c>
       <c r="H594" t="n">
         <v>81075</v>
@@ -17624,7 +17624,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G595" t="n">
-        <v>5.31929063796997</v>
+        <v>5.31929016113281</v>
       </c>
       <c r="H595" t="n">
         <v>348016</v>
@@ -17653,7 +17653,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G596" t="n">
-        <v>5.33658885955811</v>
+        <v>5.33658933639526</v>
       </c>
       <c r="H596" t="n">
         <v>202717</v>
@@ -17682,7 +17682,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>5.37118625640869</v>
+        <v>5.37118577957153</v>
       </c>
       <c r="H597" t="n">
         <v>334253</v>
@@ -17740,7 +17740,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>5.39713430404663</v>
+        <v>5.39713335037231</v>
       </c>
       <c r="H599" t="n">
         <v>258483</v>
@@ -17769,7 +17769,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G600" t="n">
-        <v>5.39713430404663</v>
+        <v>5.39713335037231</v>
       </c>
       <c r="H600" t="n">
         <v>304811</v>
@@ -17885,7 +17885,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G604" t="n">
-        <v>5.46632862091064</v>
+        <v>5.46632814407349</v>
       </c>
       <c r="H604" t="n">
         <v>504646</v>
@@ -17914,7 +17914,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>5.25874614715576</v>
+        <v>5.2587456703186</v>
       </c>
       <c r="H605" t="n">
         <v>357370</v>
@@ -17943,7 +17943,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>5.30199241638184</v>
+        <v>5.30199289321899</v>
       </c>
       <c r="H606" t="n">
         <v>280448</v>
@@ -18001,7 +18001,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G608" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H608" t="n">
         <v>230665</v>
@@ -18117,7 +18117,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G612" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H612" t="n">
         <v>205497</v>
@@ -18146,7 +18146,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.0664381980896</v>
+        <v>5.06643772125244</v>
       </c>
       <c r="H613" t="n">
         <v>402155</v>
@@ -18204,7 +18204,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G615" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H615" t="n">
         <v>358974</v>
@@ -18262,7 +18262,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G617" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H617" t="n">
         <v>326565</v>
@@ -18291,7 +18291,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G618" t="n">
-        <v>5.26769495010376</v>
+        <v>5.26769542694092</v>
       </c>
       <c r="H618" t="n">
         <v>200156</v>
@@ -18320,7 +18320,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G619" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H619" t="n">
         <v>614934</v>
@@ -18349,7 +18349,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.20644283294678</v>
+        <v>5.20644235610962</v>
       </c>
       <c r="H620" t="n">
         <v>291258</v>
@@ -18378,7 +18378,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H621" t="n">
         <v>298828</v>
@@ -18407,7 +18407,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G622" t="n">
-        <v>5.23269319534302</v>
+        <v>5.23269367218018</v>
       </c>
       <c r="H622" t="n">
         <v>164085</v>
@@ -18465,7 +18465,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>5.28519630432129</v>
+        <v>5.28519582748413</v>
       </c>
       <c r="H624" t="n">
         <v>262813</v>
@@ -18552,7 +18552,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>5.23269319534302</v>
+        <v>5.23269367218018</v>
       </c>
       <c r="H627" t="n">
         <v>331367</v>
@@ -18581,7 +18581,7 @@
         <v>6</v>
       </c>
       <c r="G628" t="n">
-        <v>5.25019454956055</v>
+        <v>5.25019407272339</v>
       </c>
       <c r="H628" t="n">
         <v>185539</v>
@@ -18610,7 +18610,7 @@
         <v>6</v>
       </c>
       <c r="G629" t="n">
-        <v>5.25019454956055</v>
+        <v>5.25019407272339</v>
       </c>
       <c r="H629" t="n">
         <v>180565</v>
@@ -18639,7 +18639,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G630" t="n">
-        <v>5.23269319534302</v>
+        <v>5.23269367218018</v>
       </c>
       <c r="H630" t="n">
         <v>144357</v>
@@ -18668,7 +18668,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H631" t="n">
         <v>214958</v>
@@ -18842,7 +18842,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>5.16269159317017</v>
+        <v>5.16269111633301</v>
       </c>
       <c r="H637" t="n">
         <v>168128</v>
@@ -18871,7 +18871,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H638" t="n">
         <v>279839</v>
@@ -18929,7 +18929,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G640" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H640" t="n">
         <v>165373</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.23269319534302</v>
+        <v>5.23269367218018</v>
       </c>
       <c r="H642" t="n">
         <v>219655</v>
@@ -19016,7 +19016,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>5.21519231796265</v>
+        <v>5.2151927947998</v>
       </c>
       <c r="H643" t="n">
         <v>143137</v>
@@ -19045,7 +19045,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G644" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H644" t="n">
         <v>127458</v>
@@ -19074,7 +19074,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G645" t="n">
-        <v>5.19769287109375</v>
+        <v>5.19769239425659</v>
       </c>
       <c r="H645" t="n">
         <v>131588</v>
@@ -19103,7 +19103,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H646" t="n">
         <v>151180</v>
@@ -19161,7 +19161,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>5.19769287109375</v>
+        <v>5.19769239425659</v>
       </c>
       <c r="H648" t="n">
         <v>135977</v>
@@ -19190,7 +19190,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21519231796265</v>
+        <v>5.2151927947998</v>
       </c>
       <c r="H649" t="n">
         <v>94966</v>
@@ -19219,7 +19219,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G650" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H650" t="n">
         <v>176317</v>
@@ -19277,7 +19277,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G652" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H652" t="n">
         <v>218820</v>
@@ -19306,7 +19306,7 @@
         <v>6</v>
       </c>
       <c r="G653" t="n">
-        <v>5.25019454956055</v>
+        <v>5.25019407272339</v>
       </c>
       <c r="H653" t="n">
         <v>89512</v>
@@ -19335,7 +19335,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G654" t="n">
-        <v>5.19769287109375</v>
+        <v>5.19769239425659</v>
       </c>
       <c r="H654" t="n">
         <v>91491</v>
@@ -19364,7 +19364,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H655" t="n">
         <v>100368</v>
@@ -19393,7 +19393,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G656" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H656" t="n">
         <v>104934</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.25019454956055</v>
+        <v>5.25019407272339</v>
       </c>
       <c r="H658" t="n">
         <v>61841</v>
@@ -19480,7 +19480,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G659" t="n">
-        <v>5.51270484924316</v>
+        <v>5.51270437240601</v>
       </c>
       <c r="H659" t="n">
         <v>790916</v>
@@ -19509,7 +19509,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G660" t="n">
-        <v>5.48645257949829</v>
+        <v>5.48645305633545</v>
       </c>
       <c r="H660" t="n">
         <v>256033</v>
@@ -19567,7 +19567,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G662" t="n">
-        <v>5.47770309448242</v>
+        <v>5.47770261764526</v>
       </c>
       <c r="H662" t="n">
         <v>127936</v>
@@ -19625,7 +19625,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G664" t="n">
-        <v>5.43395137786865</v>
+        <v>5.43395090103149</v>
       </c>
       <c r="H664" t="n">
         <v>130416</v>
@@ -19654,7 +19654,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G665" t="n">
-        <v>5.52145385742188</v>
+        <v>5.52145433425903</v>
       </c>
       <c r="H665" t="n">
         <v>177146</v>
@@ -19683,7 +19683,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>5.61770820617676</v>
+        <v>5.61770868301392</v>
       </c>
       <c r="H666" t="n">
         <v>248959</v>
@@ -19712,7 +19712,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G667" t="n">
-        <v>5.46020221710205</v>
+        <v>5.46020174026489</v>
       </c>
       <c r="H667" t="n">
         <v>192887</v>
@@ -19741,7 +19741,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G668" t="n">
-        <v>5.51270484924316</v>
+        <v>5.51270437240601</v>
       </c>
       <c r="H668" t="n">
         <v>229456</v>
@@ -19770,7 +19770,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G669" t="n">
-        <v>5.46020221710205</v>
+        <v>5.46020174026489</v>
       </c>
       <c r="H669" t="n">
         <v>261552</v>
@@ -19799,7 +19799,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G670" t="n">
-        <v>5.47770309448242</v>
+        <v>5.47770261764526</v>
       </c>
       <c r="H670" t="n">
         <v>281439</v>
@@ -19828,7 +19828,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G671" t="n">
-        <v>5.45145225524902</v>
+        <v>5.45145177841187</v>
       </c>
       <c r="H671" t="n">
         <v>182006</v>
@@ -19857,7 +19857,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>5.5389552116394</v>
+        <v>5.53895473480225</v>
       </c>
       <c r="H672" t="n">
         <v>160142</v>
@@ -19886,7 +19886,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>5.69646120071411</v>
+        <v>5.69646167755127</v>
       </c>
       <c r="H673" t="n">
         <v>242459</v>
@@ -19915,7 +19915,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G674" t="n">
-        <v>5.69646120071411</v>
+        <v>5.69646167755127</v>
       </c>
       <c r="H674" t="n">
         <v>212783</v>
@@ -19944,7 +19944,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G675" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H675" t="n">
         <v>279194</v>
@@ -19973,7 +19973,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G676" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H676" t="n">
         <v>75671</v>
@@ -20002,7 +20002,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G677" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H677" t="n">
         <v>313127</v>
@@ -20031,7 +20031,7 @@
         <v>6.5</v>
       </c>
       <c r="G678" t="n">
-        <v>5.68771028518677</v>
+        <v>5.68770980834961</v>
       </c>
       <c r="H678" t="n">
         <v>316052</v>
@@ -20089,7 +20089,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G680" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H680" t="n">
         <v>278128</v>
@@ -20147,7 +20147,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H682" t="n">
         <v>231167</v>
@@ -20205,7 +20205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H684" t="n">
         <v>191204</v>
@@ -20263,7 +20263,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>5.76646375656128</v>
+        <v>5.76646327972412</v>
       </c>
       <c r="H686" t="n">
         <v>234212</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>5.81021451950073</v>
+        <v>5.81021499633789</v>
       </c>
       <c r="H688" t="n">
         <v>263462</v>
@@ -20379,7 +20379,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>5.67020988464355</v>
+        <v>5.6702094078064</v>
       </c>
       <c r="H690" t="n">
         <v>186414</v>
@@ -20437,7 +20437,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>5.58270597457886</v>
+        <v>5.58270645141602</v>
       </c>
       <c r="H692" t="n">
         <v>205826</v>
@@ -20466,7 +20466,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>5.61770820617676</v>
+        <v>5.61770868301392</v>
       </c>
       <c r="H693" t="n">
         <v>234680</v>
@@ -20524,7 +20524,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G695" t="n">
-        <v>5.67895936965942</v>
+        <v>5.67896032333374</v>
       </c>
       <c r="H695" t="n">
         <v>173243</v>
@@ -20553,7 +20553,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G696" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H696" t="n">
         <v>2775017</v>
@@ -20582,7 +20582,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>5.75771331787109</v>
+        <v>5.75771236419678</v>
       </c>
       <c r="H697" t="n">
         <v>205507</v>
@@ -20611,7 +20611,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>5.8539662361145</v>
+        <v>5.85396671295166</v>
       </c>
       <c r="H698" t="n">
         <v>313492</v>
@@ -20640,7 +20640,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>5.74896287918091</v>
+        <v>5.74896335601807</v>
       </c>
       <c r="H699" t="n">
         <v>187174</v>
@@ -20669,7 +20669,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G700" t="n">
-        <v>5.75771331787109</v>
+        <v>5.75771236419678</v>
       </c>
       <c r="H700" t="n">
         <v>430939</v>
@@ -20698,7 +20698,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G701" t="n">
-        <v>5.67895936965942</v>
+        <v>5.67896032333374</v>
       </c>
       <c r="H701" t="n">
         <v>335638</v>
@@ -20727,7 +20727,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G702" t="n">
-        <v>5.71396207809448</v>
+        <v>5.71396112442017</v>
       </c>
       <c r="H702" t="n">
         <v>183347</v>
@@ -20785,7 +20785,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G704" t="n">
-        <v>5.67020988464355</v>
+        <v>5.6702094078064</v>
       </c>
       <c r="H704" t="n">
         <v>255665</v>
@@ -20843,7 +20843,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>5.54770612716675</v>
+        <v>5.54770517349243</v>
       </c>
       <c r="H706" t="n">
         <v>277755</v>
@@ -20901,7 +20901,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>5.35519886016846</v>
+        <v>5.3551983833313</v>
       </c>
       <c r="H708" t="n">
         <v>495999</v>
@@ -20930,7 +20930,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H709" t="n">
         <v>680613</v>
@@ -20959,7 +20959,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G710" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H710" t="n">
         <v>545215</v>
@@ -21046,7 +21046,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>5.26769495010376</v>
+        <v>5.26769542694092</v>
       </c>
       <c r="H713" t="n">
         <v>439088</v>
@@ -21075,7 +21075,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>5.1189398765564</v>
+        <v>5.11893939971924</v>
       </c>
       <c r="H714" t="n">
         <v>473307</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H715" t="n">
         <v>271362</v>
@@ -21133,7 +21133,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G716" t="n">
-        <v>5.02268648147583</v>
+        <v>5.02268552780151</v>
       </c>
       <c r="H716" t="n">
         <v>419537</v>
@@ -21162,7 +21162,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G717" t="n">
-        <v>4.9789342880249</v>
+        <v>4.97893476486206</v>
       </c>
       <c r="H717" t="n">
         <v>331986</v>
@@ -21220,7 +21220,7 @@
         <v>5.5</v>
       </c>
       <c r="G719" t="n">
-        <v>4.81267881393433</v>
+        <v>4.81267786026001</v>
       </c>
       <c r="H719" t="n">
         <v>253977</v>
@@ -21307,7 +21307,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G722" t="n">
-        <v>5.10143899917603</v>
+        <v>5.10143852233887</v>
       </c>
       <c r="H722" t="n">
         <v>343683</v>
@@ -21336,7 +21336,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G723" t="n">
-        <v>5.02268648147583</v>
+        <v>5.02268552780151</v>
       </c>
       <c r="H723" t="n">
         <v>240552</v>
@@ -21423,7 +21423,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G726" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H726" t="n">
         <v>142072</v>
@@ -21452,7 +21452,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G727" t="n">
-        <v>5.02268648147583</v>
+        <v>5.02268552780151</v>
       </c>
       <c r="H727" t="n">
         <v>92500</v>
@@ -21481,7 +21481,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G728" t="n">
-        <v>5.02268648147583</v>
+        <v>5.02268552780151</v>
       </c>
       <c r="H728" t="n">
         <v>138074</v>
@@ -21510,7 +21510,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>5.16269159317017</v>
+        <v>5.16269111633301</v>
       </c>
       <c r="H729" t="n">
         <v>181705</v>
@@ -21539,7 +21539,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H730" t="n">
         <v>132511</v>
@@ -21568,7 +21568,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>5.16269159317017</v>
+        <v>5.16269111633301</v>
       </c>
       <c r="H731" t="n">
         <v>85335</v>
@@ -21597,7 +21597,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G732" t="n">
-        <v>5.092689037323</v>
+        <v>5.09268856048584</v>
       </c>
       <c r="H732" t="n">
         <v>113427</v>
@@ -21626,7 +21626,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>5.1189398765564</v>
+        <v>5.11893939971924</v>
       </c>
       <c r="H733" t="n">
         <v>102651</v>
@@ -21655,7 +21655,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.98768472671509</v>
+        <v>4.98768424987793</v>
       </c>
       <c r="H734" t="n">
         <v>159529</v>
@@ -21684,7 +21684,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G735" t="n">
-        <v>4.92643308639526</v>
+        <v>4.92643260955811</v>
       </c>
       <c r="H735" t="n">
         <v>390248</v>
@@ -21829,7 +21829,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G740" t="n">
-        <v>4.64642190933228</v>
+        <v>4.64642238616943</v>
       </c>
       <c r="H740" t="n">
         <v>156355</v>
@@ -21916,7 +21916,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G743" t="n">
-        <v>4.92643308639526</v>
+        <v>4.92643260955811</v>
       </c>
       <c r="H743" t="n">
         <v>195640</v>
@@ -21945,7 +21945,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G744" t="n">
-        <v>4.91768217086792</v>
+        <v>4.91768169403076</v>
       </c>
       <c r="H744" t="n">
         <v>174485</v>
@@ -21974,7 +21974,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G745" t="n">
-        <v>4.94393253326416</v>
+        <v>4.94393301010132</v>
       </c>
       <c r="H745" t="n">
         <v>256010</v>
@@ -22003,7 +22003,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G746" t="n">
-        <v>4.9789342880249</v>
+        <v>4.97893476486206</v>
       </c>
       <c r="H746" t="n">
         <v>281346</v>
@@ -22032,7 +22032,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>5.10143899917603</v>
+        <v>5.10143852233887</v>
       </c>
       <c r="H747" t="n">
         <v>131515</v>
@@ -22090,7 +22090,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G749" t="n">
-        <v>4.9789342880249</v>
+        <v>4.97893476486206</v>
       </c>
       <c r="H749" t="n">
         <v>116022</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>4.98768472671509</v>
+        <v>4.98768424987793</v>
       </c>
       <c r="H754" t="n">
         <v>289680</v>
@@ -22264,7 +22264,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G755" t="n">
-        <v>4.9789342880249</v>
+        <v>4.97893476486206</v>
       </c>
       <c r="H755" t="n">
         <v>245616</v>
@@ -22293,7 +22293,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G756" t="n">
-        <v>4.95268297195435</v>
+        <v>4.9526834487915</v>
       </c>
       <c r="H756" t="n">
         <v>280564</v>
@@ -22322,7 +22322,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G757" t="n">
-        <v>4.90893268585205</v>
+        <v>4.90893220901489</v>
       </c>
       <c r="H757" t="n">
         <v>361957</v>
@@ -22351,7 +22351,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G758" t="n">
-        <v>4.93518304824829</v>
+        <v>4.93518257141113</v>
       </c>
       <c r="H758" t="n">
         <v>290789</v>
@@ -22496,7 +22496,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G763" t="n">
-        <v>5.02268648147583</v>
+        <v>5.02268552780151</v>
       </c>
       <c r="H763" t="n">
         <v>424777</v>
@@ -22525,7 +22525,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>5.1189398765564</v>
+        <v>5.11893939971924</v>
       </c>
       <c r="H764" t="n">
         <v>159130</v>
@@ -22554,7 +22554,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G765" t="n">
-        <v>5.0576868057251</v>
+        <v>5.05768728256226</v>
       </c>
       <c r="H765" t="n">
         <v>241488</v>
@@ -22583,7 +22583,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>5.20644283294678</v>
+        <v>5.20644235610962</v>
       </c>
       <c r="H766" t="n">
         <v>334776</v>
@@ -22612,7 +22612,7 @@
         <v>6</v>
       </c>
       <c r="G767" t="n">
-        <v>5.25019454956055</v>
+        <v>5.25019407272339</v>
       </c>
       <c r="H767" t="n">
         <v>163227</v>
@@ -22670,7 +22670,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G769" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H769" t="n">
         <v>252566</v>
@@ -22728,7 +22728,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>5.21519231796265</v>
+        <v>5.2151927947998</v>
       </c>
       <c r="H771" t="n">
         <v>101123</v>
@@ -22757,7 +22757,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H772" t="n">
         <v>87614</v>
@@ -22786,7 +22786,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G773" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H773" t="n">
         <v>150849</v>
@@ -22873,7 +22873,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>5.38144969940186</v>
+        <v>5.38144874572754</v>
       </c>
       <c r="H776" t="n">
         <v>157400</v>
@@ -22902,7 +22902,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>5.38144969940186</v>
+        <v>5.38144874572754</v>
       </c>
       <c r="H777" t="n">
         <v>161166</v>
@@ -22931,7 +22931,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G778" t="n">
-        <v>5.35519886016846</v>
+        <v>5.3551983833313</v>
       </c>
       <c r="H778" t="n">
         <v>230954</v>
@@ -22989,7 +22989,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G780" t="n">
-        <v>5.39019966125488</v>
+        <v>5.39019918441772</v>
       </c>
       <c r="H780" t="n">
         <v>181250</v>
@@ -23018,7 +23018,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G781" t="n">
-        <v>5.39019966125488</v>
+        <v>5.39019918441772</v>
       </c>
       <c r="H781" t="n">
         <v>152835</v>
@@ -23047,7 +23047,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>5.35519886016846</v>
+        <v>5.3551983833313</v>
       </c>
       <c r="H782" t="n">
         <v>247195</v>
@@ -23105,7 +23105,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>5.37269926071167</v>
+        <v>5.37269830703735</v>
       </c>
       <c r="H784" t="n">
         <v>132978</v>
@@ -23279,7 +23279,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.18019247055054</v>
+        <v>5.18019199371338</v>
       </c>
       <c r="H790" t="n">
         <v>271681</v>
@@ -23453,7 +23453,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>5.28519630432129</v>
+        <v>5.28519582748413</v>
       </c>
       <c r="H796" t="n">
         <v>134267</v>
@@ -23482,7 +23482,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G797" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H797" t="n">
         <v>82806</v>
@@ -23511,7 +23511,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G798" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H798" t="n">
         <v>96339</v>
@@ -23569,7 +23569,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G800" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H800" t="n">
         <v>157920</v>
@@ -23598,7 +23598,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>5.26769495010376</v>
+        <v>5.26769542694092</v>
       </c>
       <c r="H801" t="n">
         <v>167256</v>
@@ -23627,7 +23627,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H802" t="n">
         <v>102270</v>
@@ -23685,7 +23685,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G804" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H804" t="n">
         <v>110679</v>
@@ -23714,7 +23714,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G805" t="n">
-        <v>5.35519886016846</v>
+        <v>5.3551983833313</v>
       </c>
       <c r="H805" t="n">
         <v>129238</v>
@@ -23743,7 +23743,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G806" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H806" t="n">
         <v>162640</v>
@@ -23772,7 +23772,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>5.26769495010376</v>
+        <v>5.26769542694092</v>
       </c>
       <c r="H807" t="n">
         <v>191414</v>
@@ -23801,7 +23801,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G808" t="n">
-        <v>5.31144618988037</v>
+        <v>5.31144714355469</v>
       </c>
       <c r="H808" t="n">
         <v>93232</v>
@@ -23859,7 +23859,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G810" t="n">
-        <v>5.27644634246826</v>
+        <v>5.27644491195679</v>
       </c>
       <c r="H810" t="n">
         <v>141183</v>
@@ -23888,7 +23888,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>5.28519630432129</v>
+        <v>5.28519582748413</v>
       </c>
       <c r="H811" t="n">
         <v>152213</v>
@@ -23917,7 +23917,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G812" t="n">
-        <v>5.34644842147827</v>
+        <v>5.34644794464111</v>
       </c>
       <c r="H812" t="n">
         <v>131774</v>
@@ -24004,7 +24004,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>5.43395137786865</v>
+        <v>5.43395090103149</v>
       </c>
       <c r="H815" t="n">
         <v>301955</v>
@@ -24033,7 +24033,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G816" t="n">
-        <v>5.50395345687866</v>
+        <v>5.5039529800415</v>
       </c>
       <c r="H816" t="n">
         <v>554791</v>
@@ -24062,7 +24062,7 @@
         <v>6.25</v>
       </c>
       <c r="G817" t="n">
-        <v>5.46895313262939</v>
+        <v>5.46895217895508</v>
       </c>
       <c r="H817" t="n">
         <v>218380</v>
@@ -24091,7 +24091,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G818" t="n">
-        <v>5.46020221710205</v>
+        <v>5.46020174026489</v>
       </c>
       <c r="H818" t="n">
         <v>166405</v>
@@ -24149,7 +24149,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>5.45145225524902</v>
+        <v>5.45145177841187</v>
       </c>
       <c r="H820" t="n">
         <v>215545</v>
@@ -24178,7 +24178,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>5.39894962310791</v>
+        <v>5.39895009994507</v>
       </c>
       <c r="H821" t="n">
         <v>194054</v>
@@ -24207,7 +24207,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G822" t="n">
-        <v>5.40769910812378</v>
+        <v>5.40769958496094</v>
       </c>
       <c r="H822" t="n">
         <v>181452</v>
@@ -24236,7 +24236,7 @@
         <v>6.25</v>
       </c>
       <c r="G823" t="n">
-        <v>5.46895313262939</v>
+        <v>5.46895217895508</v>
       </c>
       <c r="H823" t="n">
         <v>103867</v>
@@ -24294,7 +24294,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>5.49520349502563</v>
+        <v>5.49520301818848</v>
       </c>
       <c r="H825" t="n">
         <v>173711</v>
@@ -24323,7 +24323,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G826" t="n">
-        <v>5.46020221710205</v>
+        <v>5.46020174026489</v>
       </c>
       <c r="H826" t="n">
         <v>166056</v>
@@ -24352,7 +24352,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>5.47770309448242</v>
+        <v>5.47770261764526</v>
       </c>
       <c r="H827" t="n">
         <v>126185</v>
@@ -24381,7 +24381,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>5.50395345687866</v>
+        <v>5.5039529800415</v>
       </c>
       <c r="H828" t="n">
         <v>138747</v>
@@ -24410,7 +24410,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G829" t="n">
-        <v>5.55645561218262</v>
+        <v>5.55645513534546</v>
       </c>
       <c r="H829" t="n">
         <v>457058</v>
@@ -24468,7 +24468,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>5.60895824432373</v>
+        <v>5.60895776748657</v>
       </c>
       <c r="H831" t="n">
         <v>162020</v>
@@ -24497,7 +24497,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G832" t="n">
-        <v>5.55645561218262</v>
+        <v>5.55645513534546</v>
       </c>
       <c r="H832" t="n">
         <v>102703</v>
@@ -24526,7 +24526,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G833" t="n">
-        <v>5.56520652770996</v>
+        <v>5.5652060508728</v>
       </c>
       <c r="H833" t="n">
         <v>148381</v>
@@ -24555,7 +24555,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>5.50395345687866</v>
+        <v>5.5039529800415</v>
       </c>
       <c r="H834" t="n">
         <v>90763</v>
@@ -24584,7 +24584,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>5.5389552116394</v>
+        <v>5.53895473480225</v>
       </c>
       <c r="H835" t="n">
         <v>80407</v>
@@ -24613,7 +24613,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G836" t="n">
-        <v>5.56520652770996</v>
+        <v>5.5652060508728</v>
       </c>
       <c r="H836" t="n">
         <v>83200</v>
@@ -24642,7 +24642,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G837" t="n">
-        <v>5.55645561218262</v>
+        <v>5.55645513534546</v>
       </c>
       <c r="H837" t="n">
         <v>112536</v>
@@ -24671,7 +24671,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G838" t="n">
-        <v>5.55645561218262</v>
+        <v>5.55645513534546</v>
       </c>
       <c r="H838" t="n">
         <v>91572</v>
@@ -24700,7 +24700,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>5.52145385742188</v>
+        <v>5.52145433425903</v>
       </c>
       <c r="H839" t="n">
         <v>154582</v>
@@ -24729,7 +24729,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>5.52145385742188</v>
+        <v>5.52145433425903</v>
       </c>
       <c r="H840" t="n">
         <v>119319</v>
@@ -24758,7 +24758,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G841" t="n">
-        <v>5.49520349502563</v>
+        <v>5.49520301818848</v>
       </c>
       <c r="H841" t="n">
         <v>130287</v>
@@ -24787,7 +24787,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>5.49520349502563</v>
+        <v>5.49520301818848</v>
       </c>
       <c r="H842" t="n">
         <v>219460</v>
@@ -24816,7 +24816,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>5.51270484924316</v>
+        <v>5.51270437240601</v>
       </c>
       <c r="H843" t="n">
         <v>47978</v>
@@ -24845,7 +24845,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>5.54770612716675</v>
+        <v>5.54770517349243</v>
       </c>
       <c r="H844" t="n">
         <v>123531</v>
@@ -24874,7 +24874,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G845" t="n">
-        <v>5.58270597457886</v>
+        <v>5.58270645141602</v>
       </c>
       <c r="H845" t="n">
         <v>113463</v>
@@ -24903,7 +24903,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G846" t="n">
-        <v>5.54770612716675</v>
+        <v>5.54770517349243</v>
       </c>
       <c r="H846" t="n">
         <v>89727</v>
@@ -24932,7 +24932,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G847" t="n">
-        <v>5.56520652770996</v>
+        <v>5.5652060508728</v>
       </c>
       <c r="H847" t="n">
         <v>107788</v>
@@ -24961,7 +24961,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>5.58270597457886</v>
+        <v>5.58270645141602</v>
       </c>
       <c r="H848" t="n">
         <v>274013</v>
@@ -25019,7 +25019,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>5.38144969940186</v>
+        <v>5.38144874572754</v>
       </c>
       <c r="H850" t="n">
         <v>94240</v>
@@ -25135,7 +25135,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>5.20644283294678</v>
+        <v>5.20644235610962</v>
       </c>
       <c r="H854" t="n">
         <v>163647</v>
@@ -25164,7 +25164,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G855" t="n">
-        <v>5.25894546508789</v>
+        <v>5.25894498825073</v>
       </c>
       <c r="H855" t="n">
         <v>106509</v>
@@ -25222,7 +25222,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G857" t="n">
-        <v>5.37269926071167</v>
+        <v>5.37269830703735</v>
       </c>
       <c r="H857" t="n">
         <v>59164</v>
@@ -25251,7 +25251,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G858" t="n">
-        <v>5.35519886016846</v>
+        <v>5.3551983833313</v>
       </c>
       <c r="H858" t="n">
         <v>101854</v>
@@ -25309,7 +25309,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>5.36404609680176</v>
+        <v>5.3640456199646</v>
       </c>
       <c r="H860" t="n">
         <v>48287</v>
@@ -25367,7 +25367,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>5.26667928695679</v>
+        <v>5.26667833328247</v>
       </c>
       <c r="H862" t="n">
         <v>165617</v>
@@ -25454,7 +25454,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>5.26667928695679</v>
+        <v>5.26667833328247</v>
       </c>
       <c r="H865" t="n">
         <v>239692</v>
@@ -25483,7 +25483,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G866" t="n">
-        <v>5.23127317428589</v>
+        <v>5.23127269744873</v>
       </c>
       <c r="H866" t="n">
         <v>107563</v>
@@ -25541,7 +25541,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G868" t="n">
-        <v>5.23127317428589</v>
+        <v>5.23127269744873</v>
       </c>
       <c r="H868" t="n">
         <v>164222</v>
@@ -25570,7 +25570,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>5.24012470245361</v>
+        <v>5.2401237487793</v>
       </c>
       <c r="H869" t="n">
         <v>81117</v>
@@ -25599,7 +25599,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G870" t="n">
-        <v>5.25782823562622</v>
+        <v>5.25782775878906</v>
       </c>
       <c r="H870" t="n">
         <v>102625</v>
@@ -25657,7 +25657,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>5.22242116928101</v>
+        <v>5.22242069244385</v>
       </c>
       <c r="H872" t="n">
         <v>98873</v>
@@ -25715,7 +25715,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>5.24012470245361</v>
+        <v>5.2401237487793</v>
       </c>
       <c r="H874" t="n">
         <v>168078</v>
@@ -25773,7 +25773,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G876" t="n">
-        <v>5.26667928695679</v>
+        <v>5.26667833328247</v>
       </c>
       <c r="H876" t="n">
         <v>159434</v>
@@ -25802,7 +25802,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>5.2755298614502</v>
+        <v>5.27553033828735</v>
       </c>
       <c r="H877" t="n">
         <v>133520</v>
@@ -25831,7 +25831,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G878" t="n">
-        <v>5.25782823562622</v>
+        <v>5.25782775878906</v>
       </c>
       <c r="H878" t="n">
         <v>127179</v>
@@ -25860,7 +25860,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>5.24012470245361</v>
+        <v>5.2401237487793</v>
       </c>
       <c r="H879" t="n">
         <v>389442</v>
@@ -25889,7 +25889,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G880" t="n">
-        <v>5.26667928695679</v>
+        <v>5.26667833328247</v>
       </c>
       <c r="H880" t="n">
         <v>205395</v>
@@ -25918,7 +25918,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>5.24012470245361</v>
+        <v>5.2401237487793</v>
       </c>
       <c r="H881" t="n">
         <v>376959</v>
@@ -25947,7 +25947,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>5.22242116928101</v>
+        <v>5.22242069244385</v>
       </c>
       <c r="H882" t="n">
         <v>435477</v>
@@ -25976,7 +25976,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G883" t="n">
-        <v>5.16931200027466</v>
+        <v>5.1693115234375</v>
       </c>
       <c r="H883" t="n">
         <v>277530</v>
@@ -26034,7 +26034,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G885" t="n">
-        <v>5.07194519042969</v>
+        <v>5.07194471359253</v>
       </c>
       <c r="H885" t="n">
         <v>159194</v>
@@ -26150,7 +26150,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G889" t="n">
-        <v>5.03653812408447</v>
+        <v>5.03653860092163</v>
       </c>
       <c r="H889" t="n">
         <v>188961</v>
@@ -26179,7 +26179,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H890" t="n">
         <v>591354</v>
@@ -26208,7 +26208,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>5.16931200027466</v>
+        <v>5.1693115234375</v>
       </c>
       <c r="H891" t="n">
         <v>378106</v>
@@ -26266,7 +26266,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G893" t="n">
-        <v>5.09849977493286</v>
+        <v>5.09849882125854</v>
       </c>
       <c r="H893" t="n">
         <v>172844</v>
@@ -26353,7 +26353,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>5.08079671859741</v>
+        <v>5.08079624176025</v>
       </c>
       <c r="H896" t="n">
         <v>246065</v>
@@ -26527,7 +26527,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H902" t="n">
         <v>122768</v>
@@ -26556,7 +26556,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G903" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H903" t="n">
         <v>135564</v>
@@ -26614,7 +26614,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H905" t="n">
         <v>194365</v>
@@ -26643,7 +26643,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G906" t="n">
-        <v>5.21356916427612</v>
+        <v>5.21356868743896</v>
       </c>
       <c r="H906" t="n">
         <v>122715</v>
@@ -26672,7 +26672,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G907" t="n">
-        <v>5.23127317428589</v>
+        <v>5.23127269744873</v>
       </c>
       <c r="H907" t="n">
         <v>169100</v>
@@ -26701,7 +26701,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>5.25782823562622</v>
+        <v>5.25782775878906</v>
       </c>
       <c r="H908" t="n">
         <v>123611</v>
@@ -26730,7 +26730,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>5.24012470245361</v>
+        <v>5.2401237487793</v>
       </c>
       <c r="H909" t="n">
         <v>213504</v>
@@ -26759,7 +26759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H910" t="n">
         <v>240944</v>
@@ -26788,7 +26788,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>5.07194519042969</v>
+        <v>5.07194471359253</v>
       </c>
       <c r="H911" t="n">
         <v>314159</v>
@@ -26817,7 +26817,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G912" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H912" t="n">
         <v>245998</v>
@@ -26875,7 +26875,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>5.07194519042969</v>
+        <v>5.07194471359253</v>
       </c>
       <c r="H914" t="n">
         <v>125292</v>
@@ -27020,7 +27020,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G919" t="n">
-        <v>4.99228096008301</v>
+        <v>4.99228048324585</v>
       </c>
       <c r="H919" t="n">
         <v>74512</v>
@@ -27049,7 +27049,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>4.98342990875244</v>
+        <v>4.98342943191528</v>
       </c>
       <c r="H920" t="n">
         <v>140055</v>
@@ -27078,7 +27078,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G921" t="n">
-        <v>4.91261625289917</v>
+        <v>4.91261672973633</v>
       </c>
       <c r="H921" t="n">
         <v>66656</v>
@@ -27136,7 +27136,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G923" t="n">
-        <v>4.97457790374756</v>
+        <v>4.97457695007324</v>
       </c>
       <c r="H923" t="n">
         <v>78918</v>
@@ -27252,7 +27252,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G927" t="n">
-        <v>4.99228096008301</v>
+        <v>4.99228048324585</v>
       </c>
       <c r="H927" t="n">
         <v>58393</v>
@@ -27281,7 +27281,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.97457790374756</v>
+        <v>4.97457695007324</v>
       </c>
       <c r="H928" t="n">
         <v>47725</v>
@@ -27368,7 +27368,7 @@
         <v>5.75</v>
       </c>
       <c r="G931" t="n">
-        <v>5.08964776992798</v>
+        <v>5.08964729309082</v>
       </c>
       <c r="H931" t="n">
         <v>91374</v>
@@ -27455,7 +27455,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H934" t="n">
         <v>263647</v>
@@ -27484,7 +27484,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G935" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H935" t="n">
         <v>96297</v>
@@ -27774,7 +27774,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H945" t="n">
         <v>132070</v>
@@ -27803,7 +27803,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>5.23127317428589</v>
+        <v>5.23127269744873</v>
       </c>
       <c r="H946" t="n">
         <v>215249</v>
@@ -27861,7 +27861,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G948" t="n">
-        <v>5.36404609680176</v>
+        <v>5.3640456199646</v>
       </c>
       <c r="H948" t="n">
         <v>279533</v>
@@ -27890,7 +27890,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>5.45256185531616</v>
+        <v>5.452561378479</v>
       </c>
       <c r="H949" t="n">
         <v>366143</v>
@@ -27919,7 +27919,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>5.34634351730347</v>
+        <v>5.34634304046631</v>
       </c>
       <c r="H950" t="n">
         <v>408435</v>
@@ -27977,7 +27977,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G952" t="n">
-        <v>5.46141338348389</v>
+        <v>5.46141386032104</v>
       </c>
       <c r="H952" t="n">
         <v>522048</v>
@@ -28006,7 +28006,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G953" t="n">
-        <v>5.49681949615479</v>
+        <v>5.49681901931763</v>
       </c>
       <c r="H953" t="n">
         <v>217476</v>
@@ -28035,7 +28035,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>5.46141338348389</v>
+        <v>5.46141386032104</v>
       </c>
       <c r="H954" t="n">
         <v>197955</v>
@@ -28122,7 +28122,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G957" t="n">
-        <v>5.62074136734009</v>
+        <v>5.62074089050293</v>
       </c>
       <c r="H957" t="n">
         <v>651441</v>
@@ -28151,7 +28151,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G958" t="n">
-        <v>5.59418678283691</v>
+        <v>5.59418725967407</v>
       </c>
       <c r="H958" t="n">
         <v>359302</v>
@@ -28209,7 +28209,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G960" t="n">
-        <v>5.59418678283691</v>
+        <v>5.59418725967407</v>
       </c>
       <c r="H960" t="n">
         <v>131065</v>
@@ -28267,7 +28267,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>5.62074136734009</v>
+        <v>5.62074089050293</v>
       </c>
       <c r="H962" t="n">
         <v>122437</v>
@@ -28325,7 +28325,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G964" t="n">
-        <v>5.6384449005127</v>
+        <v>5.63844442367554</v>
       </c>
       <c r="H964" t="n">
         <v>342438</v>
@@ -28354,7 +28354,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G965" t="n">
-        <v>5.65614748001099</v>
+        <v>5.65614700317383</v>
       </c>
       <c r="H965" t="n">
         <v>328836</v>
@@ -28499,7 +28499,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G970" t="n">
-        <v>5.66499996185303</v>
+        <v>5.66499948501587</v>
       </c>
       <c r="H970" t="n">
         <v>168556</v>
@@ -28528,7 +28528,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>5.71810913085938</v>
+        <v>5.71810865402222</v>
       </c>
       <c r="H971" t="n">
         <v>256313</v>
@@ -28644,7 +28644,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G975" t="n">
-        <v>5.74466323852539</v>
+        <v>5.74466371536255</v>
       </c>
       <c r="H975" t="n">
         <v>186230</v>
@@ -28702,7 +28702,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>5.72696018218994</v>
+        <v>5.72695970535278</v>
       </c>
       <c r="H977" t="n">
         <v>86453</v>
@@ -28760,7 +28760,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>5.78007030487061</v>
+        <v>5.78006935119629</v>
       </c>
       <c r="H979" t="n">
         <v>267065</v>
@@ -28789,7 +28789,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>5.78892183303833</v>
+        <v>5.78892087936401</v>
       </c>
       <c r="H980" t="n">
         <v>156394</v>
@@ -28818,7 +28818,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G981" t="n">
-        <v>5.78892183303833</v>
+        <v>5.78892087936401</v>
       </c>
       <c r="H981" t="n">
         <v>233084</v>
@@ -28876,7 +28876,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>5.80662393569946</v>
+        <v>5.80662441253662</v>
       </c>
       <c r="H983" t="n">
         <v>223147</v>
@@ -28992,7 +28992,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>5.85088205337524</v>
+        <v>5.85088157653809</v>
       </c>
       <c r="H987" t="n">
         <v>244819</v>
@@ -29050,7 +29050,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>5.90399169921875</v>
+        <v>5.90399122238159</v>
       </c>
       <c r="H989" t="n">
         <v>98735</v>
@@ -29137,7 +29137,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G992" t="n">
-        <v>5.8862886428833</v>
+        <v>5.88628816604614</v>
       </c>
       <c r="H992" t="n">
         <v>143166</v>
@@ -29195,7 +29195,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G994" t="n">
-        <v>5.94824934005737</v>
+        <v>5.94824886322021</v>
       </c>
       <c r="H994" t="n">
         <v>320883</v>
@@ -29224,7 +29224,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>6.05446815490723</v>
+        <v>6.05446767807007</v>
       </c>
       <c r="H995" t="n">
         <v>446369</v>
@@ -29282,7 +29282,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>6.05446815490723</v>
+        <v>6.05446767807007</v>
       </c>
       <c r="H997" t="n">
         <v>287676</v>
@@ -29311,7 +29311,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G998" t="n">
-        <v>5.99250745773315</v>
+        <v>5.992506980896</v>
       </c>
       <c r="H998" t="n">
         <v>392205</v>
@@ -29340,7 +29340,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>5.99250745773315</v>
+        <v>5.992506980896</v>
       </c>
       <c r="H999" t="n">
         <v>180336</v>
@@ -29514,7 +29514,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.14298391342163</v>
+        <v>6.14298295974731</v>
       </c>
       <c r="H1005" t="n">
         <v>151000</v>
@@ -29572,7 +29572,7 @@
         <v>7</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.19609308242798</v>
+        <v>6.19609260559082</v>
       </c>
       <c r="H1007" t="n">
         <v>456813</v>
@@ -29601,7 +29601,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>6.1695384979248</v>
+        <v>6.16953802108765</v>
       </c>
       <c r="H1008" t="n">
         <v>290496</v>
@@ -29659,7 +29659,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>6.12528085708618</v>
+        <v>6.12528038024902</v>
       </c>
       <c r="H1010" t="n">
         <v>243925</v>
@@ -29717,7 +29717,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1012" t="n">
-        <v>6.07217121124268</v>
+        <v>6.07217073440552</v>
       </c>
       <c r="H1012" t="n">
         <v>409550</v>
@@ -29746,7 +29746,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1013" t="n">
-        <v>6.1164288520813</v>
+        <v>6.11642837524414</v>
       </c>
       <c r="H1013" t="n">
         <v>120852</v>
@@ -29775,7 +29775,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1014" t="n">
-        <v>6.1164288520813</v>
+        <v>6.11642837524414</v>
       </c>
       <c r="H1014" t="n">
         <v>132547</v>
@@ -29862,7 +29862,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1017" t="n">
-        <v>6.07217121124268</v>
+        <v>6.07217073440552</v>
       </c>
       <c r="H1017" t="n">
         <v>100246</v>
@@ -29949,7 +29949,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1020" t="n">
-        <v>6.05446815490723</v>
+        <v>6.05446767807007</v>
       </c>
       <c r="H1020" t="n">
         <v>181556</v>
@@ -29978,7 +29978,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1021" t="n">
-        <v>6.1695384979248</v>
+        <v>6.16953802108765</v>
       </c>
       <c r="H1021" t="n">
         <v>195476</v>
@@ -30065,7 +30065,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.1695384979248</v>
+        <v>6.16953802108765</v>
       </c>
       <c r="H1024" t="n">
         <v>130498</v>
@@ -30181,7 +30181,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.48819398880005</v>
+        <v>6.48819446563721</v>
       </c>
       <c r="H1028" t="n">
         <v>402258</v>
@@ -30210,7 +30210,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.37312459945679</v>
+        <v>6.37312507629395</v>
       </c>
       <c r="H1029" t="n">
         <v>423303</v>
@@ -30239,7 +30239,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.28460836410522</v>
+        <v>6.28460884094238</v>
       </c>
       <c r="H1030" t="n">
         <v>250713</v>
@@ -30268,7 +30268,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.26690578460693</v>
+        <v>6.26690483093262</v>
       </c>
       <c r="H1031" t="n">
         <v>181592</v>
@@ -30297,7 +30297,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1032" t="n">
-        <v>6.27575778961182</v>
+        <v>6.2757568359375</v>
       </c>
       <c r="H1032" t="n">
         <v>119998</v>
@@ -30355,7 +30355,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.1695384979248</v>
+        <v>6.16953802108765</v>
       </c>
       <c r="H1034" t="n">
         <v>319955</v>
@@ -30471,7 +30471,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.12528085708618</v>
+        <v>6.12528038024902</v>
       </c>
       <c r="H1038" t="n">
         <v>224701</v>
@@ -30500,7 +30500,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.27575778961182</v>
+        <v>6.2757568359375</v>
       </c>
       <c r="H1039" t="n">
         <v>197125</v>
@@ -30616,7 +30616,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.14298391342163</v>
+        <v>6.14298295974731</v>
       </c>
       <c r="H1043" t="n">
         <v>201881</v>
@@ -30703,7 +30703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.1695384979248</v>
+        <v>6.16953802108765</v>
       </c>
       <c r="H1046" t="n">
         <v>120883</v>
@@ -30732,7 +30732,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.14298391342163</v>
+        <v>6.14298295974731</v>
       </c>
       <c r="H1047" t="n">
         <v>119304</v>
@@ -30761,7 +30761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.28460836410522</v>
+        <v>6.28460884094238</v>
       </c>
       <c r="H1048" t="n">
         <v>201924</v>
@@ -30790,7 +30790,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.24920225143433</v>
+        <v>6.24920272827148</v>
       </c>
       <c r="H1049" t="n">
         <v>93353</v>
@@ -30819,7 +30819,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.27575778961182</v>
+        <v>6.2757568359375</v>
       </c>
       <c r="H1050" t="n">
         <v>169773</v>
@@ -30877,7 +30877,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.1164288520813</v>
+        <v>6.11642837524414</v>
       </c>
       <c r="H1052" t="n">
         <v>155559</v>
@@ -31051,7 +31051,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.54992866516113</v>
+        <v>5.54992914199829</v>
       </c>
       <c r="H1058" t="n">
         <v>532019</v>
@@ -31080,7 +31080,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1059" t="n">
-        <v>5.6384449005127</v>
+        <v>5.63844442367554</v>
       </c>
       <c r="H1059" t="n">
         <v>249090</v>
@@ -31109,7 +31109,7 @@
         <v>6.25</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.5322265625</v>
+        <v>5.53222560882568</v>
       </c>
       <c r="H1060" t="n">
         <v>1238952</v>
@@ -31138,7 +31138,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.23127317428589</v>
+        <v>5.23127269744873</v>
       </c>
       <c r="H1061" t="n">
         <v>924204</v>
@@ -31225,7 +31225,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.68247509002686</v>
+        <v>4.68247556686401</v>
       </c>
       <c r="H1064" t="n">
         <v>795956</v>
@@ -31283,7 +31283,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.02303504943848</v>
+        <v>4.02303409576416</v>
       </c>
       <c r="H1066" t="n">
         <v>1206251</v>
@@ -31370,7 +31370,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.50544452667236</v>
+        <v>4.50544404983521</v>
       </c>
       <c r="H1069" t="n">
         <v>603497</v>
@@ -31631,7 +31631,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98342990875244</v>
+        <v>4.98342943191528</v>
       </c>
       <c r="H1078" t="n">
         <v>114376</v>
@@ -31660,7 +31660,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98342990875244</v>
+        <v>4.98342943191528</v>
       </c>
       <c r="H1079" t="n">
         <v>253686</v>
@@ -31689,7 +31689,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1080" t="n">
-        <v>4.77099132537842</v>
+        <v>4.77099227905273</v>
       </c>
       <c r="H1080" t="n">
         <v>202976</v>
@@ -31747,7 +31747,7 @@
         <v>5.5</v>
       </c>
       <c r="G1082" t="n">
-        <v>4.86835908889771</v>
+        <v>4.86835861206055</v>
       </c>
       <c r="H1082" t="n">
         <v>104895</v>
@@ -31776,7 +31776,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1083" t="n">
-        <v>4.90376567840576</v>
+        <v>4.9037652015686</v>
       </c>
       <c r="H1083" t="n">
         <v>89918</v>
@@ -31805,7 +31805,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.08079671859741</v>
+        <v>5.08079624176025</v>
       </c>
       <c r="H1084" t="n">
         <v>238345</v>
@@ -31863,7 +31863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H1086" t="n">
         <v>115122</v>
@@ -31892,7 +31892,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H1087" t="n">
         <v>113442</v>
@@ -31921,7 +31921,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H1088" t="n">
         <v>105395</v>
@@ -31979,7 +31979,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.25782823562622</v>
+        <v>5.25782775878906</v>
       </c>
       <c r="H1090" t="n">
         <v>217878</v>
@@ -32037,7 +32037,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.22242116928101</v>
+        <v>5.22242069244385</v>
       </c>
       <c r="H1092" t="n">
         <v>76961</v>
@@ -32066,7 +32066,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.16931200027466</v>
+        <v>5.1693115234375</v>
       </c>
       <c r="H1093" t="n">
         <v>81621</v>
@@ -32095,7 +32095,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.21356916427612</v>
+        <v>5.21356868743896</v>
       </c>
       <c r="H1094" t="n">
         <v>61436</v>
@@ -32153,7 +32153,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.17816400527954</v>
+        <v>5.17816352844238</v>
       </c>
       <c r="H1096" t="n">
         <v>123854</v>
@@ -32240,7 +32240,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.22242116928101</v>
+        <v>5.22242069244385</v>
       </c>
       <c r="H1099" t="n">
         <v>96506</v>
@@ -32327,7 +32327,7 @@
         <v>5.75</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.08964776992798</v>
+        <v>5.08964729309082</v>
       </c>
       <c r="H1102" t="n">
         <v>40634</v>
@@ -32414,7 +32414,7 @@
         <v>5.75</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.08964776992798</v>
+        <v>5.08964729309082</v>
       </c>
       <c r="H1105" t="n">
         <v>55418</v>
@@ -32472,7 +32472,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.11620235443115</v>
+        <v>5.11620283126831</v>
       </c>
       <c r="H1107" t="n">
         <v>62293</v>
@@ -32501,7 +32501,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.97457790374756</v>
+        <v>4.97457695007324</v>
       </c>
       <c r="H1108" t="n">
         <v>62073</v>
@@ -32559,7 +32559,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.30590105056763</v>
+        <v>5.30590009689331</v>
       </c>
       <c r="H1110" t="n">
         <v>135600</v>
@@ -32675,7 +32675,7 @@
         <v>5.75</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1114" t="n">
         <v>131014</v>
@@ -32704,7 +32704,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.25194311141968</v>
+        <v>5.25194263458252</v>
       </c>
       <c r="H1115" t="n">
         <v>165256</v>
@@ -32733,7 +32733,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.17999839782715</v>
+        <v>5.17999792098999</v>
       </c>
       <c r="H1116" t="n">
         <v>152357</v>
@@ -32791,7 +32791,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.31489419937134</v>
+        <v>5.31489372253418</v>
       </c>
       <c r="H1118" t="n">
         <v>250841</v>
@@ -32849,7 +32849,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.25194311141968</v>
+        <v>5.25194263458252</v>
       </c>
       <c r="H1120" t="n">
         <v>316966</v>
@@ -32878,7 +32878,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.26093626022339</v>
+        <v>5.26093530654907</v>
       </c>
       <c r="H1121" t="n">
         <v>214573</v>
@@ -33023,7 +33023,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.58468580245972</v>
+        <v>5.58468532562256</v>
       </c>
       <c r="H1126" t="n">
         <v>477754</v>
@@ -33052,7 +33052,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>5.44978904724121</v>
+        <v>5.44978952407837</v>
       </c>
       <c r="H1127" t="n">
         <v>216640</v>
@@ -33081,7 +33081,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.30590105056763</v>
+        <v>5.30590009689331</v>
       </c>
       <c r="H1128" t="n">
         <v>312773</v>
@@ -33110,7 +33110,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.30590105056763</v>
+        <v>5.30590009689331</v>
       </c>
       <c r="H1129" t="n">
         <v>349978</v>
@@ -33226,7 +33226,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.24294996261597</v>
+        <v>5.24294948577881</v>
       </c>
       <c r="H1133" t="n">
         <v>242008</v>
@@ -33284,7 +33284,7 @@
         <v>5.75</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1135" t="n">
         <v>490340</v>
@@ -33371,7 +33371,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.01812314987183</v>
+        <v>5.01812267303467</v>
       </c>
       <c r="H1138" t="n">
         <v>1021287</v>
@@ -33400,7 +33400,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.11704730987549</v>
+        <v>5.11704683303833</v>
       </c>
       <c r="H1139" t="n">
         <v>441321</v>
@@ -33429,7 +33429,7 @@
         <v>5.75</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1140" t="n">
         <v>298714</v>
@@ -33458,7 +33458,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1141" t="n">
-        <v>5.23395681381226</v>
+        <v>5.2339563369751</v>
       </c>
       <c r="H1141" t="n">
         <v>198468</v>
@@ -33487,7 +33487,7 @@
         <v>5.75</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1142" t="n">
         <v>221294</v>
@@ -33632,7 +33632,7 @@
         <v>5.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1147" t="n">
         <v>84071</v>
@@ -33661,7 +33661,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.15301895141602</v>
+        <v>5.15301847457886</v>
       </c>
       <c r="H1148" t="n">
         <v>155032</v>
@@ -33748,7 +33748,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.06308889389038</v>
+        <v>5.06308841705322</v>
       </c>
       <c r="H1151" t="n">
         <v>162410</v>
@@ -33777,7 +33777,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.15301895141602</v>
+        <v>5.15301847457886</v>
       </c>
       <c r="H1152" t="n">
         <v>197161</v>
@@ -33893,7 +33893,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.31489419937134</v>
+        <v>5.31489372253418</v>
       </c>
       <c r="H1156" t="n">
         <v>396084</v>
@@ -33951,7 +33951,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.26093626022339</v>
+        <v>5.26093530654907</v>
       </c>
       <c r="H1158" t="n">
         <v>131505</v>
@@ -33980,7 +33980,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.16201210021973</v>
+        <v>5.16201162338257</v>
       </c>
       <c r="H1159" t="n">
         <v>187803</v>
@@ -34009,7 +34009,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.16201210021973</v>
+        <v>5.16201162338257</v>
       </c>
       <c r="H1160" t="n">
         <v>121501</v>
@@ -34154,7 +34154,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.06308889389038</v>
+        <v>5.06308841705322</v>
       </c>
       <c r="H1165" t="n">
         <v>165771</v>
@@ -34212,7 +34212,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.15301895141602</v>
+        <v>5.15301847457886</v>
       </c>
       <c r="H1167" t="n">
         <v>110319</v>
@@ -34357,7 +34357,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.23395681381226</v>
+        <v>5.2339563369751</v>
       </c>
       <c r="H1172" t="n">
         <v>74655</v>
@@ -34386,7 +34386,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.20697736740112</v>
+        <v>5.20697689056396</v>
       </c>
       <c r="H1173" t="n">
         <v>75937</v>
@@ -34473,7 +34473,7 @@
         <v>5.75</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1176" t="n">
         <v>62872</v>
@@ -34531,7 +34531,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1178" t="n">
-        <v>5.11704730987549</v>
+        <v>5.11704683303833</v>
       </c>
       <c r="H1178" t="n">
         <v>62170</v>
@@ -34560,7 +34560,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.12603998184204</v>
+        <v>5.12603902816772</v>
       </c>
       <c r="H1179" t="n">
         <v>59599</v>
@@ -34589,7 +34589,7 @@
         <v>5.75</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1180" t="n">
         <v>69163</v>
@@ -34676,7 +34676,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>5.11704730987549</v>
+        <v>5.11704683303833</v>
       </c>
       <c r="H1183" t="n">
         <v>78859</v>
@@ -34734,7 +34734,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.05409574508667</v>
+        <v>5.05409479141235</v>
       </c>
       <c r="H1185" t="n">
         <v>178424</v>
@@ -34966,7 +34966,7 @@
         <v>5.75</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1193" t="n">
         <v>68328</v>
@@ -34995,7 +34995,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.20697736740112</v>
+        <v>5.20697689056396</v>
       </c>
       <c r="H1194" t="n">
         <v>100243</v>
@@ -35169,7 +35169,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.25194311141968</v>
+        <v>5.25194263458252</v>
       </c>
       <c r="H1200" t="n">
         <v>301602</v>
@@ -35198,7 +35198,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>5.24294996261597</v>
+        <v>5.24294948577881</v>
       </c>
       <c r="H1201" t="n">
         <v>246369</v>
@@ -35459,7 +35459,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.16201210021973</v>
+        <v>5.16201162338257</v>
       </c>
       <c r="H1210" t="n">
         <v>89412</v>
@@ -35488,7 +35488,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>5.24294996261597</v>
+        <v>5.24294948577881</v>
       </c>
       <c r="H1211" t="n">
         <v>113956</v>
@@ -35517,7 +35517,7 @@
         <v>5.75</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.1710057258606</v>
+        <v>5.17100524902344</v>
       </c>
       <c r="H1212" t="n">
         <v>83123</v>
@@ -35575,7 +35575,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.17999839782715</v>
+        <v>5.17999792098999</v>
       </c>
       <c r="H1214" t="n">
         <v>73439</v>
@@ -35691,7 +35691,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.20697736740112</v>
+        <v>5.20697689056396</v>
       </c>
       <c r="H1218" t="n">
         <v>101647</v>
@@ -35836,7 +35836,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.07208156585693</v>
+        <v>5.07208108901978</v>
       </c>
       <c r="H1223" t="n">
         <v>89992</v>
@@ -35865,7 +35865,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1224" t="n">
-        <v>5.11704730987549</v>
+        <v>5.11704683303833</v>
       </c>
       <c r="H1224" t="n">
         <v>78742</v>
@@ -35894,7 +35894,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.01812314987183</v>
+        <v>5.01812267303467</v>
       </c>
       <c r="H1225" t="n">
         <v>133178</v>
@@ -35981,7 +35981,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.80228996276855</v>
+        <v>4.8022894859314</v>
       </c>
       <c r="H1228" t="n">
         <v>271057</v>
@@ -36039,7 +36039,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.90121364593506</v>
+        <v>4.9012131690979</v>
       </c>
       <c r="H1230" t="n">
         <v>111942</v>
@@ -36068,7 +36068,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1231" t="n">
-        <v>5.00013732910156</v>
+        <v>5.0001368522644</v>
       </c>
       <c r="H1231" t="n">
         <v>63603</v>
@@ -36155,7 +36155,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1234" t="n">
-        <v>5.12603998184204</v>
+        <v>5.12603902816772</v>
       </c>
       <c r="H1234" t="n">
         <v>38959</v>
@@ -36184,7 +36184,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.26093626022339</v>
+        <v>5.26093530654907</v>
       </c>
       <c r="H1235" t="n">
         <v>238197</v>
@@ -36242,7 +36242,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.30590105056763</v>
+        <v>5.30590009689331</v>
       </c>
       <c r="H1237" t="n">
         <v>144615</v>
@@ -36271,7 +36271,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.31489419937134</v>
+        <v>5.31489372253418</v>
       </c>
       <c r="H1238" t="n">
         <v>62105</v>
@@ -36329,7 +36329,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1240" t="n">
-        <v>5.5217342376709</v>
+        <v>5.52173328399658</v>
       </c>
       <c r="H1240" t="n">
         <v>192244</v>
@@ -36358,7 +36358,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>5.46777582168579</v>
+        <v>5.46777534484863</v>
       </c>
       <c r="H1241" t="n">
         <v>132165</v>
@@ -36387,7 +36387,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.70159578323364</v>
+        <v>5.70159530639648</v>
       </c>
       <c r="H1242" t="n">
         <v>642197</v>
@@ -36416,7 +36416,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.66562271118164</v>
+        <v>5.6656231880188</v>
       </c>
       <c r="H1243" t="n">
         <v>356782</v>
@@ -36503,7 +36503,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.92642259597778</v>
+        <v>5.92642164230347</v>
       </c>
       <c r="H1246" t="n">
         <v>248921</v>
@@ -36619,7 +36619,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1250" t="n">
-        <v>5.66562271118164</v>
+        <v>5.6656231880188</v>
       </c>
       <c r="H1250" t="n">
         <v>301977</v>
@@ -36648,7 +36648,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353954315186</v>
       </c>
       <c r="H1251" t="n">
         <v>103077</v>
@@ -36677,7 +36677,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353954315186</v>
       </c>
       <c r="H1252" t="n">
         <v>73914</v>
@@ -36735,7 +36735,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1254" t="n">
-        <v>5.7645468711853</v>
+        <v>5.76454639434814</v>
       </c>
       <c r="H1254" t="n">
         <v>84005</v>
@@ -36793,7 +36793,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.89044904708862</v>
+        <v>5.89044952392578</v>
       </c>
       <c r="H1256" t="n">
         <v>42030</v>
@@ -36851,7 +36851,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1258" t="n">
-        <v>5.81850481033325</v>
+        <v>5.81850433349609</v>
       </c>
       <c r="H1258" t="n">
         <v>79450</v>
@@ -36880,7 +36880,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1259" t="n">
-        <v>5.83649015426636</v>
+        <v>5.83649063110352</v>
       </c>
       <c r="H1259" t="n">
         <v>98434</v>
@@ -36938,7 +36938,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.89044904708862</v>
+        <v>5.89044952392578</v>
       </c>
       <c r="H1261" t="n">
         <v>82915</v>
@@ -36967,7 +36967,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.94440793991089</v>
+        <v>5.94440698623657</v>
       </c>
       <c r="H1262" t="n">
         <v>131098</v>
@@ -36996,7 +36996,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1263" t="n">
-        <v>6.04333114624023</v>
+        <v>6.04333066940308</v>
       </c>
       <c r="H1263" t="n">
         <v>220988</v>
@@ -37083,7 +37083,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1266" t="n">
-        <v>6.20520639419556</v>
+        <v>6.2052059173584</v>
       </c>
       <c r="H1266" t="n">
         <v>145435</v>
@@ -37170,7 +37170,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>6.25916481018066</v>
+        <v>6.25916433334351</v>
       </c>
       <c r="H1269" t="n">
         <v>172917</v>
@@ -37257,7 +37257,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>6.22319221496582</v>
+        <v>6.22319173812866</v>
       </c>
       <c r="H1272" t="n">
         <v>78648</v>
@@ -37286,7 +37286,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>6.22319221496582</v>
+        <v>6.22319173812866</v>
       </c>
       <c r="H1273" t="n">
         <v>71839</v>
@@ -37373,7 +37373,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1276" t="n">
-        <v>6.26815700531006</v>
+        <v>6.2681565284729</v>
       </c>
       <c r="H1276" t="n">
         <v>90984</v>
@@ -37489,7 +37489,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1280" t="n">
-        <v>6.17822694778442</v>
+        <v>6.17822647094727</v>
       </c>
       <c r="H1280" t="n">
         <v>140674</v>
@@ -37518,7 +37518,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1281" t="n">
-        <v>6.20520639419556</v>
+        <v>6.2052059173584</v>
       </c>
       <c r="H1281" t="n">
         <v>111526</v>
@@ -37576,7 +37576,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>6.25916481018066</v>
+        <v>6.25916433334351</v>
       </c>
       <c r="H1283" t="n">
         <v>86316</v>
@@ -37605,7 +37605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.16923379898071</v>
+        <v>6.16923332214355</v>
       </c>
       <c r="H1284" t="n">
         <v>81473</v>
@@ -37634,7 +37634,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.15124797821045</v>
+        <v>6.15124750137329</v>
       </c>
       <c r="H1285" t="n">
         <v>122620</v>
@@ -37663,7 +37663,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.0613169670105</v>
+        <v>6.06131649017334</v>
       </c>
       <c r="H1286" t="n">
         <v>150874</v>
@@ -37692,7 +37692,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1287" t="n">
-        <v>6.1422553062439</v>
+        <v>6.14225482940674</v>
       </c>
       <c r="H1287" t="n">
         <v>86396</v>
@@ -37721,7 +37721,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.98937225341797</v>
+        <v>5.98937273025513</v>
       </c>
       <c r="H1288" t="n">
         <v>115284</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.0613169670105</v>
+        <v>6.06131649017334</v>
       </c>
       <c r="H1289" t="n">
         <v>66895</v>
@@ -37779,7 +37779,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.96239423751831</v>
+        <v>5.96239376068115</v>
       </c>
       <c r="H1290" t="n">
         <v>94564</v>
@@ -37808,7 +37808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1291" t="n">
-        <v>6.02534532546997</v>
+        <v>6.02534484863281</v>
       </c>
       <c r="H1291" t="n">
         <v>70537</v>
@@ -37837,7 +37837,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.20520639419556</v>
+        <v>6.2052059173584</v>
       </c>
       <c r="H1292" t="n">
         <v>56120</v>
@@ -38040,7 +38040,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1299" t="n">
-        <v>6.59190702438354</v>
+        <v>6.5919075012207</v>
       </c>
       <c r="H1299" t="n">
         <v>96645</v>
@@ -38069,7 +38069,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.60090017318726</v>
+        <v>6.60090112686157</v>
       </c>
       <c r="H1300" t="n">
         <v>113566</v>
@@ -38156,7 +38156,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.45701122283936</v>
+        <v>6.45701217651367</v>
       </c>
       <c r="H1303" t="n">
         <v>68220</v>
@@ -38185,7 +38185,7 @@
         <v>7</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.29513692855835</v>
+        <v>6.29513645172119</v>
       </c>
       <c r="H1304" t="n">
         <v>112068</v>
@@ -38301,7 +38301,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.31312274932861</v>
+        <v>6.31312227249146</v>
       </c>
       <c r="H1308" t="n">
         <v>122732</v>
@@ -38359,7 +38359,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1310" t="n">
-        <v>6.31312274932861</v>
+        <v>6.31312227249146</v>
       </c>
       <c r="H1310" t="n">
         <v>217995</v>
@@ -38388,7 +38388,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.40305328369141</v>
+        <v>6.40305376052856</v>
       </c>
       <c r="H1311" t="n">
         <v>301099</v>
@@ -38417,7 +38417,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>6.4480185508728</v>
+        <v>6.44801902770996</v>
       </c>
       <c r="H1312" t="n">
         <v>133564</v>
@@ -38446,7 +38446,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1313" t="n">
-        <v>6.43902492523193</v>
+        <v>6.43902540206909</v>
       </c>
       <c r="H1313" t="n">
         <v>133858</v>
@@ -38475,7 +38475,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1314" t="n">
-        <v>6.43902492523193</v>
+        <v>6.43902540206909</v>
       </c>
       <c r="H1314" t="n">
         <v>133223</v>
@@ -38533,7 +38533,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.51096963882446</v>
+        <v>6.51097011566162</v>
       </c>
       <c r="H1316" t="n">
         <v>114486</v>
@@ -38562,7 +38562,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1317" t="n">
-        <v>6.65485906600952</v>
+        <v>6.65485954284668</v>
       </c>
       <c r="H1317" t="n">
         <v>181693</v>
@@ -38591,7 +38591,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1318" t="n">
-        <v>6.64586544036865</v>
+        <v>6.64586591720581</v>
       </c>
       <c r="H1318" t="n">
         <v>136662</v>
@@ -38649,7 +38649,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>6.71780967712402</v>
+        <v>6.71781015396118</v>
       </c>
       <c r="H1320" t="n">
         <v>103160</v>
@@ -38678,7 +38678,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.71780967712402</v>
+        <v>6.71781015396118</v>
       </c>
       <c r="H1321" t="n">
         <v>207077</v>
@@ -38765,7 +38765,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1324" t="n">
-        <v>6.65485906600952</v>
+        <v>6.65485954284668</v>
       </c>
       <c r="H1324" t="n">
         <v>112806</v>
@@ -38794,7 +38794,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G1325" t="n">
-        <v>6.60989332199097</v>
+        <v>6.60989379882812</v>
       </c>
       <c r="H1325" t="n">
         <v>206710</v>
@@ -38881,7 +38881,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.72680330276489</v>
+        <v>6.72680377960205</v>
       </c>
       <c r="H1328" t="n">
         <v>149348</v>
@@ -38939,7 +38939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1330" t="n">
-        <v>6.87069225311279</v>
+        <v>6.87069177627563</v>
       </c>
       <c r="H1330" t="n">
         <v>216187</v>
@@ -38968,7 +38968,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.81673431396484</v>
+        <v>6.81673336029053</v>
       </c>
       <c r="H1331" t="n">
         <v>94645</v>
@@ -38997,7 +38997,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1332" t="n">
-        <v>6.8257269859314</v>
+        <v>6.82572746276855</v>
       </c>
       <c r="H1332" t="n">
         <v>100607</v>
@@ -39026,7 +39026,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1333" t="n">
-        <v>6.81673431396484</v>
+        <v>6.81673336029053</v>
       </c>
       <c r="H1333" t="n">
         <v>176499</v>
@@ -39084,7 +39084,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.91565799713135</v>
+        <v>6.91565704345703</v>
       </c>
       <c r="H1335" t="n">
         <v>97238</v>
@@ -39142,7 +39142,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1337" t="n">
-        <v>6.95162963867188</v>
+        <v>6.95163011550903</v>
       </c>
       <c r="H1337" t="n">
         <v>155514</v>
@@ -39171,7 +39171,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1338" t="n">
-        <v>6.87069225311279</v>
+        <v>6.87069177627563</v>
       </c>
       <c r="H1338" t="n">
         <v>85560</v>
@@ -39200,7 +39200,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.89767122268677</v>
+        <v>6.89767169952393</v>
       </c>
       <c r="H1339" t="n">
         <v>99309</v>
@@ -39229,7 +39229,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.91565799713135</v>
+        <v>6.91565704345703</v>
       </c>
       <c r="H1340" t="n">
         <v>96905</v>
@@ -39287,7 +39287,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>6.93364334106445</v>
+        <v>6.93364381790161</v>
       </c>
       <c r="H1342" t="n">
         <v>82963</v>
@@ -39316,7 +39316,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.00558805465698</v>
+        <v>7.00558853149414</v>
       </c>
       <c r="H1343" t="n">
         <v>99337</v>
@@ -39374,7 +39374,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1345" t="n">
-        <v>7.00558805465698</v>
+        <v>7.00558853149414</v>
       </c>
       <c r="H1345" t="n">
         <v>291998</v>
@@ -39403,7 +39403,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.98760223388672</v>
+        <v>6.98760175704956</v>
       </c>
       <c r="H1346" t="n">
         <v>300940</v>
@@ -39519,7 +39519,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1350" t="n">
-        <v>7.03256750106812</v>
+        <v>7.03256702423096</v>
       </c>
       <c r="H1350" t="n">
         <v>192415</v>
@@ -39548,7 +39548,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1351" t="n">
-        <v>7.03256750106812</v>
+        <v>7.03256702423096</v>
       </c>
       <c r="H1351" t="n">
         <v>214825</v>
@@ -39577,7 +39577,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1352" t="n">
-        <v>7.05055332183838</v>
+        <v>7.05055379867554</v>
       </c>
       <c r="H1352" t="n">
         <v>116077</v>
@@ -39606,7 +39606,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1353" t="n">
-        <v>7.03256750106812</v>
+        <v>7.03256702423096</v>
       </c>
       <c r="H1353" t="n">
         <v>93589</v>
@@ -39664,7 +39664,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1355" t="n">
-        <v>7.03256750106812</v>
+        <v>7.03256702423096</v>
       </c>
       <c r="H1355" t="n">
         <v>109570</v>
@@ -39780,7 +39780,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>7.10451126098633</v>
+        <v>7.10451173782349</v>
       </c>
       <c r="H1359" t="n">
         <v>99010</v>
@@ -39896,7 +39896,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1363" t="n">
-        <v>7.10451126098633</v>
+        <v>7.10451173782349</v>
       </c>
       <c r="H1363" t="n">
         <v>118984</v>
@@ -39925,7 +39925,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1364" t="n">
-        <v>7.02357339859009</v>
+        <v>7.02357387542725</v>
       </c>
       <c r="H1364" t="n">
         <v>169565</v>
@@ -39954,7 +39954,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1365" t="n">
-        <v>6.99659490585327</v>
+        <v>6.99659538269043</v>
       </c>
       <c r="H1365" t="n">
         <v>147290</v>
@@ -39983,7 +39983,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1366" t="n">
-        <v>6.91565799713135</v>
+        <v>6.91565704345703</v>
       </c>
       <c r="H1366" t="n">
         <v>165000</v>
@@ -40041,7 +40041,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.95162963867188</v>
+        <v>6.95163011550903</v>
       </c>
       <c r="H1368" t="n">
         <v>240781</v>
@@ -40099,7 +40099,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1370" t="n">
-        <v>7.10651016235352</v>
+        <v>7.10651063919067</v>
       </c>
       <c r="H1370" t="n">
         <v>196869</v>
@@ -40157,7 +40157,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1372" t="n">
-        <v>7.04273366928101</v>
+        <v>7.04273414611816</v>
       </c>
       <c r="H1372" t="n">
         <v>599104</v>
@@ -40302,7 +40302,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>7.34339427947998</v>
+        <v>7.34339475631714</v>
       </c>
       <c r="H1377" t="n">
         <v>157404</v>
@@ -40331,7 +40331,7 @@
         <v>8</v>
       </c>
       <c r="G1378" t="n">
-        <v>7.2887282371521</v>
+        <v>7.28872871398926</v>
       </c>
       <c r="H1378" t="n">
         <v>75557</v>
@@ -40360,7 +40360,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1379" t="n">
-        <v>7.3707275390625</v>
+        <v>7.37072706222534</v>
       </c>
       <c r="H1379" t="n">
         <v>149156</v>
@@ -40389,7 +40389,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1380" t="n">
-        <v>7.3889479637146</v>
+        <v>7.38894844055176</v>
       </c>
       <c r="H1380" t="n">
         <v>125195</v>
@@ -40418,7 +40418,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1381" t="n">
-        <v>7.43450307846069</v>
+        <v>7.43450260162354</v>
       </c>
       <c r="H1381" t="n">
         <v>464308</v>
@@ -40476,7 +40476,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1383" t="n">
-        <v>7.3889479637146</v>
+        <v>7.38894844055176</v>
       </c>
       <c r="H1383" t="n">
         <v>96050</v>
@@ -40505,7 +40505,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.3707275390625</v>
+        <v>7.37072706222534</v>
       </c>
       <c r="H1384" t="n">
         <v>151071</v>
@@ -40621,7 +40621,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.22495174407959</v>
+        <v>7.22495222091675</v>
       </c>
       <c r="H1388" t="n">
         <v>286037</v>
@@ -40650,7 +40650,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1389" t="n">
-        <v>7.37983751296997</v>
+        <v>7.37983798980713</v>
       </c>
       <c r="H1389" t="n">
         <v>377221</v>
@@ -40679,7 +40679,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1390" t="n">
-        <v>7.42539167404175</v>
+        <v>7.42539215087891</v>
       </c>
       <c r="H1390" t="n">
         <v>416005</v>
@@ -40766,7 +40766,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.39805889129639</v>
+        <v>7.3980598449707</v>
       </c>
       <c r="H1393" t="n">
         <v>102035</v>
@@ -40795,7 +40795,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>7.39805889129639</v>
+        <v>7.3980598449707</v>
       </c>
       <c r="H1394" t="n">
         <v>418203</v>
@@ -40824,7 +40824,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>7.55294513702393</v>
+        <v>7.55294466018677</v>
       </c>
       <c r="H1395" t="n">
         <v>363699</v>
@@ -40853,7 +40853,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1396" t="n">
-        <v>7.53472375869751</v>
+        <v>7.53472328186035</v>
       </c>
       <c r="H1396" t="n">
         <v>531591</v>
@@ -40882,7 +40882,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1397" t="n">
-        <v>7.65316534042358</v>
+        <v>7.65316390991211</v>
       </c>
       <c r="H1397" t="n">
         <v>309839</v>
@@ -40911,7 +40911,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1398" t="n">
-        <v>7.77160692214966</v>
+        <v>7.7716064453125</v>
       </c>
       <c r="H1398" t="n">
         <v>494640</v>
@@ -40940,7 +40940,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1399" t="n">
-        <v>7.84449338912964</v>
+        <v>7.8444938659668</v>
       </c>
       <c r="H1399" t="n">
         <v>158638</v>
@@ -40969,7 +40969,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.77160692214966</v>
+        <v>7.7716064453125</v>
       </c>
       <c r="H1400" t="n">
         <v>315434</v>
@@ -40998,7 +40998,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.81716060638428</v>
+        <v>7.81716012954712</v>
       </c>
       <c r="H1401" t="n">
         <v>228667</v>
@@ -41056,7 +41056,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.66227531433105</v>
+        <v>7.66227579116821</v>
       </c>
       <c r="H1403" t="n">
         <v>229263</v>
@@ -41085,7 +41085,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1404" t="n">
-        <v>7.73516273498535</v>
+        <v>7.73516321182251</v>
       </c>
       <c r="H1404" t="n">
         <v>262110</v>
@@ -41114,7 +41114,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.88093662261963</v>
+        <v>7.88093757629395</v>
       </c>
       <c r="H1405" t="n">
         <v>470672</v>
@@ -41172,7 +41172,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.71694135665894</v>
+        <v>7.71694231033325</v>
       </c>
       <c r="H1407" t="n">
         <v>402536</v>
@@ -41201,7 +41201,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.54383325576782</v>
+        <v>7.54383373260498</v>
       </c>
       <c r="H1408" t="n">
         <v>300708</v>
@@ -41230,7 +41230,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>7.25228500366211</v>
+        <v>7.25228452682495</v>
       </c>
       <c r="H1409" t="n">
         <v>500341</v>
@@ -41288,7 +41288,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1411" t="n">
-        <v>7.41628217697144</v>
+        <v>7.41628170013428</v>
       </c>
       <c r="H1411" t="n">
         <v>604867</v>
@@ -41317,7 +41317,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1412" t="n">
-        <v>7.53472375869751</v>
+        <v>7.53472328186035</v>
       </c>
       <c r="H1412" t="n">
         <v>241976</v>
@@ -41375,7 +41375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>7.63494348526001</v>
+        <v>7.63494300842285</v>
       </c>
       <c r="H1414" t="n">
         <v>305244</v>
@@ -41433,7 +41433,7 @@
         <v>8.25</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.51650094985962</v>
+        <v>7.51650142669678</v>
       </c>
       <c r="H1416" t="n">
         <v>115695</v>
@@ -41462,7 +41462,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.57116794586182</v>
+        <v>7.5711669921875</v>
       </c>
       <c r="H1417" t="n">
         <v>62074</v>
@@ -41491,7 +41491,7 @@
         <v>8.25</v>
       </c>
       <c r="G1418" t="n">
-        <v>7.51650094985962</v>
+        <v>7.51650142669678</v>
       </c>
       <c r="H1418" t="n">
         <v>64706</v>
@@ -41520,7 +41520,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1419" t="n">
-        <v>7.63494348526001</v>
+        <v>7.63494300842285</v>
       </c>
       <c r="H1419" t="n">
         <v>67360</v>
@@ -41607,7 +41607,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>7.81716060638428</v>
+        <v>7.81716012954712</v>
       </c>
       <c r="H1422" t="n">
         <v>171338</v>
@@ -41665,7 +41665,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1424" t="n">
-        <v>7.65316534042358</v>
+        <v>7.65316390991211</v>
       </c>
       <c r="H1424" t="n">
         <v>56956</v>
@@ -41723,7 +41723,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1426" t="n">
-        <v>7.77160692214966</v>
+        <v>7.7716064453125</v>
       </c>
       <c r="H1426" t="n">
         <v>56904</v>
@@ -41781,7 +41781,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>7.70782995223999</v>
+        <v>7.70783042907715</v>
       </c>
       <c r="H1428" t="n">
         <v>149387</v>
@@ -41810,7 +41810,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>7.62583208084106</v>
+        <v>7.62583255767822</v>
       </c>
       <c r="H1429" t="n">
         <v>53420</v>
@@ -41839,7 +41839,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.63494348526001</v>
+        <v>7.63494300842285</v>
       </c>
       <c r="H1430" t="n">
         <v>156377</v>
@@ -41926,7 +41926,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1433" t="n">
-        <v>7.68960762023926</v>
+        <v>7.6896071434021</v>
       </c>
       <c r="H1433" t="n">
         <v>62051</v>
@@ -41955,7 +41955,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1434" t="n">
-        <v>7.83538389205933</v>
+        <v>7.83538341522217</v>
       </c>
       <c r="H1434" t="n">
         <v>250086</v>
@@ -41984,7 +41984,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1435" t="n">
-        <v>7.83538389205933</v>
+        <v>7.83538341522217</v>
       </c>
       <c r="H1435" t="n">
         <v>418852</v>
@@ -42071,7 +42071,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>8.27270698547363</v>
+        <v>8.27270603179932</v>
       </c>
       <c r="H1438" t="n">
         <v>347569</v>
@@ -42100,7 +42100,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1439" t="n">
-        <v>8.40025997161865</v>
+        <v>8.40025901794434</v>
       </c>
       <c r="H1439" t="n">
         <v>416421</v>
@@ -42129,7 +42129,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.40937042236328</v>
+        <v>8.4093713760376</v>
       </c>
       <c r="H1440" t="n">
         <v>524582</v>
@@ -42158,7 +42158,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1441" t="n">
-        <v>8.53692245483398</v>
+        <v>8.5369234085083</v>
       </c>
       <c r="H1441" t="n">
         <v>134841</v>
@@ -42303,7 +42303,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1446" t="n">
-        <v>8.51870155334473</v>
+        <v>8.51870250701904</v>
       </c>
       <c r="H1446" t="n">
         <v>724510</v>
@@ -42361,7 +42361,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1448" t="n">
-        <v>8.30914974212646</v>
+        <v>8.30915069580078</v>
       </c>
       <c r="H1448" t="n">
         <v>406269</v>
@@ -42390,7 +42390,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1449" t="n">
-        <v>8.28181838989258</v>
+        <v>8.28181743621826</v>
       </c>
       <c r="H1449" t="n">
         <v>212676</v>
@@ -42448,7 +42448,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1451" t="n">
-        <v>8.21804237365723</v>
+        <v>8.21804141998291</v>
       </c>
       <c r="H1451" t="n">
         <v>163363</v>
@@ -42477,7 +42477,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.21804237365723</v>
+        <v>8.21804141998291</v>
       </c>
       <c r="H1452" t="n">
         <v>158987</v>
@@ -42506,7 +42506,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.25448417663574</v>
+        <v>8.25448513031006</v>
       </c>
       <c r="H1453" t="n">
         <v>341657</v>
@@ -42564,7 +42564,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1455" t="n">
-        <v>8.31826114654541</v>
+        <v>8.31826210021973</v>
       </c>
       <c r="H1455" t="n">
         <v>455361</v>
@@ -42593,7 +42593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.51870155334473</v>
+        <v>8.51870250701904</v>
       </c>
       <c r="H1456" t="n">
         <v>358638</v>
@@ -42622,7 +42622,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1457" t="n">
-        <v>8.51870155334473</v>
+        <v>8.51870250701904</v>
       </c>
       <c r="H1457" t="n">
         <v>136998</v>
@@ -42738,7 +42738,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.27270698547363</v>
+        <v>8.27270603179932</v>
       </c>
       <c r="H1461" t="n">
         <v>206005</v>
@@ -42767,7 +42767,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.34559440612793</v>
+        <v>8.34559345245361</v>
       </c>
       <c r="H1462" t="n">
         <v>146931</v>
@@ -42796,7 +42796,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.33648204803467</v>
+        <v>8.33648300170898</v>
       </c>
       <c r="H1463" t="n">
         <v>97042</v>
@@ -42825,7 +42825,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.24537467956543</v>
+        <v>8.24537372589111</v>
       </c>
       <c r="H1464" t="n">
         <v>119102</v>
@@ -42854,7 +42854,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.38203811645508</v>
+        <v>8.38203716278076</v>
       </c>
       <c r="H1465" t="n">
         <v>194837</v>
@@ -42883,7 +42883,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.30003929138184</v>
+        <v>8.30004024505615</v>
       </c>
       <c r="H1466" t="n">
         <v>251320</v>
@@ -42912,7 +42912,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1467" t="n">
-        <v>8.45492362976074</v>
+        <v>8.45492458343506</v>
       </c>
       <c r="H1467" t="n">
         <v>160411</v>
@@ -42941,7 +42941,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.30914974212646</v>
+        <v>8.30915069580078</v>
       </c>
       <c r="H1468" t="n">
         <v>377007</v>
@@ -42970,7 +42970,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.30003929138184</v>
+        <v>8.30004024505615</v>
       </c>
       <c r="H1469" t="n">
         <v>137492</v>
@@ -42999,7 +42999,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.45492362976074</v>
+        <v>8.45492458343506</v>
       </c>
       <c r="H1470" t="n">
         <v>123877</v>
@@ -43028,7 +43028,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1471" t="n">
-        <v>8.56425476074219</v>
+        <v>8.5642557144165</v>
       </c>
       <c r="H1471" t="n">
         <v>135068</v>
@@ -43173,7 +43173,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.18379783630371</v>
+        <v>9.18379688262939</v>
       </c>
       <c r="H1476" t="n">
         <v>185092</v>
@@ -43231,7 +43231,7 @@
         <v>10</v>
       </c>
       <c r="G1478" t="n">
-        <v>9.11091041564941</v>
+        <v>9.11091136932373</v>
       </c>
       <c r="H1478" t="n">
         <v>369787</v>
@@ -43289,7 +43289,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.06535530090332</v>
+        <v>9.06535625457764</v>
       </c>
       <c r="H1480" t="n">
         <v>100398</v>
@@ -43550,7 +43550,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.5482349395752</v>
+        <v>9.54823398590088</v>
       </c>
       <c r="H1489" t="n">
         <v>390865</v>
@@ -43579,7 +43579,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.38423824310303</v>
+        <v>9.38423728942871</v>
       </c>
       <c r="H1490" t="n">
         <v>121808</v>
@@ -43637,7 +43637,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1492" t="n">
-        <v>9.29312896728516</v>
+        <v>9.29312801361084</v>
       </c>
       <c r="H1492" t="n">
         <v>126265</v>
@@ -43753,7 +43753,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.06535530090332</v>
+        <v>9.06535625457764</v>
       </c>
       <c r="H1496" t="n">
         <v>183051</v>
@@ -43811,7 +43811,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.87402629852295</v>
+        <v>8.87402534484863</v>
       </c>
       <c r="H1498" t="n">
         <v>250714</v>
@@ -43927,7 +43927,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.7100305557251</v>
+        <v>8.71003150939941</v>
       </c>
       <c r="H1502" t="n">
         <v>2119767</v>
@@ -43956,7 +43956,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.54603481292725</v>
+        <v>8.54603385925293</v>
       </c>
       <c r="H1503" t="n">
         <v>173808</v>
@@ -44043,7 +44043,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1506" t="n">
-        <v>8.87402629852295</v>
+        <v>8.87402534484863</v>
       </c>
       <c r="H1506" t="n">
         <v>135498</v>
@@ -44101,7 +44101,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>8.7100305557251</v>
+        <v>8.71003150939941</v>
       </c>
       <c r="H1508" t="n">
         <v>151592</v>
@@ -44130,7 +44130,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1509" t="n">
-        <v>8.76469421386719</v>
+        <v>8.76469612121582</v>
       </c>
       <c r="H1509" t="n">
         <v>411694</v>
@@ -44188,7 +44188,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G1511" t="n">
-        <v>8.864914894104</v>
+        <v>8.86491584777832</v>
       </c>
       <c r="H1511" t="n">
         <v>231856</v>
@@ -44217,7 +44217,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1512" t="n">
-        <v>8.87402629852295</v>
+        <v>8.87402534484863</v>
       </c>
       <c r="H1512" t="n">
         <v>159952</v>
@@ -44246,7 +44246,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G1513" t="n">
-        <v>8.864914894104</v>
+        <v>8.86491584777832</v>
       </c>
       <c r="H1513" t="n">
         <v>61970</v>
@@ -44275,7 +44275,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.72825336456299</v>
+        <v>8.72825145721436</v>
       </c>
       <c r="H1514" t="n">
         <v>339786</v>
@@ -44391,7 +44391,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>8.54603481292725</v>
+        <v>8.54603385925293</v>
       </c>
       <c r="H1518" t="n">
         <v>394587</v>
@@ -44420,7 +44420,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1519" t="n">
-        <v>8.52781295776367</v>
+        <v>8.52781200408936</v>
       </c>
       <c r="H1519" t="n">
         <v>321284</v>
@@ -44507,7 +44507,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>8.84669303894043</v>
+        <v>8.84669399261475</v>
       </c>
       <c r="H1522" t="n">
         <v>72417</v>
@@ -44536,7 +44536,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1523" t="n">
-        <v>8.97424793243408</v>
+        <v>8.97424697875977</v>
       </c>
       <c r="H1523" t="n">
         <v>76228</v>
@@ -44594,7 +44594,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1525" t="n">
-        <v>9.01980113983154</v>
+        <v>9.01980209350586</v>
       </c>
       <c r="H1525" t="n">
         <v>64850</v>
@@ -44623,7 +44623,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1526" t="n">
-        <v>9.04713344573975</v>
+        <v>9.04713439941406</v>
       </c>
       <c r="H1526" t="n">
         <v>112835</v>
@@ -44652,7 +44652,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1527" t="n">
-        <v>9.18379783630371</v>
+        <v>9.18379688262939</v>
       </c>
       <c r="H1527" t="n">
         <v>180585</v>
@@ -44739,7 +44739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.01980113983154</v>
+        <v>9.01980209350586</v>
       </c>
       <c r="H1530" t="n">
         <v>85340</v>
@@ -44884,7 +44884,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1535" t="n">
-        <v>8.72825336456299</v>
+        <v>8.72825145721436</v>
       </c>
       <c r="H1535" t="n">
         <v>89162</v>
@@ -44913,7 +44913,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1536" t="n">
-        <v>8.56425476074219</v>
+        <v>8.5642557144165</v>
       </c>
       <c r="H1536" t="n">
         <v>145214</v>
@@ -44971,7 +44971,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1538" t="n">
-        <v>8.51870155334473</v>
+        <v>8.51870250701904</v>
       </c>
       <c r="H1538" t="n">
         <v>169636</v>
@@ -45000,7 +45000,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1539" t="n">
-        <v>8.51870155334473</v>
+        <v>8.51870250701904</v>
       </c>
       <c r="H1539" t="n">
         <v>118856</v>
@@ -45058,7 +45058,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1541" t="n">
-        <v>8.46403694152832</v>
+        <v>8.464035987854</v>
       </c>
       <c r="H1541" t="n">
         <v>155449</v>
@@ -45145,7 +45145,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.13604164123535</v>
+        <v>8.13604259490967</v>
       </c>
       <c r="H1544" t="n">
         <v>455133</v>
@@ -45203,7 +45203,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1546" t="n">
-        <v>8.04493427276611</v>
+        <v>8.0449333190918</v>
       </c>
       <c r="H1546" t="n">
         <v>193972</v>
@@ -45261,7 +45261,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1548" t="n">
-        <v>8.30914974212646</v>
+        <v>8.30915069580078</v>
       </c>
       <c r="H1548" t="n">
         <v>215436</v>
@@ -45377,7 +45377,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1552" t="n">
-        <v>8.06315612792969</v>
+        <v>8.063157081604</v>
       </c>
       <c r="H1552" t="n">
         <v>254744</v>
@@ -45406,7 +45406,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1553" t="n">
-        <v>7.83538389205933</v>
+        <v>7.83538341522217</v>
       </c>
       <c r="H1553" t="n">
         <v>322116</v>
@@ -45435,7 +45435,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1554" t="n">
-        <v>8.00849056243896</v>
+        <v>8.00849151611328</v>
       </c>
       <c r="H1554" t="n">
         <v>209054</v>
@@ -45493,7 +45493,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1556" t="n">
-        <v>8.01760196685791</v>
+        <v>8.01760101318359</v>
       </c>
       <c r="H1556" t="n">
         <v>154101</v>
@@ -45522,7 +45522,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1557" t="n">
-        <v>8.072265625</v>
+        <v>8.07226657867432</v>
       </c>
       <c r="H1557" t="n">
         <v>388054</v>
@@ -45580,7 +45580,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1559" t="n">
-        <v>8.17248630523682</v>
+        <v>8.17248725891113</v>
       </c>
       <c r="H1559" t="n">
         <v>135145</v>
@@ -45609,7 +45609,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1560" t="n">
-        <v>8.05404376983643</v>
+        <v>8.05404567718506</v>
       </c>
       <c r="H1560" t="n">
         <v>132860</v>
@@ -45638,7 +45638,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1561" t="n">
-        <v>7.9447135925293</v>
+        <v>7.94471454620361</v>
       </c>
       <c r="H1561" t="n">
         <v>195649</v>
@@ -45667,7 +45667,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1562" t="n">
-        <v>7.83538389205933</v>
+        <v>7.83538341522217</v>
       </c>
       <c r="H1562" t="n">
         <v>245030</v>
@@ -45725,7 +45725,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1564" t="n">
-        <v>7.71694135665894</v>
+        <v>7.71694231033325</v>
       </c>
       <c r="H1564" t="n">
         <v>216207</v>
@@ -45754,7 +45754,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.54383325576782</v>
+        <v>7.54383373260498</v>
       </c>
       <c r="H1565" t="n">
         <v>318120</v>
@@ -45783,7 +45783,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>7.81716060638428</v>
+        <v>7.81716012954712</v>
       </c>
       <c r="H1566" t="n">
         <v>269154</v>
@@ -45841,7 +45841,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.77160692214966</v>
+        <v>7.7716064453125</v>
       </c>
       <c r="H1568" t="n">
         <v>253851</v>
@@ -45870,7 +45870,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1569" t="n">
-        <v>7.71694135665894</v>
+        <v>7.71694231033325</v>
       </c>
       <c r="H1569" t="n">
         <v>193334</v>
@@ -45899,7 +45899,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.54383325576782</v>
+        <v>7.54383373260498</v>
       </c>
       <c r="H1570" t="n">
         <v>223901</v>
@@ -45928,7 +45928,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.29783916473389</v>
+        <v>7.2978401184082</v>
       </c>
       <c r="H1571" t="n">
         <v>248691</v>
@@ -46015,7 +46015,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.53472375869751</v>
+        <v>7.53472328186035</v>
       </c>
       <c r="H1574" t="n">
         <v>211307</v>
@@ -46073,7 +46073,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>7.5984992980957</v>
+        <v>7.59850025177002</v>
       </c>
       <c r="H1576" t="n">
         <v>212331</v>
@@ -46102,7 +46102,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1577" t="n">
-        <v>7.67138767242432</v>
+        <v>7.67138671875</v>
       </c>
       <c r="H1577" t="n">
         <v>120281</v>
@@ -46131,7 +46131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.54383325576782</v>
+        <v>7.54383373260498</v>
       </c>
       <c r="H1578" t="n">
         <v>226208</v>
@@ -46218,7 +46218,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.89004850387573</v>
+        <v>7.89004802703857</v>
       </c>
       <c r="H1581" t="n">
         <v>380805</v>
@@ -46247,7 +46247,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.14515399932861</v>
+        <v>8.1451530456543</v>
       </c>
       <c r="H1582" t="n">
         <v>256482</v>
@@ -46305,7 +46305,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1584" t="n">
-        <v>8.21804237365723</v>
+        <v>8.21804141998291</v>
       </c>
       <c r="H1584" t="n">
         <v>194460</v>
@@ -46334,7 +46334,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1585" t="n">
-        <v>8.072265625</v>
+        <v>8.07226657867432</v>
       </c>
       <c r="H1585" t="n">
         <v>158695</v>
@@ -46363,7 +46363,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1586" t="n">
-        <v>8.13604164123535</v>
+        <v>8.13604259490967</v>
       </c>
       <c r="H1586" t="n">
         <v>108019</v>
@@ -46421,7 +46421,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1588" t="n">
-        <v>8.30914974212646</v>
+        <v>8.30915069580078</v>
       </c>
       <c r="H1588" t="n">
         <v>115304</v>
@@ -46479,7 +46479,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1590" t="n">
-        <v>8.19070816040039</v>
+        <v>8.19070911407471</v>
       </c>
       <c r="H1590" t="n">
         <v>147536</v>
@@ -46508,7 +46508,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1591" t="n">
-        <v>8.24537467956543</v>
+        <v>8.24537372589111</v>
       </c>
       <c r="H1591" t="n">
         <v>120042</v>
@@ -46566,7 +46566,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1593" t="n">
-        <v>8.27270698547363</v>
+        <v>8.27270603179932</v>
       </c>
       <c r="H1593" t="n">
         <v>189547</v>
@@ -46595,7 +46595,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1594" t="n">
-        <v>8.14515399932861</v>
+        <v>8.1451530456543</v>
       </c>
       <c r="H1594" t="n">
         <v>354494</v>
@@ -46624,7 +46624,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1595" t="n">
-        <v>8.1633768081665</v>
+        <v>8.16337585449219</v>
       </c>
       <c r="H1595" t="n">
         <v>197052</v>
@@ -46711,7 +46711,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1598" t="n">
-        <v>8.1633768081665</v>
+        <v>8.16337585449219</v>
       </c>
       <c r="H1598" t="n">
         <v>225715</v>
@@ -46827,7 +46827,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1602" t="n">
-        <v>8.21804237365723</v>
+        <v>8.21804141998291</v>
       </c>
       <c r="H1602" t="n">
         <v>195474</v>
@@ -46856,7 +46856,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>8.19070816040039</v>
+        <v>8.19070911407471</v>
       </c>
       <c r="H1603" t="n">
         <v>152256</v>
@@ -46914,7 +46914,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1605" t="n">
-        <v>7.88093662261963</v>
+        <v>7.88093757629395</v>
       </c>
       <c r="H1605" t="n">
         <v>98280</v>
@@ -46943,7 +46943,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>7.73516273498535</v>
+        <v>7.73516321182251</v>
       </c>
       <c r="H1606" t="n">
         <v>128898</v>
@@ -46972,7 +46972,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1607" t="n">
-        <v>7.72605180740356</v>
+        <v>7.72605228424072</v>
       </c>
       <c r="H1607" t="n">
         <v>155525</v>
@@ -47001,7 +47001,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.81716060638428</v>
+        <v>7.81716012954712</v>
       </c>
       <c r="H1608" t="n">
         <v>70123</v>
@@ -47030,7 +47030,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.9447135925293</v>
+        <v>7.94471454620361</v>
       </c>
       <c r="H1609" t="n">
         <v>161749</v>
@@ -47117,7 +47117,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.81716060638428</v>
+        <v>7.81716012954712</v>
       </c>
       <c r="H1612" t="n">
         <v>82555</v>
@@ -47146,7 +47146,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.75338554382324</v>
+        <v>7.75338506698608</v>
       </c>
       <c r="H1613" t="n">
         <v>94135</v>
@@ -47175,7 +47175,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1614" t="n">
-        <v>7.54383325576782</v>
+        <v>7.54383373260498</v>
       </c>
       <c r="H1614" t="n">
         <v>251105</v>
@@ -47233,7 +47233,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.41628217697144</v>
+        <v>7.41628170013428</v>
       </c>
       <c r="H1616" t="n">
         <v>99243</v>
@@ -47407,7 +47407,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.55294513702393</v>
+        <v>7.55294466018677</v>
       </c>
       <c r="H1622" t="n">
         <v>122793</v>
@@ -47523,7 +47523,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1626" t="n">
-        <v>7.71864223480225</v>
+        <v>7.7186427116394</v>
       </c>
       <c r="H1626" t="n">
         <v>77842</v>
@@ -47639,7 +47639,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G1630" t="n">
-        <v>7.96792888641357</v>
+        <v>7.96792984008789</v>
       </c>
       <c r="H1630" t="n">
         <v>66372</v>
@@ -47668,7 +47668,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1631" t="n">
-        <v>7.76480722427368</v>
+        <v>7.76480627059937</v>
       </c>
       <c r="H1631" t="n">
         <v>326667</v>
@@ -47697,7 +47697,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1632" t="n">
-        <v>7.64478015899658</v>
+        <v>7.64477968215942</v>
       </c>
       <c r="H1632" t="n">
         <v>148291</v>
@@ -47726,7 +47726,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1633" t="n">
-        <v>7.79250431060791</v>
+        <v>7.79250383377075</v>
       </c>
       <c r="H1633" t="n">
         <v>38210</v>
@@ -47755,7 +47755,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1634" t="n">
-        <v>7.64478015899658</v>
+        <v>7.64477968215942</v>
       </c>
       <c r="H1634" t="n">
         <v>45471</v>
@@ -47813,7 +47813,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1636" t="n">
-        <v>7.57091760635376</v>
+        <v>7.5709171295166</v>
       </c>
       <c r="H1636" t="n">
         <v>79344</v>
@@ -47871,7 +47871,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1638" t="n">
-        <v>7.48782205581665</v>
+        <v>7.48782157897949</v>
       </c>
       <c r="H1638" t="n">
         <v>152037</v>
@@ -47900,7 +47900,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1639" t="n">
-        <v>7.18313884735107</v>
+        <v>7.18313932418823</v>
       </c>
       <c r="H1639" t="n">
         <v>255431</v>
@@ -48045,7 +48045,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1644" t="n">
-        <v>6.81382608413696</v>
+        <v>6.8138256072998</v>
       </c>
       <c r="H1644" t="n">
         <v>200637</v>
@@ -48103,7 +48103,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1646" t="n">
-        <v>6.76766157150269</v>
+        <v>6.76766204833984</v>
       </c>
       <c r="H1646" t="n">
         <v>118308</v>
@@ -48248,7 +48248,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1651" t="n">
-        <v>6.91538667678833</v>
+        <v>6.91538715362549</v>
       </c>
       <c r="H1651" t="n">
         <v>117299</v>
@@ -48277,7 +48277,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1652" t="n">
-        <v>6.80459308624268</v>
+        <v>6.80459260940552</v>
       </c>
       <c r="H1652" t="n">
         <v>119463</v>
@@ -48306,7 +48306,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1653" t="n">
-        <v>6.76766157150269</v>
+        <v>6.76766204833984</v>
       </c>
       <c r="H1653" t="n">
         <v>161842</v>
@@ -48335,7 +48335,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1654" t="n">
-        <v>6.74919605255127</v>
+        <v>6.74919557571411</v>
       </c>
       <c r="H1654" t="n">
         <v>47222</v>
@@ -48364,7 +48364,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1655" t="n">
-        <v>6.80459308624268</v>
+        <v>6.80459260940552</v>
       </c>
       <c r="H1655" t="n">
         <v>59825</v>
@@ -48422,7 +48422,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1657" t="n">
-        <v>6.9061541557312</v>
+        <v>6.90615367889404</v>
       </c>
       <c r="H1657" t="n">
         <v>144650</v>
@@ -48451,7 +48451,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1658" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1658" t="n">
         <v>70414</v>
@@ -48625,7 +48625,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1664" t="n">
-        <v>6.81382608413696</v>
+        <v>6.8138256072998</v>
       </c>
       <c r="H1664" t="n">
         <v>37504</v>
@@ -48654,7 +48654,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1665" t="n">
-        <v>6.95231771469116</v>
+        <v>6.95231819152832</v>
       </c>
       <c r="H1665" t="n">
         <v>50409</v>
@@ -48683,7 +48683,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1666" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1666" t="n">
         <v>28495</v>
@@ -48712,7 +48712,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1667" t="n">
-        <v>7.05387926101685</v>
+        <v>7.05387878417969</v>
       </c>
       <c r="H1667" t="n">
         <v>71023</v>
@@ -48741,7 +48741,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1668" t="n">
-        <v>7.09080982208252</v>
+        <v>7.09081029891968</v>
       </c>
       <c r="H1668" t="n">
         <v>303233</v>
@@ -48770,7 +48770,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1669" t="n">
-        <v>7.16467380523682</v>
+        <v>7.16467332839966</v>
       </c>
       <c r="H1669" t="n">
         <v>50413</v>
@@ -48857,7 +48857,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1672" t="n">
-        <v>7.1923713684082</v>
+        <v>7.19237184524536</v>
       </c>
       <c r="H1672" t="n">
         <v>54016</v>
@@ -48886,7 +48886,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1673" t="n">
-        <v>7.1923713684082</v>
+        <v>7.19237184524536</v>
       </c>
       <c r="H1673" t="n">
         <v>120379</v>
@@ -48973,7 +48973,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1676" t="n">
-        <v>7.37702798843384</v>
+        <v>7.37702751159668</v>
       </c>
       <c r="H1676" t="n">
         <v>84329</v>
@@ -49002,7 +49002,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1677" t="n">
-        <v>7.52475309371948</v>
+        <v>7.52475261688232</v>
       </c>
       <c r="H1677" t="n">
         <v>43537</v>
@@ -49031,7 +49031,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1678" t="n">
-        <v>7.53398561477661</v>
+        <v>7.53398609161377</v>
       </c>
       <c r="H1678" t="n">
         <v>37685</v>
@@ -49089,7 +49089,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1680" t="n">
-        <v>7.55245161056519</v>
+        <v>7.5524525642395</v>
       </c>
       <c r="H1680" t="n">
         <v>78379</v>
@@ -49118,7 +49118,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1681" t="n">
-        <v>7.39549350738525</v>
+        <v>7.39549398422241</v>
       </c>
       <c r="H1681" t="n">
         <v>73218</v>
@@ -49234,7 +49234,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1685" t="n">
-        <v>7.78327322006226</v>
+        <v>7.78327226638794</v>
       </c>
       <c r="H1685" t="n">
         <v>73086</v>
@@ -49292,7 +49292,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1687" t="n">
-        <v>7.64478015899658</v>
+        <v>7.64477968215942</v>
       </c>
       <c r="H1687" t="n">
         <v>19957</v>
@@ -49466,7 +49466,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1693" t="n">
-        <v>7.16467380523682</v>
+        <v>7.16467332839966</v>
       </c>
       <c r="H1693" t="n">
         <v>47478</v>
@@ -49495,7 +49495,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1694" t="n">
-        <v>7.05387926101685</v>
+        <v>7.05387878417969</v>
       </c>
       <c r="H1694" t="n">
         <v>80014</v>
@@ -49553,7 +49553,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1696" t="n">
-        <v>7.12774133682251</v>
+        <v>7.12774181365967</v>
       </c>
       <c r="H1696" t="n">
         <v>100644</v>
@@ -49582,7 +49582,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1697" t="n">
-        <v>7.05387926101685</v>
+        <v>7.05387878417969</v>
       </c>
       <c r="H1697" t="n">
         <v>69152</v>
@@ -49611,7 +49611,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1698" t="n">
-        <v>7.17390584945679</v>
+        <v>7.17390537261963</v>
       </c>
       <c r="H1698" t="n">
         <v>82264</v>
@@ -49669,7 +49669,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G1700" t="n">
-        <v>6.84152364730835</v>
+        <v>6.84152412414551</v>
       </c>
       <c r="H1700" t="n">
         <v>75511</v>
@@ -49901,7 +49901,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1708" t="n">
-        <v>6.61993598937988</v>
+        <v>6.61993646621704</v>
       </c>
       <c r="H1708" t="n">
         <v>119132</v>
@@ -49930,7 +49930,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1709" t="n">
-        <v>6.57377243041992</v>
+        <v>6.57377195358276</v>
       </c>
       <c r="H1709" t="n">
         <v>137619</v>
@@ -49959,7 +49959,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1710" t="n">
-        <v>6.45374488830566</v>
+        <v>6.45374536514282</v>
       </c>
       <c r="H1710" t="n">
         <v>132896</v>
@@ -50104,7 +50104,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1715" t="n">
-        <v>6.13982963562012</v>
+        <v>6.13982915878296</v>
       </c>
       <c r="H1715" t="n">
         <v>201572</v>
@@ -50133,7 +50133,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>6.13982963562012</v>
+        <v>6.13982915878296</v>
       </c>
       <c r="H1716" t="n">
         <v>271324</v>
@@ -50220,7 +50220,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1719" t="n">
-        <v>6.12136363983154</v>
+        <v>6.1213641166687</v>
       </c>
       <c r="H1719" t="n">
         <v>169308</v>
@@ -50249,7 +50249,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1720" t="n">
-        <v>6.32448625564575</v>
+        <v>6.32448577880859</v>
       </c>
       <c r="H1720" t="n">
         <v>200528</v>
@@ -50278,7 +50278,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1721" t="n">
-        <v>6.24139070510864</v>
+        <v>6.2413911819458</v>
       </c>
       <c r="H1721" t="n">
         <v>196636</v>
@@ -50365,7 +50365,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1724" t="n">
-        <v>5.94593954086304</v>
+        <v>5.9459400177002</v>
       </c>
       <c r="H1724" t="n">
         <v>166343</v>
@@ -50423,7 +50423,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1726" t="n">
-        <v>5.82591342926025</v>
+        <v>5.8259129524231</v>
       </c>
       <c r="H1726" t="n">
         <v>175016</v>
@@ -50481,7 +50481,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1728" t="n">
-        <v>6.06596660614014</v>
+        <v>6.06596708297729</v>
       </c>
       <c r="H1728" t="n">
         <v>175096</v>
@@ -50568,7 +50568,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1731" t="n">
-        <v>6.37065029144287</v>
+        <v>6.37064981460571</v>
       </c>
       <c r="H1731" t="n">
         <v>105594</v>
@@ -50626,7 +50626,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1733" t="n">
-        <v>6.51837539672852</v>
+        <v>6.51837491989136</v>
       </c>
       <c r="H1733" t="n">
         <v>155299</v>
@@ -50800,7 +50800,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>6.57377243041992</v>
+        <v>6.57377195358276</v>
       </c>
       <c r="H1739" t="n">
         <v>101140</v>
@@ -51032,7 +51032,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1747" t="n">
-        <v>6.98924970626831</v>
+        <v>6.98924922943115</v>
       </c>
       <c r="H1747" t="n">
         <v>307572</v>
@@ -51177,7 +51177,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1752" t="n">
-        <v>6.83229207992554</v>
+        <v>6.83229160308838</v>
       </c>
       <c r="H1752" t="n">
         <v>80568</v>
@@ -51293,7 +51293,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1756" t="n">
-        <v>7.12774133682251</v>
+        <v>7.12774181365967</v>
       </c>
       <c r="H1756" t="n">
         <v>99125</v>
@@ -51496,7 +51496,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1763" t="n">
         <v>87911</v>
@@ -51525,7 +51525,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1764" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1764" t="n">
         <v>125001</v>
@@ -51554,7 +51554,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1765" t="n">
-        <v>6.80459308624268</v>
+        <v>6.80459260940552</v>
       </c>
       <c r="H1765" t="n">
         <v>128051</v>
@@ -51641,7 +51641,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1768" t="n">
-        <v>6.83229207992554</v>
+        <v>6.83229160308838</v>
       </c>
       <c r="H1768" t="n">
         <v>56524</v>
@@ -51670,7 +51670,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1769" t="n">
-        <v>6.80459308624268</v>
+        <v>6.80459260940552</v>
       </c>
       <c r="H1769" t="n">
         <v>42108</v>
@@ -51786,7 +51786,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1773" t="n">
-        <v>6.80459308624268</v>
+        <v>6.80459260940552</v>
       </c>
       <c r="H1773" t="n">
         <v>159839</v>
@@ -51815,7 +51815,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1774" t="n">
-        <v>6.6107029914856</v>
+        <v>6.61070346832275</v>
       </c>
       <c r="H1774" t="n">
         <v>104855</v>
@@ -51931,7 +51931,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>6.63840198516846</v>
+        <v>6.6384015083313</v>
       </c>
       <c r="H1778" t="n">
         <v>36191</v>
@@ -51960,7 +51960,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1779" t="n">
-        <v>6.74919605255127</v>
+        <v>6.74919557571411</v>
       </c>
       <c r="H1779" t="n">
         <v>95186</v>
@@ -51989,7 +51989,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1780" t="n">
-        <v>6.67533349990845</v>
+        <v>6.67533302307129</v>
       </c>
       <c r="H1780" t="n">
         <v>39774</v>
@@ -52018,7 +52018,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1781" t="n">
-        <v>6.74919605255127</v>
+        <v>6.74919557571411</v>
       </c>
       <c r="H1781" t="n">
         <v>36982</v>
@@ -52047,7 +52047,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1782" t="n">
-        <v>6.74919605255127</v>
+        <v>6.74919557571411</v>
       </c>
       <c r="H1782" t="n">
         <v>89075</v>
@@ -52134,7 +52134,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1785" t="n">
-        <v>6.91538667678833</v>
+        <v>6.91538715362549</v>
       </c>
       <c r="H1785" t="n">
         <v>87234</v>
@@ -52221,7 +52221,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1788" t="n">
-        <v>6.95231771469116</v>
+        <v>6.95231819152832</v>
       </c>
       <c r="H1788" t="n">
         <v>188360</v>
@@ -52337,7 +52337,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1792" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1792" t="n">
         <v>126294</v>
@@ -52366,7 +52366,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1793" t="n">
-        <v>7.12774133682251</v>
+        <v>7.12774181365967</v>
       </c>
       <c r="H1793" t="n">
         <v>112165</v>
@@ -52395,7 +52395,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1794" t="n">
-        <v>7.09080982208252</v>
+        <v>7.09081029891968</v>
       </c>
       <c r="H1794" t="n">
         <v>114971</v>
@@ -52424,7 +52424,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1795" t="n">
-        <v>7.23853588104248</v>
+        <v>7.23853635787964</v>
       </c>
       <c r="H1795" t="n">
         <v>208751</v>
@@ -52453,7 +52453,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1796" t="n">
-        <v>7.09080982208252</v>
+        <v>7.09081029891968</v>
       </c>
       <c r="H1796" t="n">
         <v>120585</v>
@@ -52482,7 +52482,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1797" t="n">
-        <v>7.22007036209106</v>
+        <v>7.22006988525391</v>
       </c>
       <c r="H1797" t="n">
         <v>194450</v>
@@ -52569,7 +52569,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1800" t="n">
-        <v>7.16467380523682</v>
+        <v>7.16467332839966</v>
       </c>
       <c r="H1800" t="n">
         <v>110050</v>
@@ -52598,7 +52598,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1801" t="n">
-        <v>7.1923713684082</v>
+        <v>7.19237184524536</v>
       </c>
       <c r="H1801" t="n">
         <v>65149</v>
@@ -52656,7 +52656,7 @@
         <v>7.75</v>
       </c>
       <c r="G1803" t="n">
-        <v>7.15544080734253</v>
+        <v>7.15544033050537</v>
       </c>
       <c r="H1803" t="n">
         <v>147844</v>
@@ -52685,7 +52685,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G1804" t="n">
-        <v>7.04464673995972</v>
+        <v>7.04464626312256</v>
       </c>
       <c r="H1804" t="n">
         <v>246735</v>
@@ -52743,7 +52743,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1806" t="n">
-        <v>7.57091760635376</v>
+        <v>7.5709171295166</v>
       </c>
       <c r="H1806" t="n">
         <v>507297</v>
@@ -52917,7 +52917,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>7.24776840209961</v>
+        <v>7.24776887893677</v>
       </c>
       <c r="H1812" t="n">
         <v>161690</v>
@@ -53033,7 +53033,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.33086442947388</v>
+        <v>7.33086395263672</v>
       </c>
       <c r="H1816" t="n">
         <v>126757</v>
@@ -53062,7 +53062,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>7.1923713684082</v>
+        <v>7.19237184524536</v>
       </c>
       <c r="H1817" t="n">
         <v>221621</v>
@@ -53091,7 +53091,7 @@
         <v>7.75</v>
       </c>
       <c r="G1818" t="n">
-        <v>7.15544080734253</v>
+        <v>7.15544033050537</v>
       </c>
       <c r="H1818" t="n">
         <v>136367</v>
@@ -53236,7 +53236,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1823" t="n">
-        <v>7.05387926101685</v>
+        <v>7.05387878417969</v>
       </c>
       <c r="H1823" t="n">
         <v>160216</v>
@@ -53265,7 +53265,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.08157777786255</v>
+        <v>7.08157825469971</v>
       </c>
       <c r="H1824" t="n">
         <v>208764</v>
@@ -53352,7 +53352,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1827" t="n">
-        <v>7.16467380523682</v>
+        <v>7.16467332839966</v>
       </c>
       <c r="H1827" t="n">
         <v>122877</v>
@@ -53381,7 +53381,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1828" t="n">
-        <v>7.22007036209106</v>
+        <v>7.22006988525391</v>
       </c>
       <c r="H1828" t="n">
         <v>148599</v>
@@ -53410,7 +53410,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1829" t="n">
-        <v>7.18313884735107</v>
+        <v>7.18313932418823</v>
       </c>
       <c r="H1829" t="n">
         <v>85547</v>
@@ -53468,7 +53468,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1831" t="n">
-        <v>7.08157777786255</v>
+        <v>7.08157825469971</v>
       </c>
       <c r="H1831" t="n">
         <v>123418</v>
@@ -53526,7 +53526,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1833" t="n">
-        <v>6.63840198516846</v>
+        <v>6.6384015083313</v>
       </c>
       <c r="H1833" t="n">
         <v>318516</v>
@@ -53555,7 +53555,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>6.77689456939697</v>
+        <v>6.77689504623413</v>
       </c>
       <c r="H1834" t="n">
         <v>253413</v>
@@ -53642,7 +53642,7 @@
         <v>7.25</v>
       </c>
       <c r="G1837" t="n">
-        <v>6.69379901885986</v>
+        <v>6.69379854202271</v>
       </c>
       <c r="H1837" t="n">
         <v>321670</v>
@@ -53758,7 +53758,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1841" t="n">
-        <v>7.8109712600708</v>
+        <v>7.81097173690796</v>
       </c>
       <c r="H1841" t="n">
         <v>260403</v>
@@ -53787,7 +53787,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1842" t="n">
-        <v>7.63554716110229</v>
+        <v>7.63554763793945</v>
       </c>
       <c r="H1842" t="n">
         <v>434363</v>
@@ -53816,7 +53816,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1843" t="n">
-        <v>7.66324615478516</v>
+        <v>7.663245677948</v>
       </c>
       <c r="H1843" t="n">
         <v>199081</v>
@@ -53845,7 +53845,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1844" t="n">
-        <v>7.52475309371948</v>
+        <v>7.52475261688232</v>
       </c>
       <c r="H1844" t="n">
         <v>254149</v>
@@ -53903,7 +53903,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1846" t="n">
-        <v>7.8109712600708</v>
+        <v>7.81097173690796</v>
       </c>
       <c r="H1846" t="n">
         <v>168597</v>
@@ -53932,7 +53932,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1847" t="n">
-        <v>7.66324615478516</v>
+        <v>7.663245677948</v>
       </c>
       <c r="H1847" t="n">
         <v>172426</v>
@@ -54019,7 +54019,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1850" t="n">
-        <v>7.64478015899658</v>
+        <v>7.64477968215942</v>
       </c>
       <c r="H1850" t="n">
         <v>215705</v>
@@ -54135,7 +54135,7 @@
         <v>8.5</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.84790182113647</v>
+        <v>7.84790229797363</v>
       </c>
       <c r="H1854" t="n">
         <v>101123</v>
@@ -54164,7 +54164,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.83866882324219</v>
+        <v>7.8386697769165</v>
       </c>
       <c r="H1855" t="n">
         <v>262205</v>
@@ -54193,7 +54193,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1856" t="n">
-        <v>7.79250431060791</v>
+        <v>7.79250383377075</v>
       </c>
       <c r="H1856" t="n">
         <v>132667</v>
@@ -54222,7 +54222,7 @@
         <v>8.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.84790182113647</v>
+        <v>7.84790229797363</v>
       </c>
       <c r="H1857" t="n">
         <v>115325</v>
@@ -54251,7 +54251,7 @@
         <v>8.5</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.84790182113647</v>
+        <v>7.84790229797363</v>
       </c>
       <c r="H1858" t="n">
         <v>103601</v>
@@ -54338,7 +54338,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1861" t="n">
-        <v>7.83866882324219</v>
+        <v>7.8386697769165</v>
       </c>
       <c r="H1861" t="n">
         <v>63582</v>
@@ -54367,7 +54367,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1862" t="n">
-        <v>7.76480722427368</v>
+        <v>7.76480627059937</v>
       </c>
       <c r="H1862" t="n">
         <v>73408</v>
@@ -54454,7 +54454,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1865" t="n">
-        <v>7.98639345169067</v>
+        <v>7.98639440536499</v>
       </c>
       <c r="H1865" t="n">
         <v>191892</v>
@@ -54483,7 +54483,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1866" t="n">
-        <v>8.12488651275635</v>
+        <v>8.12488746643066</v>
       </c>
       <c r="H1866" t="n">
         <v>325771</v>
@@ -54831,7 +54831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1878" t="n">
-        <v>8.12488651275635</v>
+        <v>8.12488746643066</v>
       </c>
       <c r="H1878" t="n">
         <v>133688</v>
@@ -54860,7 +54860,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1879" t="n">
-        <v>8.26337909698486</v>
+        <v>8.26337814331055</v>
       </c>
       <c r="H1879" t="n">
         <v>193592</v>
@@ -54918,7 +54918,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1881" t="n">
-        <v>8.26337909698486</v>
+        <v>8.26337814331055</v>
       </c>
       <c r="H1881" t="n">
         <v>163910</v>
@@ -54947,7 +54947,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1882" t="n">
-        <v>8.15258598327637</v>
+        <v>8.15258502960205</v>
       </c>
       <c r="H1882" t="n">
         <v>264348</v>
@@ -54976,7 +54976,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1883" t="n">
-        <v>8.17105102539062</v>
+        <v>8.17105197906494</v>
       </c>
       <c r="H1883" t="n">
         <v>61130</v>
@@ -55005,7 +55005,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1884" t="n">
-        <v>8.26337909698486</v>
+        <v>8.26337814331055</v>
       </c>
       <c r="H1884" t="n">
         <v>84127</v>
@@ -55063,7 +55063,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1886" t="n">
-        <v>8.23568153381348</v>
+        <v>8.23568058013916</v>
       </c>
       <c r="H1886" t="n">
         <v>224429</v>
@@ -55121,7 +55121,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1888" t="n">
-        <v>8.21721458435059</v>
+        <v>8.2172155380249</v>
       </c>
       <c r="H1888" t="n">
         <v>123441</v>
@@ -55179,7 +55179,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1890" t="n">
-        <v>8.23568153381348</v>
+        <v>8.23568058013916</v>
       </c>
       <c r="H1890" t="n">
         <v>130824</v>
@@ -55208,7 +55208,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H1891" t="n">
         <v>98296</v>
@@ -55295,7 +55295,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1894" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H1894" t="n">
         <v>65526</v>
@@ -55440,7 +55440,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1899" t="n">
-        <v>8.65115737915039</v>
+        <v>8.65115833282471</v>
       </c>
       <c r="H1899" t="n">
         <v>248917</v>
@@ -80067,6 +80067,35 @@
         <v>188902</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>8.67000007629395</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>8.6899995803833</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>8.6899995803833</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>214345</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TIP.MI.xlsx
+++ b/data/TIP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G2" t="n">
-        <v>2.77823376655579</v>
+        <v>2.77823328971863</v>
       </c>
       <c r="H2" t="n">
         <v>152343</v>
@@ -456,7 +456,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G3" t="n">
-        <v>2.77991271018982</v>
+        <v>2.77991318702698</v>
       </c>
       <c r="H3" t="n">
         <v>45654</v>
@@ -543,7 +543,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66233348846436</v>
+        <v>2.66233396530151</v>
       </c>
       <c r="H6" t="n">
         <v>101924</v>
@@ -601,7 +601,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66233348846436</v>
+        <v>2.66233396530151</v>
       </c>
       <c r="H8" t="n">
         <v>67534</v>
@@ -630,7 +630,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68249011039734</v>
+        <v>2.68248987197876</v>
       </c>
       <c r="H9" t="n">
         <v>47799</v>
@@ -775,7 +775,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G14" t="n">
-        <v>2.40197920799255</v>
+        <v>2.40197896957397</v>
       </c>
       <c r="H14" t="n">
         <v>250168</v>
@@ -804,7 +804,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G15" t="n">
-        <v>2.49604249000549</v>
+        <v>2.49604225158691</v>
       </c>
       <c r="H15" t="n">
         <v>236506</v>
@@ -833,7 +833,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6203408241272</v>
+        <v>2.62034106254578</v>
       </c>
       <c r="H16" t="n">
         <v>247530</v>
@@ -862,7 +862,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G17" t="n">
-        <v>2.55483222007751</v>
+        <v>2.55483245849609</v>
       </c>
       <c r="H17" t="n">
         <v>111221</v>
@@ -891,7 +891,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G18" t="n">
-        <v>2.56994986534119</v>
+        <v>2.56994962692261</v>
       </c>
       <c r="H18" t="n">
         <v>86548</v>
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51955890655518</v>
+        <v>2.51955819129944</v>
       </c>
       <c r="H20" t="n">
         <v>71539</v>
@@ -978,7 +978,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5296368598938</v>
+        <v>2.52963709831238</v>
       </c>
       <c r="H21" t="n">
         <v>56267</v>
@@ -1036,7 +1036,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48764443397522</v>
+        <v>2.48764419555664</v>
       </c>
       <c r="H23" t="n">
         <v>72870</v>
@@ -1065,7 +1065,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G24" t="n">
-        <v>2.44061255455017</v>
+        <v>2.44061231613159</v>
       </c>
       <c r="H24" t="n">
         <v>176081</v>
@@ -1094,7 +1094,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G25" t="n">
-        <v>2.44397139549255</v>
+        <v>2.44397187232971</v>
       </c>
       <c r="H25" t="n">
         <v>105192</v>
@@ -1123,7 +1123,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G26" t="n">
-        <v>2.42717480659485</v>
+        <v>2.42717504501343</v>
       </c>
       <c r="H26" t="n">
         <v>93464</v>
@@ -1152,7 +1152,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22560977935791</v>
+        <v>2.22561025619507</v>
       </c>
       <c r="H27" t="n">
         <v>529181</v>
@@ -1181,7 +1181,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G28" t="n">
-        <v>2.17521905899048</v>
+        <v>2.1752188205719</v>
       </c>
       <c r="H28" t="n">
         <v>493129</v>
@@ -1210,7 +1210,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20041418075562</v>
+        <v>2.20041441917419</v>
       </c>
       <c r="H29" t="n">
         <v>154588</v>
@@ -1268,7 +1268,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G31" t="n">
-        <v>2.21049308776855</v>
+        <v>2.2104926109314</v>
       </c>
       <c r="H31" t="n">
         <v>93450</v>
@@ -1297,7 +1297,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G32" t="n">
-        <v>2.31463432312012</v>
+        <v>2.31463408470154</v>
       </c>
       <c r="H32" t="n">
         <v>95609</v>
@@ -1326,7 +1326,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>2.33311152458191</v>
+        <v>2.33311128616333</v>
       </c>
       <c r="H33" t="n">
         <v>134932</v>
@@ -1355,7 +1355,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45237040519714</v>
+        <v>2.45237064361572</v>
       </c>
       <c r="H34" t="n">
         <v>111775</v>
@@ -1413,7 +1413,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>2.50276136398315</v>
+        <v>2.50276184082031</v>
       </c>
       <c r="H36" t="n">
         <v>50466</v>
@@ -1500,7 +1500,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>2.41205739974976</v>
+        <v>2.41205716133118</v>
       </c>
       <c r="H39" t="n">
         <v>479838</v>
@@ -1529,7 +1529,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G40" t="n">
-        <v>2.56827044487</v>
+        <v>2.56826996803284</v>
       </c>
       <c r="H40" t="n">
         <v>281502</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.51955890655518</v>
+        <v>2.51955819129944</v>
       </c>
       <c r="H41" t="n">
         <v>243349</v>
@@ -1587,7 +1587,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G42" t="n">
-        <v>2.53971529006958</v>
+        <v>2.53971481323242</v>
       </c>
       <c r="H42" t="n">
         <v>123602</v>
@@ -1616,7 +1616,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G43" t="n">
-        <v>2.59178638458252</v>
+        <v>2.59178614616394</v>
       </c>
       <c r="H43" t="n">
         <v>130900</v>
@@ -1645,7 +1645,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G44" t="n">
-        <v>2.54979348182678</v>
+        <v>2.54979372024536</v>
       </c>
       <c r="H44" t="n">
         <v>121100</v>
@@ -1674,7 +1674,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G45" t="n">
-        <v>2.59178638458252</v>
+        <v>2.59178614616394</v>
       </c>
       <c r="H45" t="n">
         <v>107783</v>
@@ -1703,7 +1703,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>2.54979348182678</v>
+        <v>2.54979372024536</v>
       </c>
       <c r="H46" t="n">
         <v>126208</v>
@@ -1732,7 +1732,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G47" t="n">
-        <v>2.56659078598022</v>
+        <v>2.56659030914307</v>
       </c>
       <c r="H47" t="n">
         <v>91697</v>
@@ -1761,7 +1761,7 @@
         <v>3.0239999294281</v>
       </c>
       <c r="G48" t="n">
-        <v>2.53971529006958</v>
+        <v>2.53971481323242</v>
       </c>
       <c r="H48" t="n">
         <v>18221</v>
@@ -1790,7 +1790,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G49" t="n">
-        <v>2.52795720100403</v>
+        <v>2.52795743942261</v>
       </c>
       <c r="H49" t="n">
         <v>39083</v>
@@ -1848,7 +1848,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G51" t="n">
-        <v>2.57666850090027</v>
+        <v>2.57666826248169</v>
       </c>
       <c r="H51" t="n">
         <v>72645</v>
@@ -1935,7 +1935,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G54" t="n">
-        <v>2.63713788986206</v>
+        <v>2.63713812828064</v>
       </c>
       <c r="H54" t="n">
         <v>77417</v>
@@ -1964,7 +1964,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G55" t="n">
-        <v>2.63713788986206</v>
+        <v>2.63713812828064</v>
       </c>
       <c r="H55" t="n">
         <v>165084</v>
@@ -1993,7 +1993,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G56" t="n">
-        <v>2.61194205284119</v>
+        <v>2.61194252967834</v>
       </c>
       <c r="H56" t="n">
         <v>79540</v>
@@ -2022,7 +2022,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G57" t="n">
-        <v>2.63881731033325</v>
+        <v>2.63881802558899</v>
       </c>
       <c r="H57" t="n">
         <v>56554</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.6203408241272</v>
+        <v>2.62034106254578</v>
       </c>
       <c r="H59" t="n">
         <v>244037</v>
@@ -2109,7 +2109,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G60" t="n">
-        <v>2.5632312297821</v>
+        <v>2.56323099136353</v>
       </c>
       <c r="H60" t="n">
         <v>42243</v>
@@ -2138,7 +2138,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G61" t="n">
-        <v>2.5632312297821</v>
+        <v>2.56323099136353</v>
       </c>
       <c r="H61" t="n">
         <v>22329</v>
@@ -2196,7 +2196,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G63" t="n">
-        <v>2.63209891319275</v>
+        <v>2.63209915161133</v>
       </c>
       <c r="H63" t="n">
         <v>31651</v>
@@ -2254,7 +2254,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>2.57834815979004</v>
+        <v>2.57834839820862</v>
       </c>
       <c r="H65" t="n">
         <v>118096</v>
@@ -2341,7 +2341,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G68" t="n">
-        <v>2.59010648727417</v>
+        <v>2.59010624885559</v>
       </c>
       <c r="H68" t="n">
         <v>75467</v>
@@ -2370,7 +2370,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G69" t="n">
-        <v>2.56827044487</v>
+        <v>2.56826996803284</v>
       </c>
       <c r="H69" t="n">
         <v>60387</v>
@@ -2486,7 +2486,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G73" t="n">
-        <v>2.66737294197083</v>
+        <v>2.66737246513367</v>
       </c>
       <c r="H73" t="n">
         <v>66614</v>
@@ -2515,7 +2515,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G74" t="n">
-        <v>2.66065359115601</v>
+        <v>2.66065430641174</v>
       </c>
       <c r="H74" t="n">
         <v>20828</v>
@@ -2544,7 +2544,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G75" t="n">
-        <v>2.63209891319275</v>
+        <v>2.63209915161133</v>
       </c>
       <c r="H75" t="n">
         <v>52279</v>
@@ -2602,7 +2602,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.67913103103638</v>
+        <v>2.67913031578064</v>
       </c>
       <c r="H77" t="n">
         <v>80578</v>
@@ -2631,7 +2631,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G78" t="n">
-        <v>2.63713788986206</v>
+        <v>2.63713812828064</v>
       </c>
       <c r="H78" t="n">
         <v>62187</v>
@@ -2660,7 +2660,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>2.60354328155518</v>
+        <v>2.60354399681091</v>
       </c>
       <c r="H79" t="n">
         <v>67023</v>
@@ -2689,7 +2689,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>2.60354328155518</v>
+        <v>2.60354399681091</v>
       </c>
       <c r="H80" t="n">
         <v>25508</v>
@@ -2747,7 +2747,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G82" t="n">
-        <v>2.61194205284119</v>
+        <v>2.61194252967834</v>
       </c>
       <c r="H82" t="n">
         <v>47197</v>
@@ -2805,7 +2805,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G84" t="n">
-        <v>2.63377809524536</v>
+        <v>2.63377833366394</v>
       </c>
       <c r="H84" t="n">
         <v>80921</v>
@@ -2834,7 +2834,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G85" t="n">
-        <v>2.59346580505371</v>
+        <v>2.59346604347229</v>
       </c>
       <c r="H85" t="n">
         <v>97052</v>
@@ -2863,7 +2863,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.56994986534119</v>
+        <v>2.56994962692261</v>
       </c>
       <c r="H86" t="n">
         <v>240688</v>
@@ -2892,7 +2892,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>2.56994986534119</v>
+        <v>2.56994962692261</v>
       </c>
       <c r="H87" t="n">
         <v>88160</v>
@@ -2921,7 +2921,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59010648727417</v>
+        <v>2.59010624885559</v>
       </c>
       <c r="H88" t="n">
         <v>31696</v>
@@ -2950,7 +2950,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G89" t="n">
-        <v>2.56491088867188</v>
+        <v>2.56491041183472</v>
       </c>
       <c r="H89" t="n">
         <v>41649</v>
@@ -3008,7 +3008,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G91" t="n">
-        <v>2.59682559967041</v>
+        <v>2.59682488441467</v>
       </c>
       <c r="H91" t="n">
         <v>56203</v>
@@ -3037,7 +3037,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G92" t="n">
-        <v>2.61194205284119</v>
+        <v>2.61194252967834</v>
       </c>
       <c r="H92" t="n">
         <v>177199</v>
@@ -3066,7 +3066,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G93" t="n">
-        <v>2.61194205284119</v>
+        <v>2.61194252967834</v>
       </c>
       <c r="H93" t="n">
         <v>159194</v>
@@ -3153,7 +3153,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G96" t="n">
-        <v>2.71608376502991</v>
+        <v>2.71608400344849</v>
       </c>
       <c r="H96" t="n">
         <v>128610</v>
@@ -3269,7 +3269,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>2.77151417732239</v>
+        <v>2.77151489257812</v>
       </c>
       <c r="H100" t="n">
         <v>212521</v>
@@ -3327,7 +3327,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>2.89581274986267</v>
+        <v>2.89581251144409</v>
       </c>
       <c r="H102" t="n">
         <v>232119</v>
@@ -3385,7 +3385,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G104" t="n">
-        <v>2.95460224151611</v>
+        <v>2.95460247993469</v>
       </c>
       <c r="H104" t="n">
         <v>202295</v>
@@ -3414,7 +3414,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>2.97425723075867</v>
+        <v>2.97425770759583</v>
       </c>
       <c r="H105" t="n">
         <v>77690</v>
@@ -3443,7 +3443,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G106" t="n">
-        <v>2.96571040153503</v>
+        <v>2.96571063995361</v>
       </c>
       <c r="H106" t="n">
         <v>150398</v>
@@ -3501,7 +3501,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G108" t="n">
-        <v>3.01699113845825</v>
+        <v>3.01699090003967</v>
       </c>
       <c r="H108" t="n">
         <v>89579</v>
@@ -3530,7 +3530,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G109" t="n">
-        <v>2.97938561439514</v>
+        <v>2.97938537597656</v>
       </c>
       <c r="H109" t="n">
         <v>62868</v>
@@ -3617,7 +3617,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>2.97425723075867</v>
+        <v>2.97425770759583</v>
       </c>
       <c r="H112" t="n">
         <v>75910</v>
@@ -3646,7 +3646,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>2.94690799713135</v>
+        <v>2.94690775871277</v>
       </c>
       <c r="H113" t="n">
         <v>31979</v>
@@ -3733,7 +3733,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G116" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H116" t="n">
         <v>111280</v>
@@ -3762,7 +3762,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G117" t="n">
-        <v>2.90588355064392</v>
+        <v>2.90588331222534</v>
       </c>
       <c r="H117" t="n">
         <v>61653</v>
@@ -3791,7 +3791,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G118" t="n">
-        <v>2.81186962127686</v>
+        <v>2.81186985969543</v>
       </c>
       <c r="H118" t="n">
         <v>99749</v>
@@ -3849,7 +3849,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G120" t="n">
-        <v>2.98451328277588</v>
+        <v>2.98451375961304</v>
       </c>
       <c r="H120" t="n">
         <v>174106</v>
@@ -3907,7 +3907,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.02553725242615</v>
+        <v>3.02553749084473</v>
       </c>
       <c r="H122" t="n">
         <v>240472</v>
@@ -3936,7 +3936,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G123" t="n">
-        <v>3.03921270370483</v>
+        <v>3.03921246528625</v>
       </c>
       <c r="H123" t="n">
         <v>125877</v>
@@ -3965,7 +3965,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G124" t="n">
-        <v>2.92981481552124</v>
+        <v>2.92981433868408</v>
       </c>
       <c r="H124" t="n">
         <v>268609</v>
@@ -4023,7 +4023,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G126" t="n">
-        <v>2.88195276260376</v>
+        <v>2.88195300102234</v>
       </c>
       <c r="H126" t="n">
         <v>123491</v>
@@ -4052,7 +4052,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G127" t="n">
-        <v>2.88878989219666</v>
+        <v>2.88879013061523</v>
       </c>
       <c r="H127" t="n">
         <v>47357</v>
@@ -4081,7 +4081,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G128" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H128" t="n">
         <v>47325</v>
@@ -4110,7 +4110,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G129" t="n">
-        <v>2.89220881462097</v>
+        <v>2.89220857620239</v>
       </c>
       <c r="H129" t="n">
         <v>68529</v>
@@ -4139,7 +4139,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G130" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H130" t="n">
         <v>8471</v>
@@ -4168,7 +4168,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G131" t="n">
-        <v>2.84605669975281</v>
+        <v>2.84605622291565</v>
       </c>
       <c r="H131" t="n">
         <v>18015</v>
@@ -4197,7 +4197,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G132" t="n">
-        <v>2.71785616874695</v>
+        <v>2.71785569190979</v>
       </c>
       <c r="H132" t="n">
         <v>69786</v>
@@ -4226,7 +4226,7 @@
         <v>3.25</v>
       </c>
       <c r="G133" t="n">
-        <v>2.77768301963806</v>
+        <v>2.77768278121948</v>
       </c>
       <c r="H133" t="n">
         <v>107042</v>
@@ -4255,7 +4255,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>2.82041621208191</v>
+        <v>2.82041692733765</v>
       </c>
       <c r="H134" t="n">
         <v>119119</v>
@@ -4313,7 +4313,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G136" t="n">
-        <v>2.82041621208191</v>
+        <v>2.82041692733765</v>
       </c>
       <c r="H136" t="n">
         <v>130246</v>
@@ -4371,7 +4371,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G138" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H138" t="n">
         <v>110344</v>
@@ -4400,7 +4400,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G139" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H139" t="n">
         <v>72008</v>
@@ -4429,7 +4429,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89220881462097</v>
+        <v>2.89220857620239</v>
       </c>
       <c r="H140" t="n">
         <v>44705</v>
@@ -4458,7 +4458,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>2.87169671058655</v>
+        <v>2.87169694900513</v>
       </c>
       <c r="H141" t="n">
         <v>131250</v>
@@ -4661,7 +4661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>3.01699113845825</v>
+        <v>3.01699090003967</v>
       </c>
       <c r="H148" t="n">
         <v>229996</v>
@@ -4777,7 +4777,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05972456932068</v>
+        <v>3.05972480773926</v>
       </c>
       <c r="H152" t="n">
         <v>38052</v>
@@ -4806,7 +4806,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>3.03408408164978</v>
+        <v>3.03408432006836</v>
       </c>
       <c r="H153" t="n">
         <v>70270</v>
@@ -4835,7 +4835,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G154" t="n">
-        <v>3.08707404136658</v>
+        <v>3.087073802948</v>
       </c>
       <c r="H154" t="n">
         <v>78818</v>
@@ -4864,7 +4864,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G155" t="n">
-        <v>3.12809872627258</v>
+        <v>3.12809824943542</v>
       </c>
       <c r="H155" t="n">
         <v>153076</v>
@@ -4893,7 +4893,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G156" t="n">
-        <v>3.17766880989075</v>
+        <v>3.17766952514648</v>
       </c>
       <c r="H156" t="n">
         <v>125694</v>
@@ -4922,7 +4922,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G157" t="n">
-        <v>3.17766880989075</v>
+        <v>3.17766952514648</v>
       </c>
       <c r="H157" t="n">
         <v>74677</v>
@@ -4951,7 +4951,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G158" t="n">
-        <v>3.16228556632996</v>
+        <v>3.16228532791138</v>
       </c>
       <c r="H158" t="n">
         <v>141495</v>
@@ -4980,7 +4980,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.16228556632996</v>
+        <v>3.16228532791138</v>
       </c>
       <c r="H159" t="n">
         <v>92789</v>
@@ -5038,7 +5038,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G161" t="n">
-        <v>3.12809872627258</v>
+        <v>3.12809824943542</v>
       </c>
       <c r="H161" t="n">
         <v>44019</v>
@@ -5067,7 +5067,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G162" t="n">
-        <v>3.17766880989075</v>
+        <v>3.17766952514648</v>
       </c>
       <c r="H162" t="n">
         <v>40904</v>
@@ -5096,7 +5096,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G163" t="n">
-        <v>3.16228556632996</v>
+        <v>3.16228532791138</v>
       </c>
       <c r="H163" t="n">
         <v>108272</v>
@@ -5125,7 +5125,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G164" t="n">
-        <v>3.19305324554443</v>
+        <v>3.19305372238159</v>
       </c>
       <c r="H164" t="n">
         <v>53423</v>
@@ -5154,7 +5154,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G165" t="n">
-        <v>3.129807472229</v>
+        <v>3.12980794906616</v>
       </c>
       <c r="H165" t="n">
         <v>249593</v>
@@ -5183,7 +5183,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>3.17425012588501</v>
+        <v>3.17425036430359</v>
       </c>
       <c r="H166" t="n">
         <v>53864</v>
@@ -5212,7 +5212,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G167" t="n">
-        <v>3.14348220825195</v>
+        <v>3.14348244667053</v>
       </c>
       <c r="H167" t="n">
         <v>26131</v>
@@ -5241,7 +5241,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G168" t="n">
-        <v>3.17937850952148</v>
+        <v>3.17937874794006</v>
       </c>
       <c r="H168" t="n">
         <v>10423</v>
@@ -5270,7 +5270,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>3.16228556632996</v>
+        <v>3.16228532791138</v>
       </c>
       <c r="H169" t="n">
         <v>60929</v>
@@ -5357,7 +5357,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G172" t="n">
-        <v>3.14348220825195</v>
+        <v>3.14348244667053</v>
       </c>
       <c r="H172" t="n">
         <v>83572</v>
@@ -5386,7 +5386,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G173" t="n">
-        <v>3.13664531707764</v>
+        <v>3.13664484024048</v>
       </c>
       <c r="H173" t="n">
         <v>40342</v>
@@ -5444,7 +5444,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G175" t="n">
-        <v>3.13835430145264</v>
+        <v>3.13835406303406</v>
       </c>
       <c r="H175" t="n">
         <v>58509</v>
@@ -5502,7 +5502,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G177" t="n">
-        <v>3.16228556632996</v>
+        <v>3.16228532791138</v>
       </c>
       <c r="H177" t="n">
         <v>92758</v>
@@ -5531,7 +5531,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G178" t="n">
-        <v>3.13322639465332</v>
+        <v>3.13322591781616</v>
       </c>
       <c r="H178" t="n">
         <v>32351</v>
@@ -5589,7 +5589,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G180" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H180" t="n">
         <v>50226</v>
@@ -5618,7 +5618,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G181" t="n">
-        <v>3.08707404136658</v>
+        <v>3.087073802948</v>
       </c>
       <c r="H181" t="n">
         <v>81429</v>
@@ -5647,7 +5647,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G182" t="n">
-        <v>3.12467908859253</v>
+        <v>3.12467932701111</v>
       </c>
       <c r="H182" t="n">
         <v>60780</v>
@@ -5676,7 +5676,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G183" t="n">
-        <v>3.07852745056152</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H183" t="n">
         <v>62479</v>
@@ -5705,7 +5705,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G184" t="n">
-        <v>3.09391140937805</v>
+        <v>3.09391164779663</v>
       </c>
       <c r="H184" t="n">
         <v>39134</v>
@@ -5734,7 +5734,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G185" t="n">
-        <v>3.08194613456726</v>
+        <v>3.08194637298584</v>
       </c>
       <c r="H185" t="n">
         <v>38222</v>
@@ -5792,7 +5792,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G187" t="n">
-        <v>3.10758638381958</v>
+        <v>3.107586145401</v>
       </c>
       <c r="H187" t="n">
         <v>53535</v>
@@ -5821,7 +5821,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G188" t="n">
-        <v>3.105877161026</v>
+        <v>3.10587692260742</v>
       </c>
       <c r="H188" t="n">
         <v>34306</v>
@@ -5850,7 +5850,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G189" t="n">
-        <v>3.07168960571289</v>
+        <v>3.07169008255005</v>
       </c>
       <c r="H189" t="n">
         <v>13448</v>
@@ -5879,7 +5879,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G190" t="n">
-        <v>3.05288743972778</v>
+        <v>3.0528872013092</v>
       </c>
       <c r="H190" t="n">
         <v>53980</v>
@@ -5908,7 +5908,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G191" t="n">
-        <v>3.10245847702026</v>
+        <v>3.10245823860168</v>
       </c>
       <c r="H191" t="n">
         <v>52101</v>
@@ -5937,7 +5937,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G192" t="n">
-        <v>3.09220242500305</v>
+        <v>3.09220218658447</v>
       </c>
       <c r="H192" t="n">
         <v>138994</v>
@@ -5966,7 +5966,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G193" t="n">
-        <v>3.07168960571289</v>
+        <v>3.07169008255005</v>
       </c>
       <c r="H193" t="n">
         <v>70631</v>
@@ -5995,7 +5995,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G194" t="n">
-        <v>3.07852745056152</v>
+        <v>3.07852721214294</v>
       </c>
       <c r="H194" t="n">
         <v>63225</v>
@@ -6024,7 +6024,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G195" t="n">
-        <v>3.08536458015442</v>
+        <v>3.08536434173584</v>
       </c>
       <c r="H195" t="n">
         <v>131706</v>
@@ -6082,7 +6082,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G197" t="n">
-        <v>3.15202879905701</v>
+        <v>3.15202951431274</v>
       </c>
       <c r="H197" t="n">
         <v>54450</v>
@@ -6111,7 +6111,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G198" t="n">
-        <v>3.19647240638733</v>
+        <v>3.19647169113159</v>
       </c>
       <c r="H198" t="n">
         <v>214245</v>
@@ -6140,7 +6140,7 @@
         <v>3.75</v>
       </c>
       <c r="G199" t="n">
-        <v>3.2050187587738</v>
+        <v>3.20501852035522</v>
       </c>
       <c r="H199" t="n">
         <v>160447</v>
@@ -6198,7 +6198,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G201" t="n">
-        <v>3.11442351341248</v>
+        <v>3.11442375183105</v>
       </c>
       <c r="H201" t="n">
         <v>81316</v>
@@ -6227,7 +6227,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G202" t="n">
-        <v>3.08536458015442</v>
+        <v>3.08536434173584</v>
       </c>
       <c r="H202" t="n">
         <v>110493</v>
@@ -6256,7 +6256,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G203" t="n">
-        <v>3.1349356174469</v>
+        <v>3.13493537902832</v>
       </c>
       <c r="H203" t="n">
         <v>81760</v>
@@ -6314,7 +6314,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G205" t="n">
-        <v>3.14177298545837</v>
+        <v>3.14177322387695</v>
       </c>
       <c r="H205" t="n">
         <v>78766</v>
@@ -6343,7 +6343,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G206" t="n">
-        <v>3.14348220825195</v>
+        <v>3.14348244667053</v>
       </c>
       <c r="H206" t="n">
         <v>62561</v>
@@ -6401,7 +6401,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14177298545837</v>
+        <v>3.14177322387695</v>
       </c>
       <c r="H208" t="n">
         <v>63926</v>
@@ -6430,7 +6430,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G209" t="n">
-        <v>3.14348220825195</v>
+        <v>3.14348244667053</v>
       </c>
       <c r="H209" t="n">
         <v>79922</v>
@@ -6488,7 +6488,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G211" t="n">
-        <v>3.12809872627258</v>
+        <v>3.12809824943542</v>
       </c>
       <c r="H211" t="n">
         <v>65236</v>
@@ -6575,7 +6575,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.12809872627258</v>
+        <v>3.12809824943542</v>
       </c>
       <c r="H214" t="n">
         <v>116511</v>
@@ -6604,7 +6604,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G215" t="n">
-        <v>3.15031957626343</v>
+        <v>3.15032005310059</v>
       </c>
       <c r="H215" t="n">
         <v>37592</v>
@@ -6691,7 +6691,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G218" t="n">
-        <v>3.02211928367615</v>
+        <v>3.02211856842041</v>
       </c>
       <c r="H218" t="n">
         <v>98671</v>
@@ -6720,7 +6720,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G219" t="n">
-        <v>3.05459642410278</v>
+        <v>3.0545961856842</v>
       </c>
       <c r="H219" t="n">
         <v>107982</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>2.97425723075867</v>
+        <v>2.97425770759583</v>
       </c>
       <c r="H220" t="n">
         <v>74403</v>
@@ -6778,7 +6778,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G221" t="n">
-        <v>3.09391140937805</v>
+        <v>3.09391164779663</v>
       </c>
       <c r="H221" t="n">
         <v>187251</v>
@@ -6807,7 +6807,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>3.05972456932068</v>
+        <v>3.05972480773926</v>
       </c>
       <c r="H222" t="n">
         <v>110461</v>
@@ -6836,7 +6836,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G223" t="n">
-        <v>3.08536458015442</v>
+        <v>3.08536434173584</v>
       </c>
       <c r="H223" t="n">
         <v>106184</v>
@@ -6865,7 +6865,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G224" t="n">
-        <v>3.05117774009705</v>
+        <v>3.05117797851562</v>
       </c>
       <c r="H224" t="n">
         <v>86249</v>
@@ -6894,7 +6894,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G225" t="n">
-        <v>3.04946875572205</v>
+        <v>3.04946851730347</v>
       </c>
       <c r="H225" t="n">
         <v>86643</v>
@@ -6923,7 +6923,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G226" t="n">
-        <v>3.03408408164978</v>
+        <v>3.03408432006836</v>
       </c>
       <c r="H226" t="n">
         <v>68454</v>
@@ -6952,7 +6952,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G227" t="n">
-        <v>3.03750276565552</v>
+        <v>3.03750324249268</v>
       </c>
       <c r="H227" t="n">
         <v>61249</v>
@@ -6981,7 +6981,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G228" t="n">
-        <v>3.02382826805115</v>
+        <v>3.02382850646973</v>
       </c>
       <c r="H228" t="n">
         <v>492149</v>
@@ -7010,7 +7010,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G229" t="n">
-        <v>3.02382826805115</v>
+        <v>3.02382850646973</v>
       </c>
       <c r="H229" t="n">
         <v>60528</v>
@@ -7039,7 +7039,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>3.02553725242615</v>
+        <v>3.02553749084473</v>
       </c>
       <c r="H230" t="n">
         <v>82568</v>
@@ -7068,7 +7068,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G231" t="n">
-        <v>2.99989748001099</v>
+        <v>2.99989771842957</v>
       </c>
       <c r="H231" t="n">
         <v>75544</v>
@@ -7097,7 +7097,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G232" t="n">
-        <v>3.01357269287109</v>
+        <v>3.01357245445251</v>
       </c>
       <c r="H232" t="n">
         <v>19834</v>
@@ -7126,7 +7126,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G233" t="n">
-        <v>3.0050253868103</v>
+        <v>3.00502562522888</v>
       </c>
       <c r="H233" t="n">
         <v>37168</v>
@@ -7155,7 +7155,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G234" t="n">
-        <v>3.02895617485046</v>
+        <v>3.02895665168762</v>
       </c>
       <c r="H234" t="n">
         <v>55217</v>
@@ -7184,7 +7184,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G235" t="n">
-        <v>2.96571040153503</v>
+        <v>2.96571063995361</v>
       </c>
       <c r="H235" t="n">
         <v>54912</v>
@@ -7213,7 +7213,7 @@
         <v>3.55399990081787</v>
       </c>
       <c r="G236" t="n">
-        <v>3.03750276565552</v>
+        <v>3.03750324249268</v>
       </c>
       <c r="H236" t="n">
         <v>129585</v>
@@ -7242,7 +7242,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G237" t="n">
-        <v>3.01699113845825</v>
+        <v>3.01699090003967</v>
       </c>
       <c r="H237" t="n">
         <v>103881</v>
@@ -7300,7 +7300,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G239" t="n">
-        <v>3.03408408164978</v>
+        <v>3.03408432006836</v>
       </c>
       <c r="H239" t="n">
         <v>118074</v>
@@ -7329,7 +7329,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G240" t="n">
-        <v>3.03921270370483</v>
+        <v>3.03921246528625</v>
       </c>
       <c r="H240" t="n">
         <v>109816</v>
@@ -7387,7 +7387,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G242" t="n">
-        <v>3.04604959487915</v>
+        <v>3.04604983329773</v>
       </c>
       <c r="H242" t="n">
         <v>114347</v>
@@ -7445,7 +7445,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G244" t="n">
-        <v>3.09903931617737</v>
+        <v>3.09903955459595</v>
       </c>
       <c r="H244" t="n">
         <v>212766</v>
@@ -7474,7 +7474,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G245" t="n">
-        <v>3.12809872627258</v>
+        <v>3.12809824943542</v>
       </c>
       <c r="H245" t="n">
         <v>161129</v>
@@ -7503,7 +7503,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G246" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H246" t="n">
         <v>286401</v>
@@ -7532,7 +7532,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G247" t="n">
-        <v>3.05972456932068</v>
+        <v>3.05972480773926</v>
       </c>
       <c r="H247" t="n">
         <v>282650</v>
@@ -7561,7 +7561,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>3.05972456932068</v>
+        <v>3.05972480773926</v>
       </c>
       <c r="H248" t="n">
         <v>179211</v>
@@ -7590,7 +7590,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>3.11955165863037</v>
+        <v>3.11955189704895</v>
       </c>
       <c r="H249" t="n">
         <v>408270</v>
@@ -7619,7 +7619,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G250" t="n">
-        <v>3.08707404136658</v>
+        <v>3.087073802948</v>
       </c>
       <c r="H250" t="n">
         <v>207332</v>
@@ -7648,7 +7648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H251" t="n">
         <v>385619</v>
@@ -7735,7 +7735,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G254" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H254" t="n">
         <v>208908</v>
@@ -7764,7 +7764,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G255" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H255" t="n">
         <v>176587</v>
@@ -7793,7 +7793,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G256" t="n">
-        <v>3.06143403053284</v>
+        <v>3.06143450737</v>
       </c>
       <c r="H256" t="n">
         <v>109911</v>
@@ -7822,7 +7822,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G257" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H257" t="n">
         <v>123713</v>
@@ -7909,7 +7909,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>3.11955165863037</v>
+        <v>3.11955189704895</v>
       </c>
       <c r="H260" t="n">
         <v>213481</v>
@@ -7938,7 +7938,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>3.11100482940674</v>
+        <v>3.11100506782532</v>
       </c>
       <c r="H261" t="n">
         <v>115617</v>
@@ -7967,7 +7967,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G262" t="n">
-        <v>3.09733033180237</v>
+        <v>3.09733057022095</v>
       </c>
       <c r="H262" t="n">
         <v>78644</v>
@@ -7996,7 +7996,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G263" t="n">
-        <v>3.07510900497437</v>
+        <v>3.07510852813721</v>
       </c>
       <c r="H263" t="n">
         <v>104543</v>
@@ -8054,7 +8054,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>3.06485247612</v>
+        <v>3.06485271453857</v>
       </c>
       <c r="H265" t="n">
         <v>127492</v>
@@ -8083,7 +8083,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>3.08023691177368</v>
+        <v>3.0802366733551</v>
       </c>
       <c r="H266" t="n">
         <v>158916</v>
@@ -8112,7 +8112,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>3.07681822776794</v>
+        <v>3.07681798934937</v>
       </c>
       <c r="H267" t="n">
         <v>125273</v>
@@ -8170,7 +8170,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>3.05972456932068</v>
+        <v>3.05972480773926</v>
       </c>
       <c r="H269" t="n">
         <v>73756</v>
@@ -8199,7 +8199,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G270" t="n">
-        <v>3.04946875572205</v>
+        <v>3.04946851730347</v>
       </c>
       <c r="H270" t="n">
         <v>126994</v>
@@ -8257,7 +8257,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.22211265563965</v>
+        <v>3.22211241722107</v>
       </c>
       <c r="H272" t="n">
         <v>187201</v>
@@ -8286,7 +8286,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G273" t="n">
-        <v>3.34689378738403</v>
+        <v>3.34689426422119</v>
       </c>
       <c r="H273" t="n">
         <v>449364</v>
@@ -8315,7 +8315,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G274" t="n">
-        <v>3.33151006698608</v>
+        <v>3.33151030540466</v>
       </c>
       <c r="H274" t="n">
         <v>254945</v>
@@ -8344,7 +8344,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G275" t="n">
-        <v>3.37766265869141</v>
+        <v>3.37766218185425</v>
       </c>
       <c r="H275" t="n">
         <v>306548</v>
@@ -8373,7 +8373,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G276" t="n">
-        <v>3.35885977745056</v>
+        <v>3.35885953903198</v>
       </c>
       <c r="H276" t="n">
         <v>342113</v>
@@ -8431,7 +8431,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.29903268814087</v>
+        <v>3.29903244972229</v>
       </c>
       <c r="H278" t="n">
         <v>98915</v>
@@ -8460,7 +8460,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G279" t="n">
-        <v>3.31099796295166</v>
+        <v>3.31099772453308</v>
       </c>
       <c r="H279" t="n">
         <v>149716</v>
@@ -8489,7 +8489,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G280" t="n">
-        <v>3.38450002670288</v>
+        <v>3.38449954986572</v>
       </c>
       <c r="H280" t="n">
         <v>93708</v>
@@ -8547,7 +8547,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G282" t="n">
-        <v>3.42723345756531</v>
+        <v>3.42723298072815</v>
       </c>
       <c r="H282" t="n">
         <v>188116</v>
@@ -8576,7 +8576,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G283" t="n">
-        <v>3.34176635742188</v>
+        <v>3.3417661190033</v>
       </c>
       <c r="H283" t="n">
         <v>130360</v>
@@ -8605,7 +8605,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G284" t="n">
-        <v>3.38620901107788</v>
+        <v>3.38620924949646</v>
       </c>
       <c r="H284" t="n">
         <v>98208</v>
@@ -8721,7 +8721,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G288" t="n">
-        <v>3.34860348701477</v>
+        <v>3.34860324859619</v>
       </c>
       <c r="H288" t="n">
         <v>99309</v>
@@ -8808,7 +8808,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G291" t="n">
-        <v>3.37595295906067</v>
+        <v>3.37595319747925</v>
       </c>
       <c r="H291" t="n">
         <v>127566</v>
@@ -8837,7 +8837,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G292" t="n">
-        <v>3.37595295906067</v>
+        <v>3.37595319747925</v>
       </c>
       <c r="H292" t="n">
         <v>113666</v>
@@ -8866,7 +8866,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G293" t="n">
-        <v>3.37595295906067</v>
+        <v>3.37595319747925</v>
       </c>
       <c r="H293" t="n">
         <v>158578</v>
@@ -8982,7 +8982,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G297" t="n">
-        <v>3.45116448402405</v>
+        <v>3.45116424560547</v>
       </c>
       <c r="H297" t="n">
         <v>239070</v>
@@ -9011,7 +9011,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G298" t="n">
-        <v>3.4391987323761</v>
+        <v>3.43919897079468</v>
       </c>
       <c r="H298" t="n">
         <v>122801</v>
@@ -9040,7 +9040,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G299" t="n">
-        <v>3.48535084724426</v>
+        <v>3.48535108566284</v>
       </c>
       <c r="H299" t="n">
         <v>178480</v>
@@ -9069,7 +9069,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G300" t="n">
-        <v>3.55030584335327</v>
+        <v>3.55030608177185</v>
       </c>
       <c r="H300" t="n">
         <v>292369</v>
@@ -9127,7 +9127,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G302" t="n">
-        <v>3.54688787460327</v>
+        <v>3.54688739776611</v>
       </c>
       <c r="H302" t="n">
         <v>281445</v>
@@ -9185,7 +9185,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53834080696106</v>
+        <v>3.53834056854248</v>
       </c>
       <c r="H304" t="n">
         <v>178128</v>
@@ -9243,7 +9243,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>3.52124714851379</v>
+        <v>3.52124691009521</v>
       </c>
       <c r="H306" t="n">
         <v>284296</v>
@@ -9301,7 +9301,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G308" t="n">
-        <v>3.70243740081787</v>
+        <v>3.70243811607361</v>
       </c>
       <c r="H308" t="n">
         <v>311354</v>
@@ -9388,7 +9388,7 @@
         <v>4.31400012969971</v>
       </c>
       <c r="G311" t="n">
-        <v>3.68705415725708</v>
+        <v>3.68705344200134</v>
       </c>
       <c r="H311" t="n">
         <v>495309</v>
@@ -9417,7 +9417,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>3.80328893661499</v>
+        <v>3.80328869819641</v>
       </c>
       <c r="H312" t="n">
         <v>578657</v>
@@ -9446,7 +9446,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G313" t="n">
-        <v>3.84431314468384</v>
+        <v>3.84431290626526</v>
       </c>
       <c r="H313" t="n">
         <v>517510</v>
@@ -9475,7 +9475,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>3.84089469909668</v>
+        <v>3.84089422225952</v>
       </c>
       <c r="H314" t="n">
         <v>389841</v>
@@ -9504,7 +9504,7 @@
         <v>4.53800010681152</v>
       </c>
       <c r="G315" t="n">
-        <v>3.87849974632263</v>
+        <v>3.87850022315979</v>
       </c>
       <c r="H315" t="n">
         <v>708378</v>
@@ -9562,7 +9562,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>3.95712971687317</v>
+        <v>3.95712947845459</v>
       </c>
       <c r="H317" t="n">
         <v>403814</v>
@@ -9591,7 +9591,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G318" t="n">
-        <v>3.99131655693054</v>
+        <v>3.99131679534912</v>
       </c>
       <c r="H318" t="n">
         <v>377054</v>
@@ -9649,7 +9649,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G320" t="n">
-        <v>3.98447918891907</v>
+        <v>3.98447966575623</v>
       </c>
       <c r="H320" t="n">
         <v>380294</v>
@@ -9707,7 +9707,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G322" t="n">
-        <v>3.95542049407959</v>
+        <v>3.95542073249817</v>
       </c>
       <c r="H322" t="n">
         <v>187589</v>
@@ -9736,7 +9736,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G323" t="n">
-        <v>3.9981541633606</v>
+        <v>3.99815344810486</v>
       </c>
       <c r="H323" t="n">
         <v>269524</v>
@@ -9765,7 +9765,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G324" t="n">
-        <v>3.97935104370117</v>
+        <v>3.97935175895691</v>
       </c>
       <c r="H324" t="n">
         <v>315513</v>
@@ -9852,7 +9852,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G327" t="n">
-        <v>4.02208518981934</v>
+        <v>4.02208471298218</v>
       </c>
       <c r="H327" t="n">
         <v>123388</v>
@@ -9881,7 +9881,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>4.00841045379639</v>
+        <v>4.00840997695923</v>
       </c>
       <c r="H328" t="n">
         <v>291725</v>
@@ -9910,7 +9910,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G329" t="n">
-        <v>4.00670099258423</v>
+        <v>4.00670051574707</v>
       </c>
       <c r="H329" t="n">
         <v>240607</v>
@@ -9997,7 +9997,7 @@
         <v>4.67199993133545</v>
       </c>
       <c r="G332" t="n">
-        <v>3.99302554130554</v>
+        <v>3.99302673339844</v>
       </c>
       <c r="H332" t="n">
         <v>556368</v>
@@ -10113,7 +10113,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>4.18789100646973</v>
+        <v>4.18789148330688</v>
       </c>
       <c r="H336" t="n">
         <v>249639</v>
@@ -10142,7 +10142,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>4.22207832336426</v>
+        <v>4.22207880020142</v>
       </c>
       <c r="H337" t="n">
         <v>265017</v>
@@ -10200,7 +10200,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>4.33745813369751</v>
+        <v>4.33745861053467</v>
       </c>
       <c r="H339" t="n">
         <v>271453</v>
@@ -10229,7 +10229,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.33745813369751</v>
+        <v>4.33745861053467</v>
       </c>
       <c r="H340" t="n">
         <v>284716</v>
@@ -10258,7 +10258,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>4.44429206848145</v>
+        <v>4.4442925453186</v>
       </c>
       <c r="H341" t="n">
         <v>510342</v>
@@ -10287,7 +10287,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>4.36737251281738</v>
+        <v>4.36737155914307</v>
       </c>
       <c r="H342" t="n">
         <v>409995</v>
@@ -10316,7 +10316,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>4.44429206848145</v>
+        <v>4.4442925453186</v>
       </c>
       <c r="H343" t="n">
         <v>316502</v>
@@ -10345,7 +10345,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G344" t="n">
-        <v>4.44429206848145</v>
+        <v>4.4442925453186</v>
       </c>
       <c r="H344" t="n">
         <v>380014</v>
@@ -10374,7 +10374,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G345" t="n">
-        <v>4.43574523925781</v>
+        <v>4.43574619293213</v>
       </c>
       <c r="H345" t="n">
         <v>221235</v>
@@ -10403,7 +10403,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G346" t="n">
-        <v>4.46138525009155</v>
+        <v>4.46138572692871</v>
       </c>
       <c r="H346" t="n">
         <v>324637</v>
@@ -10432,7 +10432,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G347" t="n">
-        <v>4.40155935287476</v>
+        <v>4.40155982971191</v>
       </c>
       <c r="H347" t="n">
         <v>342562</v>
@@ -10461,7 +10461,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G348" t="n">
-        <v>4.35455179214478</v>
+        <v>4.35455226898193</v>
       </c>
       <c r="H348" t="n">
         <v>1219966</v>
@@ -10519,7 +10519,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G350" t="n">
-        <v>4.51266670227051</v>
+        <v>4.51266717910767</v>
       </c>
       <c r="H350" t="n">
         <v>467077</v>
@@ -10548,7 +10548,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G351" t="n">
-        <v>4.67505359649658</v>
+        <v>4.67505311965942</v>
       </c>
       <c r="H351" t="n">
         <v>642036</v>
@@ -10606,7 +10606,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G353" t="n">
-        <v>4.67078113555908</v>
+        <v>4.67078018188477</v>
       </c>
       <c r="H353" t="n">
         <v>658370</v>
@@ -10635,7 +10635,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>4.72206163406372</v>
+        <v>4.7220606803894</v>
       </c>
       <c r="H354" t="n">
         <v>446009</v>
@@ -10722,7 +10722,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>4.92290925979614</v>
+        <v>4.92290830612183</v>
       </c>
       <c r="H357" t="n">
         <v>507023</v>
@@ -10751,7 +10751,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G358" t="n">
-        <v>4.96991586685181</v>
+        <v>4.96991539001465</v>
       </c>
       <c r="H358" t="n">
         <v>430499</v>
@@ -10780,7 +10780,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G359" t="n">
-        <v>4.97418832778931</v>
+        <v>4.97418928146362</v>
       </c>
       <c r="H359" t="n">
         <v>377192</v>
@@ -10838,7 +10838,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G361" t="n">
-        <v>4.91277599334717</v>
+        <v>4.91277551651001</v>
       </c>
       <c r="H361" t="n">
         <v>376356</v>
@@ -11041,7 +11041,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G368" t="n">
-        <v>4.91710138320923</v>
+        <v>4.91709995269775</v>
       </c>
       <c r="H368" t="n">
         <v>379109</v>
@@ -11070,7 +11070,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G369" t="n">
-        <v>4.84790658950806</v>
+        <v>4.8479061126709</v>
       </c>
       <c r="H369" t="n">
         <v>306807</v>
@@ -11099,7 +11099,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G370" t="n">
-        <v>4.52355909347534</v>
+        <v>4.5235595703125</v>
       </c>
       <c r="H370" t="n">
         <v>1242963</v>
@@ -11157,7 +11157,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G372" t="n">
-        <v>4.52788400650024</v>
+        <v>4.5278844833374</v>
       </c>
       <c r="H372" t="n">
         <v>529131</v>
@@ -11215,7 +11215,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G374" t="n">
-        <v>4.48031234741211</v>
+        <v>4.48031330108643</v>
       </c>
       <c r="H374" t="n">
         <v>293039</v>
@@ -11244,7 +11244,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>4.57977962493896</v>
+        <v>4.57978010177612</v>
       </c>
       <c r="H375" t="n">
         <v>656485</v>
@@ -11273,7 +11273,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G376" t="n">
-        <v>4.52788400650024</v>
+        <v>4.5278844833374</v>
       </c>
       <c r="H376" t="n">
         <v>512779</v>
@@ -11360,7 +11360,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>4.445716381073</v>
+        <v>4.44571590423584</v>
       </c>
       <c r="H379" t="n">
         <v>145570</v>
@@ -11418,7 +11418,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G381" t="n">
-        <v>4.51058626174927</v>
+        <v>4.51058530807495</v>
       </c>
       <c r="H381" t="n">
         <v>268402</v>
@@ -11447,7 +11447,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>4.55815649032593</v>
+        <v>4.55815696716309</v>
       </c>
       <c r="H382" t="n">
         <v>212506</v>
@@ -11476,7 +11476,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G383" t="n">
-        <v>4.37219762802124</v>
+        <v>4.3721981048584</v>
       </c>
       <c r="H383" t="n">
         <v>339934</v>
@@ -11505,7 +11505,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G384" t="n">
-        <v>4.33760118484497</v>
+        <v>4.33760070800781</v>
       </c>
       <c r="H384" t="n">
         <v>328719</v>
@@ -11534,7 +11534,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G385" t="n">
-        <v>4.37219762802124</v>
+        <v>4.3721981048584</v>
       </c>
       <c r="H385" t="n">
         <v>271930</v>
@@ -11592,7 +11592,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G387" t="n">
-        <v>4.3678731918335</v>
+        <v>4.36787271499634</v>
       </c>
       <c r="H387" t="n">
         <v>211703</v>
@@ -11621,7 +11621,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G388" t="n">
-        <v>4.36354875564575</v>
+        <v>4.36354827880859</v>
       </c>
       <c r="H388" t="n">
         <v>158333</v>
@@ -11650,7 +11650,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G389" t="n">
-        <v>4.34625005722046</v>
+        <v>4.34625053405762</v>
       </c>
       <c r="H389" t="n">
         <v>217764</v>
@@ -11708,7 +11708,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>4.41544389724731</v>
+        <v>4.41544437408447</v>
       </c>
       <c r="H391" t="n">
         <v>285596</v>
@@ -11737,7 +11737,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G392" t="n">
-        <v>4.55815649032593</v>
+        <v>4.55815696716309</v>
       </c>
       <c r="H392" t="n">
         <v>285504</v>
@@ -11795,7 +11795,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>4.57977962493896</v>
+        <v>4.57978010177612</v>
       </c>
       <c r="H394" t="n">
         <v>170900</v>
@@ -11853,7 +11853,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G396" t="n">
-        <v>4.63600015640259</v>
+        <v>4.63599967956543</v>
       </c>
       <c r="H396" t="n">
         <v>180908</v>
@@ -11882,7 +11882,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G397" t="n">
-        <v>4.6792459487915</v>
+        <v>4.67924642562866</v>
       </c>
       <c r="H397" t="n">
         <v>193488</v>
@@ -11911,7 +11911,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G398" t="n">
-        <v>4.65329790115356</v>
+        <v>4.65329837799072</v>
       </c>
       <c r="H398" t="n">
         <v>188616</v>
@@ -11940,7 +11940,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.63167572021484</v>
+        <v>4.63167524337769</v>
       </c>
       <c r="H399" t="n">
         <v>100820</v>
@@ -11969,7 +11969,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G400" t="n">
-        <v>4.65329790115356</v>
+        <v>4.65329837799072</v>
       </c>
       <c r="H400" t="n">
         <v>91142</v>
@@ -12027,7 +12027,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.67059707641602</v>
+        <v>4.67059659957886</v>
       </c>
       <c r="H402" t="n">
         <v>134607</v>
@@ -12085,7 +12085,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G404" t="n">
-        <v>4.74411582946777</v>
+        <v>4.74411535263062</v>
       </c>
       <c r="H404" t="n">
         <v>211993</v>
@@ -12114,7 +12114,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G405" t="n">
-        <v>4.91710138320923</v>
+        <v>4.91709995269775</v>
       </c>
       <c r="H405" t="n">
         <v>558746</v>
@@ -12143,7 +12143,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G406" t="n">
-        <v>4.81763410568237</v>
+        <v>4.81763505935669</v>
       </c>
       <c r="H406" t="n">
         <v>155403</v>
@@ -12230,7 +12230,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>4.83060884475708</v>
+        <v>4.83060789108276</v>
       </c>
       <c r="H409" t="n">
         <v>259833</v>
@@ -12259,7 +12259,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78736162185669</v>
+        <v>4.78736114501953</v>
       </c>
       <c r="H410" t="n">
         <v>208008</v>
@@ -12288,7 +12288,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G411" t="n">
-        <v>4.91710138320923</v>
+        <v>4.91709995269775</v>
       </c>
       <c r="H411" t="n">
         <v>347196</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.99926853179932</v>
+        <v>4.99926948547363</v>
       </c>
       <c r="H412" t="n">
         <v>293363</v>
@@ -12346,7 +12346,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G413" t="n">
-        <v>4.90412616729736</v>
+        <v>4.90412712097168</v>
       </c>
       <c r="H413" t="n">
         <v>259954</v>
@@ -12375,7 +12375,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>4.84790658950806</v>
+        <v>4.8479061126709</v>
       </c>
       <c r="H414" t="n">
         <v>166900</v>
@@ -12433,7 +12433,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G416" t="n">
-        <v>4.9560227394104</v>
+        <v>4.95602226257324</v>
       </c>
       <c r="H416" t="n">
         <v>142286</v>
@@ -12462,7 +12462,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>4.99061870574951</v>
+        <v>4.99061965942383</v>
       </c>
       <c r="H417" t="n">
         <v>218175</v>
@@ -12491,7 +12491,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>4.9560227394104</v>
+        <v>4.95602226257324</v>
       </c>
       <c r="H418" t="n">
         <v>119237</v>
@@ -12549,7 +12549,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G420" t="n">
-        <v>4.99061870574951</v>
+        <v>4.99061965942383</v>
       </c>
       <c r="H420" t="n">
         <v>97531</v>
@@ -12665,7 +12665,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>4.86087989807129</v>
+        <v>4.86088037490845</v>
       </c>
       <c r="H424" t="n">
         <v>75493</v>
@@ -12781,7 +12781,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G428" t="n">
-        <v>5.02089214324951</v>
+        <v>5.02089071273804</v>
       </c>
       <c r="H428" t="n">
         <v>198478</v>
@@ -12868,7 +12868,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G431" t="n">
-        <v>4.9560227394104</v>
+        <v>4.95602226257324</v>
       </c>
       <c r="H431" t="n">
         <v>165485</v>
@@ -12926,7 +12926,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G433" t="n">
-        <v>5.0252161026001</v>
+        <v>5.02521657943726</v>
       </c>
       <c r="H433" t="n">
         <v>167721</v>
@@ -13013,7 +13013,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G436" t="n">
-        <v>5.11170864105225</v>
+        <v>5.1117091178894</v>
       </c>
       <c r="H436" t="n">
         <v>238097</v>
@@ -13129,7 +13129,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H440" t="n">
         <v>312144</v>
@@ -13158,7 +13158,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H441" t="n">
         <v>187414</v>
@@ -13216,7 +13216,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H443" t="n">
         <v>239935</v>
@@ -13245,7 +13245,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G444" t="n">
-        <v>5.15495443344116</v>
+        <v>5.15495538711548</v>
       </c>
       <c r="H444" t="n">
         <v>259160</v>
@@ -13274,7 +13274,7 @@
         <v>5.83500003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>5.04683923721313</v>
+        <v>5.04683828353882</v>
       </c>
       <c r="H445" t="n">
         <v>301985</v>
@@ -13303,7 +13303,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H446" t="n">
         <v>310359</v>
@@ -13332,7 +13332,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H447" t="n">
         <v>262911</v>
@@ -13361,7 +13361,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G448" t="n">
-        <v>5.11603307723999</v>
+        <v>5.11603355407715</v>
       </c>
       <c r="H448" t="n">
         <v>133755</v>
@@ -13390,7 +13390,7 @@
         <v>6.0149998664856</v>
       </c>
       <c r="G449" t="n">
-        <v>5.20252561569214</v>
+        <v>5.2025260925293</v>
       </c>
       <c r="H449" t="n">
         <v>307624</v>
@@ -13419,7 +13419,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G450" t="n">
-        <v>5.15927982330322</v>
+        <v>5.15928030014038</v>
       </c>
       <c r="H450" t="n">
         <v>163379</v>
@@ -13448,7 +13448,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>5.15063047409058</v>
+        <v>5.15062999725342</v>
       </c>
       <c r="H451" t="n">
         <v>258487</v>
@@ -13535,7 +13535,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G454" t="n">
-        <v>5.10738515853882</v>
+        <v>5.10738468170166</v>
       </c>
       <c r="H454" t="n">
         <v>174661</v>
@@ -13564,7 +13564,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>5.12035799026489</v>
+        <v>5.12035894393921</v>
       </c>
       <c r="H455" t="n">
         <v>137091</v>
@@ -13593,7 +13593,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.12468338012695</v>
+        <v>5.12468290328979</v>
       </c>
       <c r="H456" t="n">
         <v>391635</v>
@@ -13622,7 +13622,7 @@
         <v>5.94500017166138</v>
       </c>
       <c r="G457" t="n">
-        <v>5.14198112487793</v>
+        <v>5.14198160171509</v>
       </c>
       <c r="H457" t="n">
         <v>276363</v>
@@ -13651,7 +13651,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>5.14630556106567</v>
+        <v>5.14630603790283</v>
       </c>
       <c r="H458" t="n">
         <v>191771</v>
@@ -13738,7 +13738,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G461" t="n">
-        <v>5.34956359863281</v>
+        <v>5.34956312179565</v>
       </c>
       <c r="H461" t="n">
         <v>556907</v>
@@ -13796,7 +13796,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G463" t="n">
-        <v>5.22414922714233</v>
+        <v>5.22414827346802</v>
       </c>
       <c r="H463" t="n">
         <v>224652</v>
@@ -13825,7 +13825,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G464" t="n">
-        <v>5.19387626647949</v>
+        <v>5.19387769699097</v>
       </c>
       <c r="H464" t="n">
         <v>368120</v>
@@ -13883,7 +13883,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G466" t="n">
-        <v>5.15927982330322</v>
+        <v>5.15928030014038</v>
       </c>
       <c r="H466" t="n">
         <v>209740</v>
@@ -13912,7 +13912,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G467" t="n">
-        <v>5.26739501953125</v>
+        <v>5.26739549636841</v>
       </c>
       <c r="H467" t="n">
         <v>280279</v>
@@ -13941,7 +13941,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G468" t="n">
-        <v>5.25009727478027</v>
+        <v>5.25009679794312</v>
       </c>
       <c r="H468" t="n">
         <v>285951</v>
@@ -13999,7 +13999,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>5.27171945571899</v>
+        <v>5.27172040939331</v>
       </c>
       <c r="H470" t="n">
         <v>292493</v>
@@ -14057,7 +14057,7 @@
         <v>6.125</v>
       </c>
       <c r="G472" t="n">
-        <v>5.29766750335693</v>
+        <v>5.29766798019409</v>
       </c>
       <c r="H472" t="n">
         <v>320585</v>
@@ -14086,7 +14086,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G473" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H473" t="n">
         <v>294814</v>
@@ -14115,7 +14115,7 @@
         <v>6.18499994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>5.34956359863281</v>
+        <v>5.34956312179565</v>
       </c>
       <c r="H474" t="n">
         <v>195823</v>
@@ -14144,7 +14144,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G475" t="n">
-        <v>5.33226537704468</v>
+        <v>5.33226442337036</v>
       </c>
       <c r="H475" t="n">
         <v>226682</v>
@@ -14231,7 +14231,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>4.99061870574951</v>
+        <v>4.99061965942383</v>
       </c>
       <c r="H478" t="n">
         <v>529854</v>
@@ -14289,7 +14289,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G480" t="n">
-        <v>4.78303718566895</v>
+        <v>4.7830376625061</v>
       </c>
       <c r="H480" t="n">
         <v>389197</v>
@@ -14318,7 +14318,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G481" t="n">
-        <v>4.73979043960571</v>
+        <v>4.73979091644287</v>
       </c>
       <c r="H481" t="n">
         <v>747857</v>
@@ -14347,7 +14347,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G482" t="n">
-        <v>4.90845108032227</v>
+        <v>4.90845251083374</v>
       </c>
       <c r="H482" t="n">
         <v>446975</v>
@@ -14376,7 +14376,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G483" t="n">
-        <v>4.77006340026855</v>
+        <v>4.7700629234314</v>
       </c>
       <c r="H483" t="n">
         <v>353313</v>
@@ -14579,7 +14579,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G490" t="n">
-        <v>4.96467065811157</v>
+        <v>4.96467113494873</v>
       </c>
       <c r="H490" t="n">
         <v>159744</v>
@@ -14695,7 +14695,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>4.86087989807129</v>
+        <v>4.86088037490845</v>
       </c>
       <c r="H494" t="n">
         <v>196034</v>
@@ -14724,7 +14724,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.90845108032227</v>
+        <v>4.90845251083374</v>
       </c>
       <c r="H495" t="n">
         <v>317223</v>
@@ -14753,7 +14753,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G496" t="n">
-        <v>4.87385511398315</v>
+        <v>4.87385416030884</v>
       </c>
       <c r="H496" t="n">
         <v>203739</v>
@@ -14898,7 +14898,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83060884475708</v>
+        <v>4.83060789108276</v>
       </c>
       <c r="H501" t="n">
         <v>212118</v>
@@ -14956,7 +14956,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>4.89980268478394</v>
+        <v>4.89980220794678</v>
       </c>
       <c r="H503" t="n">
         <v>344279</v>
@@ -15014,7 +15014,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.83060884475708</v>
+        <v>4.83060789108276</v>
       </c>
       <c r="H505" t="n">
         <v>188563</v>
@@ -15043,7 +15043,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G506" t="n">
-        <v>4.86087989807129</v>
+        <v>4.86088037490845</v>
       </c>
       <c r="H506" t="n">
         <v>155510</v>
@@ -15072,7 +15072,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.90845108032227</v>
+        <v>4.90845251083374</v>
       </c>
       <c r="H507" t="n">
         <v>101198</v>
@@ -15130,7 +15130,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G509" t="n">
-        <v>4.83925724029541</v>
+        <v>4.83925676345825</v>
       </c>
       <c r="H509" t="n">
         <v>153500</v>
@@ -15188,7 +15188,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G511" t="n">
-        <v>4.80466079711914</v>
+        <v>4.80465984344482</v>
       </c>
       <c r="H511" t="n">
         <v>148244</v>
@@ -15217,7 +15217,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>4.80898380279541</v>
+        <v>4.80898475646973</v>
       </c>
       <c r="H512" t="n">
         <v>181953</v>
@@ -15275,7 +15275,7 @@
         <v>5.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.97332143783569</v>
+        <v>4.97332096099854</v>
       </c>
       <c r="H514" t="n">
         <v>169760</v>
@@ -15304,7 +15304,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.96467065811157</v>
+        <v>4.96467113494873</v>
       </c>
       <c r="H515" t="n">
         <v>264465</v>
@@ -15333,7 +15333,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G516" t="n">
-        <v>5.08576107025146</v>
+        <v>5.08576154708862</v>
       </c>
       <c r="H516" t="n">
         <v>305733</v>
@@ -15362,7 +15362,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G517" t="n">
-        <v>5.25009727478027</v>
+        <v>5.25009679794312</v>
       </c>
       <c r="H517" t="n">
         <v>434448</v>
@@ -15478,7 +15478,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>5.30199289321899</v>
+        <v>5.30199241638184</v>
       </c>
       <c r="H521" t="n">
         <v>435702</v>
@@ -15507,7 +15507,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G522" t="n">
-        <v>5.20685052871704</v>
+        <v>5.2068510055542</v>
       </c>
       <c r="H522" t="n">
         <v>325870</v>
@@ -15565,7 +15565,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G524" t="n">
-        <v>5.25009727478027</v>
+        <v>5.25009679794312</v>
       </c>
       <c r="H524" t="n">
         <v>185841</v>
@@ -15681,7 +15681,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H528" t="n">
         <v>230837</v>
@@ -15710,7 +15710,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H529" t="n">
         <v>218110</v>
@@ -15739,7 +15739,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>5.44037961959839</v>
+        <v>5.44038057327271</v>
       </c>
       <c r="H530" t="n">
         <v>126571</v>
@@ -15768,7 +15768,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G531" t="n">
-        <v>5.37983560562134</v>
+        <v>5.3798360824585</v>
       </c>
       <c r="H531" t="n">
         <v>140959</v>
@@ -15797,7 +15797,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H532" t="n">
         <v>486411</v>
@@ -16029,7 +16029,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G540" t="n">
-        <v>4.91277599334717</v>
+        <v>4.91277551651001</v>
       </c>
       <c r="H540" t="n">
         <v>331497</v>
@@ -16058,7 +16058,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G541" t="n">
-        <v>4.9473729133606</v>
+        <v>4.94737243652344</v>
       </c>
       <c r="H541" t="n">
         <v>191805</v>
@@ -16087,7 +16087,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G542" t="n">
-        <v>4.99926853179932</v>
+        <v>4.99926948547363</v>
       </c>
       <c r="H542" t="n">
         <v>469641</v>
@@ -16290,7 +16290,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>5.08576107025146</v>
+        <v>5.08576154708862</v>
       </c>
       <c r="H549" t="n">
         <v>201005</v>
@@ -16348,7 +16348,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G551" t="n">
-        <v>5.06846284866333</v>
+        <v>5.06846237182617</v>
       </c>
       <c r="H551" t="n">
         <v>207351</v>
@@ -16464,7 +16464,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G555" t="n">
-        <v>4.87817907333374</v>
+        <v>4.87817859649658</v>
       </c>
       <c r="H555" t="n">
         <v>460820</v>
@@ -16638,7 +16638,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G561" t="n">
-        <v>5.29334306716919</v>
+        <v>5.29334259033203</v>
       </c>
       <c r="H561" t="n">
         <v>400906</v>
@@ -16667,7 +16667,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G562" t="n">
-        <v>5.28469371795654</v>
+        <v>5.2846941947937</v>
       </c>
       <c r="H562" t="n">
         <v>606194</v>
@@ -16696,7 +16696,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G563" t="n">
-        <v>5.30199289321899</v>
+        <v>5.30199241638184</v>
       </c>
       <c r="H563" t="n">
         <v>280196</v>
@@ -16725,7 +16725,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H564" t="n">
         <v>256807</v>
@@ -16841,7 +16841,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G568" t="n">
-        <v>5.28469371795654</v>
+        <v>5.2846941947937</v>
       </c>
       <c r="H568" t="n">
         <v>117389</v>
@@ -17015,7 +17015,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G574" t="n">
-        <v>5.29334306716919</v>
+        <v>5.29334259033203</v>
       </c>
       <c r="H574" t="n">
         <v>254433</v>
@@ -17044,7 +17044,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G575" t="n">
-        <v>5.27604484558105</v>
+        <v>5.27604389190674</v>
       </c>
       <c r="H575" t="n">
         <v>188121</v>
@@ -17102,7 +17102,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G577" t="n">
-        <v>5.26739501953125</v>
+        <v>5.26739549636841</v>
       </c>
       <c r="H577" t="n">
         <v>184600</v>
@@ -17131,7 +17131,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G578" t="n">
-        <v>5.27604484558105</v>
+        <v>5.27604389190674</v>
       </c>
       <c r="H578" t="n">
         <v>147386</v>
@@ -17189,7 +17189,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H580" t="n">
         <v>241429</v>
@@ -17218,7 +17218,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G581" t="n">
-        <v>5.29334306716919</v>
+        <v>5.29334259033203</v>
       </c>
       <c r="H581" t="n">
         <v>116988</v>
@@ -17247,7 +17247,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G582" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H582" t="n">
         <v>152528</v>
@@ -17276,7 +17276,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G583" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H583" t="n">
         <v>134082</v>
@@ -17305,7 +17305,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.31929016113281</v>
+        <v>5.31929063796997</v>
       </c>
       <c r="H584" t="n">
         <v>211164</v>
@@ -17363,7 +17363,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.3538875579834</v>
+        <v>5.35388851165771</v>
       </c>
       <c r="H586" t="n">
         <v>181479</v>
@@ -17392,7 +17392,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G587" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H587" t="n">
         <v>102963</v>
@@ -17421,7 +17421,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G588" t="n">
-        <v>5.27604484558105</v>
+        <v>5.27604389190674</v>
       </c>
       <c r="H588" t="n">
         <v>205665</v>
@@ -17450,7 +17450,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G589" t="n">
-        <v>5.26739501953125</v>
+        <v>5.26739549636841</v>
       </c>
       <c r="H589" t="n">
         <v>171564</v>
@@ -17479,7 +17479,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G590" t="n">
-        <v>5.26739501953125</v>
+        <v>5.26739549636841</v>
       </c>
       <c r="H590" t="n">
         <v>107170</v>
@@ -17508,7 +17508,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G591" t="n">
-        <v>5.25009727478027</v>
+        <v>5.25009679794312</v>
       </c>
       <c r="H591" t="n">
         <v>82268</v>
@@ -17537,7 +17537,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G592" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H592" t="n">
         <v>51217</v>
@@ -17595,7 +17595,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G594" t="n">
-        <v>5.31064081192017</v>
+        <v>5.31064128875732</v>
       </c>
       <c r="H594" t="n">
         <v>81075</v>
@@ -17624,7 +17624,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G595" t="n">
-        <v>5.31929016113281</v>
+        <v>5.31929063796997</v>
       </c>
       <c r="H595" t="n">
         <v>348016</v>
@@ -17682,7 +17682,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>5.37118577957153</v>
+        <v>5.37118625640869</v>
       </c>
       <c r="H597" t="n">
         <v>334253</v>
@@ -17711,7 +17711,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>5.41443252563477</v>
+        <v>5.41443300247192</v>
       </c>
       <c r="H598" t="n">
         <v>146406</v>
@@ -17740,7 +17740,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G599" t="n">
-        <v>5.39713335037231</v>
+        <v>5.39713382720947</v>
       </c>
       <c r="H599" t="n">
         <v>258483</v>
@@ -17769,7 +17769,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G600" t="n">
-        <v>5.39713335037231</v>
+        <v>5.39713382720947</v>
       </c>
       <c r="H600" t="n">
         <v>304811</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.36253690719604</v>
+        <v>5.3625373840332</v>
       </c>
       <c r="H601" t="n">
         <v>157793</v>
@@ -17827,7 +17827,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>5.36253690719604</v>
+        <v>5.3625373840332</v>
       </c>
       <c r="H602" t="n">
         <v>131446</v>
@@ -17856,7 +17856,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G603" t="n">
-        <v>5.37983560562134</v>
+        <v>5.3798360824585</v>
       </c>
       <c r="H603" t="n">
         <v>154664</v>
@@ -17943,7 +17943,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>5.30199289321899</v>
+        <v>5.30199241638184</v>
       </c>
       <c r="H606" t="n">
         <v>280448</v>
@@ -18001,7 +18001,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G608" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H608" t="n">
         <v>230665</v>
@@ -18146,7 +18146,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.06643772125244</v>
+        <v>5.06643724441528</v>
       </c>
       <c r="H613" t="n">
         <v>402155</v>
@@ -18204,7 +18204,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G615" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H615" t="n">
         <v>358974</v>
@@ -18233,7 +18233,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G616" t="n">
-        <v>5.18894195556641</v>
+        <v>5.18894147872925</v>
       </c>
       <c r="H616" t="n">
         <v>864096</v>
@@ -18349,7 +18349,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.20644235610962</v>
+        <v>5.20644283294678</v>
       </c>
       <c r="H620" t="n">
         <v>291258</v>
@@ -18378,7 +18378,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H621" t="n">
         <v>298828</v>
@@ -18465,7 +18465,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>5.28519582748413</v>
+        <v>5.28519487380981</v>
       </c>
       <c r="H624" t="n">
         <v>262813</v>
@@ -18668,7 +18668,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H631" t="n">
         <v>214958</v>
@@ -18726,7 +18726,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G633" t="n">
-        <v>5.15394067764282</v>
+        <v>5.15394020080566</v>
       </c>
       <c r="H633" t="n">
         <v>170995</v>
@@ -18755,7 +18755,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G634" t="n">
-        <v>5.15394067764282</v>
+        <v>5.15394020080566</v>
       </c>
       <c r="H634" t="n">
         <v>129808</v>
@@ -18784,7 +18784,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>5.14519023895264</v>
+        <v>5.14519119262695</v>
       </c>
       <c r="H635" t="n">
         <v>213690</v>
@@ -18813,7 +18813,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G636" t="n">
-        <v>5.15394067764282</v>
+        <v>5.15394020080566</v>
       </c>
       <c r="H636" t="n">
         <v>314192</v>
@@ -18842,7 +18842,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>5.16269111633301</v>
+        <v>5.16269159317017</v>
       </c>
       <c r="H637" t="n">
         <v>168128</v>
@@ -18871,7 +18871,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G638" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H638" t="n">
         <v>279839</v>
@@ -18900,7 +18900,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>5.14519023895264</v>
+        <v>5.14519119262695</v>
       </c>
       <c r="H639" t="n">
         <v>144087</v>
@@ -18929,7 +18929,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G640" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H640" t="n">
         <v>165373</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.14519023895264</v>
+        <v>5.14519119262695</v>
       </c>
       <c r="H641" t="n">
         <v>349001</v>
@@ -19016,7 +19016,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>5.2151927947998</v>
+        <v>5.21519327163696</v>
       </c>
       <c r="H643" t="n">
         <v>143137</v>
@@ -19103,7 +19103,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H646" t="n">
         <v>151180</v>
@@ -19190,7 +19190,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>5.2151927947998</v>
+        <v>5.21519327163696</v>
       </c>
       <c r="H649" t="n">
         <v>94966</v>
@@ -19219,7 +19219,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G650" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H650" t="n">
         <v>176317</v>
@@ -19364,7 +19364,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H655" t="n">
         <v>100368</v>
@@ -19509,7 +19509,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G660" t="n">
-        <v>5.48645305633545</v>
+        <v>5.48645257949829</v>
       </c>
       <c r="H660" t="n">
         <v>256033</v>
@@ -19538,7 +19538,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>5.42520046234131</v>
+        <v>5.42520093917847</v>
       </c>
       <c r="H661" t="n">
         <v>251611</v>
@@ -19567,7 +19567,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G662" t="n">
-        <v>5.47770261764526</v>
+        <v>5.47770309448242</v>
       </c>
       <c r="H662" t="n">
         <v>127936</v>
@@ -19596,7 +19596,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>5.41645050048828</v>
+        <v>5.41645097732544</v>
       </c>
       <c r="H663" t="n">
         <v>56554</v>
@@ -19654,7 +19654,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G665" t="n">
-        <v>5.52145433425903</v>
+        <v>5.52145385742188</v>
       </c>
       <c r="H665" t="n">
         <v>177146</v>
@@ -19683,7 +19683,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G666" t="n">
-        <v>5.61770868301392</v>
+        <v>5.61770725250244</v>
       </c>
       <c r="H666" t="n">
         <v>248959</v>
@@ -19799,7 +19799,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G670" t="n">
-        <v>5.47770261764526</v>
+        <v>5.47770309448242</v>
       </c>
       <c r="H670" t="n">
         <v>281439</v>
@@ -19857,7 +19857,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>5.53895473480225</v>
+        <v>5.53895425796509</v>
       </c>
       <c r="H672" t="n">
         <v>160142</v>
@@ -19886,7 +19886,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G673" t="n">
-        <v>5.69646167755127</v>
+        <v>5.69646120071411</v>
       </c>
       <c r="H673" t="n">
         <v>242459</v>
@@ -19915,7 +19915,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G674" t="n">
-        <v>5.69646167755127</v>
+        <v>5.69646120071411</v>
       </c>
       <c r="H674" t="n">
         <v>212783</v>
@@ -19944,7 +19944,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G675" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H675" t="n">
         <v>279194</v>
@@ -19973,7 +19973,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G676" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H676" t="n">
         <v>75671</v>
@@ -20002,7 +20002,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G677" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H677" t="n">
         <v>313127</v>
@@ -20031,7 +20031,7 @@
         <v>6.5</v>
       </c>
       <c r="G678" t="n">
-        <v>5.68770980834961</v>
+        <v>5.68771028518677</v>
       </c>
       <c r="H678" t="n">
         <v>316052</v>
@@ -20060,7 +20060,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>5.79271459579468</v>
+        <v>5.79271507263184</v>
       </c>
       <c r="H679" t="n">
         <v>427188</v>
@@ -20089,7 +20089,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G680" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H680" t="n">
         <v>278128</v>
@@ -20118,7 +20118,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>5.77521324157715</v>
+        <v>5.77521419525146</v>
       </c>
       <c r="H681" t="n">
         <v>302080</v>
@@ -20147,7 +20147,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G682" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H682" t="n">
         <v>231167</v>
@@ -20176,7 +20176,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>5.74021244049072</v>
+        <v>5.74021339416504</v>
       </c>
       <c r="H683" t="n">
         <v>243331</v>
@@ -20205,7 +20205,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H684" t="n">
         <v>191204</v>
@@ -20234,7 +20234,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G685" t="n">
-        <v>5.7314624786377</v>
+        <v>5.73146295547485</v>
       </c>
       <c r="H685" t="n">
         <v>187991</v>
@@ -20263,7 +20263,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>5.76646327972412</v>
+        <v>5.76646423339844</v>
       </c>
       <c r="H686" t="n">
         <v>234212</v>
@@ -20292,7 +20292,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>5.82771587371826</v>
+        <v>5.8277153968811</v>
       </c>
       <c r="H687" t="n">
         <v>283223</v>
@@ -20321,7 +20321,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>5.81021499633789</v>
+        <v>5.81021547317505</v>
       </c>
       <c r="H688" t="n">
         <v>263462</v>
@@ -20350,7 +20350,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.7314624786377</v>
+        <v>5.73146295547485</v>
       </c>
       <c r="H689" t="n">
         <v>389981</v>
@@ -20379,7 +20379,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>5.6702094078064</v>
+        <v>5.67021036148071</v>
       </c>
       <c r="H690" t="n">
         <v>186414</v>
@@ -20408,7 +20408,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G691" t="n">
-        <v>5.63520908355713</v>
+        <v>5.63520860671997</v>
       </c>
       <c r="H691" t="n">
         <v>211267</v>
@@ -20466,7 +20466,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>5.61770868301392</v>
+        <v>5.61770725250244</v>
       </c>
       <c r="H693" t="n">
         <v>234680</v>
@@ -20524,7 +20524,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G695" t="n">
-        <v>5.67896032333374</v>
+        <v>5.6789608001709</v>
       </c>
       <c r="H695" t="n">
         <v>173243</v>
@@ -20553,7 +20553,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G696" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H696" t="n">
         <v>2775017</v>
@@ -20582,7 +20582,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>5.75771236419678</v>
+        <v>5.75771379470825</v>
       </c>
       <c r="H697" t="n">
         <v>205507</v>
@@ -20611,7 +20611,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>5.85396671295166</v>
+        <v>5.8539662361145</v>
       </c>
       <c r="H698" t="n">
         <v>313492</v>
@@ -20640,7 +20640,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G699" t="n">
-        <v>5.74896335601807</v>
+        <v>5.74896287918091</v>
       </c>
       <c r="H699" t="n">
         <v>187174</v>
@@ -20669,7 +20669,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G700" t="n">
-        <v>5.75771236419678</v>
+        <v>5.75771379470825</v>
       </c>
       <c r="H700" t="n">
         <v>430939</v>
@@ -20698,7 +20698,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G701" t="n">
-        <v>5.67896032333374</v>
+        <v>5.6789608001709</v>
       </c>
       <c r="H701" t="n">
         <v>335638</v>
@@ -20727,7 +20727,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G702" t="n">
-        <v>5.71396112442017</v>
+        <v>5.71396255493164</v>
       </c>
       <c r="H702" t="n">
         <v>183347</v>
@@ -20756,7 +20756,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.643958568573</v>
+        <v>5.64395904541016</v>
       </c>
       <c r="H703" t="n">
         <v>334129</v>
@@ -20785,7 +20785,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G704" t="n">
-        <v>5.6702094078064</v>
+        <v>5.67021036148071</v>
       </c>
       <c r="H704" t="n">
         <v>255665</v>
@@ -20814,7 +20814,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>5.643958568573</v>
+        <v>5.64395904541016</v>
       </c>
       <c r="H705" t="n">
         <v>177562</v>
@@ -20843,7 +20843,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>5.54770517349243</v>
+        <v>5.54770565032959</v>
       </c>
       <c r="H706" t="n">
         <v>277755</v>
@@ -20872,7 +20872,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G707" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H707" t="n">
         <v>441362</v>
@@ -20901,7 +20901,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>5.3551983833313</v>
+        <v>5.35519790649414</v>
       </c>
       <c r="H708" t="n">
         <v>495999</v>
@@ -20930,7 +20930,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H709" t="n">
         <v>680613</v>
@@ -20959,7 +20959,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G710" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H710" t="n">
         <v>545215</v>
@@ -20988,7 +20988,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G711" t="n">
-        <v>5.15394067764282</v>
+        <v>5.15394020080566</v>
       </c>
       <c r="H711" t="n">
         <v>489354</v>
@@ -21075,7 +21075,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>5.11893939971924</v>
+        <v>5.1189398765564</v>
       </c>
       <c r="H714" t="n">
         <v>473307</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H715" t="n">
         <v>271362</v>
@@ -21162,7 +21162,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G717" t="n">
-        <v>4.97893476486206</v>
+        <v>4.9789342880249</v>
       </c>
       <c r="H717" t="n">
         <v>331986</v>
@@ -21191,7 +21191,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>4.84767961502075</v>
+        <v>4.84768009185791</v>
       </c>
       <c r="H718" t="n">
         <v>375775</v>
@@ -21220,7 +21220,7 @@
         <v>5.5</v>
       </c>
       <c r="G719" t="n">
-        <v>4.81267786026001</v>
+        <v>4.81267881393433</v>
       </c>
       <c r="H719" t="n">
         <v>253977</v>
@@ -21278,7 +21278,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G721" t="n">
-        <v>4.84767961502075</v>
+        <v>4.84768009185791</v>
       </c>
       <c r="H721" t="n">
         <v>295015</v>
@@ -21423,7 +21423,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G726" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H726" t="n">
         <v>142072</v>
@@ -21510,7 +21510,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G729" t="n">
-        <v>5.16269111633301</v>
+        <v>5.16269159317017</v>
       </c>
       <c r="H729" t="n">
         <v>181705</v>
@@ -21539,7 +21539,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H730" t="n">
         <v>132511</v>
@@ -21568,7 +21568,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>5.16269111633301</v>
+        <v>5.16269159317017</v>
       </c>
       <c r="H731" t="n">
         <v>85335</v>
@@ -21597,7 +21597,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G732" t="n">
-        <v>5.09268856048584</v>
+        <v>5.09268808364868</v>
       </c>
       <c r="H732" t="n">
         <v>113427</v>
@@ -21626,7 +21626,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>5.11893939971924</v>
+        <v>5.1189398765564</v>
       </c>
       <c r="H733" t="n">
         <v>102651</v>
@@ -21655,7 +21655,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.98768424987793</v>
+        <v>4.98768377304077</v>
       </c>
       <c r="H734" t="n">
         <v>159529</v>
@@ -21713,7 +21713,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G736" t="n">
-        <v>4.90018129348755</v>
+        <v>4.90018177032471</v>
       </c>
       <c r="H736" t="n">
         <v>281232</v>
@@ -21742,7 +21742,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G737" t="n">
-        <v>4.88268041610718</v>
+        <v>4.88268089294434</v>
       </c>
       <c r="H737" t="n">
         <v>191269</v>
@@ -21771,7 +21771,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>4.74267578125</v>
+        <v>4.74267625808716</v>
       </c>
       <c r="H738" t="n">
         <v>304605</v>
@@ -21800,7 +21800,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G739" t="n">
-        <v>4.60267066955566</v>
+        <v>4.60267019271851</v>
       </c>
       <c r="H739" t="n">
         <v>476143</v>
@@ -21858,7 +21858,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G741" t="n">
-        <v>4.74267578125</v>
+        <v>4.74267625808716</v>
       </c>
       <c r="H741" t="n">
         <v>124228</v>
@@ -21887,7 +21887,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>4.84767961502075</v>
+        <v>4.84768009185791</v>
       </c>
       <c r="H742" t="n">
         <v>239994</v>
@@ -21945,7 +21945,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G744" t="n">
-        <v>4.91768169403076</v>
+        <v>4.91768217086792</v>
       </c>
       <c r="H744" t="n">
         <v>174485</v>
@@ -22003,7 +22003,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G746" t="n">
-        <v>4.97893476486206</v>
+        <v>4.9789342880249</v>
       </c>
       <c r="H746" t="n">
         <v>281346</v>
@@ -22090,7 +22090,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G749" t="n">
-        <v>4.97893476486206</v>
+        <v>4.9789342880249</v>
       </c>
       <c r="H749" t="n">
         <v>116022</v>
@@ -22119,7 +22119,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G750" t="n">
-        <v>4.86517953872681</v>
+        <v>4.86518001556396</v>
       </c>
       <c r="H750" t="n">
         <v>209832</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.88268041610718</v>
+        <v>4.88268089294434</v>
       </c>
       <c r="H751" t="n">
         <v>193331</v>
@@ -22206,7 +22206,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G753" t="n">
-        <v>4.80392789840698</v>
+        <v>4.80392742156982</v>
       </c>
       <c r="H753" t="n">
         <v>255608</v>
@@ -22235,7 +22235,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G754" t="n">
-        <v>4.98768424987793</v>
+        <v>4.98768377304077</v>
       </c>
       <c r="H754" t="n">
         <v>289680</v>
@@ -22264,7 +22264,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G755" t="n">
-        <v>4.97893476486206</v>
+        <v>4.9789342880249</v>
       </c>
       <c r="H755" t="n">
         <v>245616</v>
@@ -22525,7 +22525,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>5.11893939971924</v>
+        <v>5.1189398765564</v>
       </c>
       <c r="H764" t="n">
         <v>159130</v>
@@ -22554,7 +22554,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G765" t="n">
-        <v>5.05768728256226</v>
+        <v>5.05768823623657</v>
       </c>
       <c r="H765" t="n">
         <v>241488</v>
@@ -22583,7 +22583,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G766" t="n">
-        <v>5.20644235610962</v>
+        <v>5.20644283294678</v>
       </c>
       <c r="H766" t="n">
         <v>334776</v>
@@ -22728,7 +22728,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>5.2151927947998</v>
+        <v>5.21519327163696</v>
       </c>
       <c r="H771" t="n">
         <v>101123</v>
@@ -22757,7 +22757,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H772" t="n">
         <v>87614</v>
@@ -22873,7 +22873,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>5.38144874572754</v>
+        <v>5.3814492225647</v>
       </c>
       <c r="H776" t="n">
         <v>157400</v>
@@ -22902,7 +22902,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>5.38144874572754</v>
+        <v>5.3814492225647</v>
       </c>
       <c r="H777" t="n">
         <v>161166</v>
@@ -22931,7 +22931,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G778" t="n">
-        <v>5.3551983833313</v>
+        <v>5.35519790649414</v>
       </c>
       <c r="H778" t="n">
         <v>230954</v>
@@ -22960,7 +22960,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G779" t="n">
-        <v>5.41645050048828</v>
+        <v>5.41645097732544</v>
       </c>
       <c r="H779" t="n">
         <v>150707</v>
@@ -23047,7 +23047,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G782" t="n">
-        <v>5.3551983833313</v>
+        <v>5.35519790649414</v>
       </c>
       <c r="H782" t="n">
         <v>247195</v>
@@ -23076,7 +23076,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G783" t="n">
-        <v>5.41645050048828</v>
+        <v>5.41645097732544</v>
       </c>
       <c r="H783" t="n">
         <v>78048</v>
@@ -23105,7 +23105,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G784" t="n">
-        <v>5.37269830703735</v>
+        <v>5.37269878387451</v>
       </c>
       <c r="H784" t="n">
         <v>132978</v>
@@ -23134,7 +23134,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G785" t="n">
-        <v>5.33769798278809</v>
+        <v>5.33769702911377</v>
       </c>
       <c r="H785" t="n">
         <v>229877</v>
@@ -23163,7 +23163,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G786" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H786" t="n">
         <v>240557</v>
@@ -23221,7 +23221,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G788" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H788" t="n">
         <v>152049</v>
@@ -23279,7 +23279,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>5.18019199371338</v>
+        <v>5.18019247055054</v>
       </c>
       <c r="H790" t="n">
         <v>271681</v>
@@ -23337,7 +23337,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G792" t="n">
-        <v>5.15394067764282</v>
+        <v>5.15394020080566</v>
       </c>
       <c r="H792" t="n">
         <v>194764</v>
@@ -23453,7 +23453,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>5.28519582748413</v>
+        <v>5.28519487380981</v>
       </c>
       <c r="H796" t="n">
         <v>134267</v>
@@ -23627,7 +23627,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G802" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H802" t="n">
         <v>102270</v>
@@ -23656,7 +23656,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H803" t="n">
         <v>104236</v>
@@ -23685,7 +23685,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G804" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H804" t="n">
         <v>110679</v>
@@ -23714,7 +23714,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G805" t="n">
-        <v>5.3551983833313</v>
+        <v>5.35519790649414</v>
       </c>
       <c r="H805" t="n">
         <v>129238</v>
@@ -23743,7 +23743,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G806" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H806" t="n">
         <v>162640</v>
@@ -23801,7 +23801,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G808" t="n">
-        <v>5.31144714355469</v>
+        <v>5.31144666671753</v>
       </c>
       <c r="H808" t="n">
         <v>93232</v>
@@ -23830,7 +23830,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H809" t="n">
         <v>142286</v>
@@ -23888,7 +23888,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>5.28519582748413</v>
+        <v>5.28519487380981</v>
       </c>
       <c r="H811" t="n">
         <v>152213</v>
@@ -23917,7 +23917,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G812" t="n">
-        <v>5.34644794464111</v>
+        <v>5.34644842147827</v>
       </c>
       <c r="H812" t="n">
         <v>131774</v>
@@ -23975,7 +23975,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.33769798278809</v>
+        <v>5.33769702911377</v>
       </c>
       <c r="H814" t="n">
         <v>136836</v>
@@ -24033,7 +24033,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G816" t="n">
-        <v>5.5039529800415</v>
+        <v>5.50395393371582</v>
       </c>
       <c r="H816" t="n">
         <v>554791</v>
@@ -24062,7 +24062,7 @@
         <v>6.25</v>
       </c>
       <c r="G817" t="n">
-        <v>5.46895217895508</v>
+        <v>5.46895265579224</v>
       </c>
       <c r="H817" t="n">
         <v>218380</v>
@@ -24178,7 +24178,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>5.39895009994507</v>
+        <v>5.39894962310791</v>
       </c>
       <c r="H821" t="n">
         <v>194054</v>
@@ -24207,7 +24207,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G822" t="n">
-        <v>5.40769958496094</v>
+        <v>5.4077000617981</v>
       </c>
       <c r="H822" t="n">
         <v>181452</v>
@@ -24236,7 +24236,7 @@
         <v>6.25</v>
       </c>
       <c r="G823" t="n">
-        <v>5.46895217895508</v>
+        <v>5.46895265579224</v>
       </c>
       <c r="H823" t="n">
         <v>103867</v>
@@ -24265,7 +24265,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G824" t="n">
-        <v>5.42520046234131</v>
+        <v>5.42520093917847</v>
       </c>
       <c r="H824" t="n">
         <v>118960</v>
@@ -24294,7 +24294,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G825" t="n">
-        <v>5.49520301818848</v>
+        <v>5.49520349502563</v>
       </c>
       <c r="H825" t="n">
         <v>173711</v>
@@ -24352,7 +24352,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G827" t="n">
-        <v>5.47770261764526</v>
+        <v>5.47770309448242</v>
       </c>
       <c r="H827" t="n">
         <v>126185</v>
@@ -24381,7 +24381,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5039529800415</v>
+        <v>5.50395393371582</v>
       </c>
       <c r="H828" t="n">
         <v>138747</v>
@@ -24555,7 +24555,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G834" t="n">
-        <v>5.5039529800415</v>
+        <v>5.50395393371582</v>
       </c>
       <c r="H834" t="n">
         <v>90763</v>
@@ -24584,7 +24584,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>5.53895473480225</v>
+        <v>5.53895425796509</v>
       </c>
       <c r="H835" t="n">
         <v>80407</v>
@@ -24700,7 +24700,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>5.52145433425903</v>
+        <v>5.52145385742188</v>
       </c>
       <c r="H839" t="n">
         <v>154582</v>
@@ -24729,7 +24729,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G840" t="n">
-        <v>5.52145433425903</v>
+        <v>5.52145385742188</v>
       </c>
       <c r="H840" t="n">
         <v>119319</v>
@@ -24758,7 +24758,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G841" t="n">
-        <v>5.49520301818848</v>
+        <v>5.49520349502563</v>
       </c>
       <c r="H841" t="n">
         <v>130287</v>
@@ -24787,7 +24787,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G842" t="n">
-        <v>5.49520301818848</v>
+        <v>5.49520349502563</v>
       </c>
       <c r="H842" t="n">
         <v>219460</v>
@@ -24845,7 +24845,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>5.54770517349243</v>
+        <v>5.54770565032959</v>
       </c>
       <c r="H844" t="n">
         <v>123531</v>
@@ -24903,7 +24903,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G846" t="n">
-        <v>5.54770517349243</v>
+        <v>5.54770565032959</v>
       </c>
       <c r="H846" t="n">
         <v>89727</v>
@@ -25019,7 +25019,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>5.38144874572754</v>
+        <v>5.3814492225647</v>
       </c>
       <c r="H850" t="n">
         <v>94240</v>
@@ -25048,7 +25048,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>5.42520046234131</v>
+        <v>5.42520093917847</v>
       </c>
       <c r="H851" t="n">
         <v>68215</v>
@@ -25106,7 +25106,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>5.32894659042358</v>
+        <v>5.3289475440979</v>
       </c>
       <c r="H853" t="n">
         <v>92850</v>
@@ -25135,7 +25135,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G854" t="n">
-        <v>5.20644235610962</v>
+        <v>5.20644283294678</v>
       </c>
       <c r="H854" t="n">
         <v>163647</v>
@@ -25193,7 +25193,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>5.33769798278809</v>
+        <v>5.33769702911377</v>
       </c>
       <c r="H856" t="n">
         <v>198016</v>
@@ -25222,7 +25222,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G857" t="n">
-        <v>5.37269830703735</v>
+        <v>5.37269878387451</v>
       </c>
       <c r="H857" t="n">
         <v>59164</v>
@@ -25251,7 +25251,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G858" t="n">
-        <v>5.3551983833313</v>
+        <v>5.35519790649414</v>
       </c>
       <c r="H858" t="n">
         <v>101854</v>
@@ -25280,7 +25280,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G859" t="n">
-        <v>5.31978845596313</v>
+        <v>5.31978893280029</v>
       </c>
       <c r="H859" t="n">
         <v>63892</v>
@@ -25309,7 +25309,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>5.3640456199646</v>
+        <v>5.36404609680176</v>
       </c>
       <c r="H860" t="n">
         <v>48287</v>
@@ -25367,7 +25367,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>5.26667833328247</v>
+        <v>5.26667881011963</v>
       </c>
       <c r="H862" t="n">
         <v>165617</v>
@@ -25396,7 +25396,7 @@
         <v>6</v>
       </c>
       <c r="G863" t="n">
-        <v>5.31093692779541</v>
+        <v>5.31093645095825</v>
       </c>
       <c r="H863" t="n">
         <v>100484</v>
@@ -25425,7 +25425,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G864" t="n">
-        <v>5.30208492279053</v>
+        <v>5.30208587646484</v>
       </c>
       <c r="H864" t="n">
         <v>76058</v>
@@ -25454,7 +25454,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>5.26667833328247</v>
+        <v>5.26667881011963</v>
       </c>
       <c r="H865" t="n">
         <v>239692</v>
@@ -25512,7 +25512,7 @@
         <v>6</v>
       </c>
       <c r="G867" t="n">
-        <v>5.31093692779541</v>
+        <v>5.31093645095825</v>
       </c>
       <c r="H867" t="n">
         <v>170200</v>
@@ -25570,7 +25570,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G869" t="n">
-        <v>5.2401237487793</v>
+        <v>5.24012422561646</v>
       </c>
       <c r="H869" t="n">
         <v>81117</v>
@@ -25599,7 +25599,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G870" t="n">
-        <v>5.25782775878906</v>
+        <v>5.2578272819519</v>
       </c>
       <c r="H870" t="n">
         <v>102625</v>
@@ -25628,7 +25628,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G871" t="n">
-        <v>5.24897575378418</v>
+        <v>5.24897527694702</v>
       </c>
       <c r="H871" t="n">
         <v>110346</v>
@@ -25657,7 +25657,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>5.22242069244385</v>
+        <v>5.22242164611816</v>
       </c>
       <c r="H872" t="n">
         <v>98873</v>
@@ -25686,7 +25686,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G873" t="n">
-        <v>5.24897575378418</v>
+        <v>5.24897527694702</v>
       </c>
       <c r="H873" t="n">
         <v>143566</v>
@@ -25715,7 +25715,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>5.2401237487793</v>
+        <v>5.24012422561646</v>
       </c>
       <c r="H874" t="n">
         <v>168078</v>
@@ -25744,7 +25744,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>5.2932333946228</v>
+        <v>5.29323434829712</v>
       </c>
       <c r="H875" t="n">
         <v>158803</v>
@@ -25773,7 +25773,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G876" t="n">
-        <v>5.26667833328247</v>
+        <v>5.26667881011963</v>
       </c>
       <c r="H876" t="n">
         <v>159434</v>
@@ -25802,7 +25802,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>5.27553033828735</v>
+        <v>5.27553081512451</v>
       </c>
       <c r="H877" t="n">
         <v>133520</v>
@@ -25831,7 +25831,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G878" t="n">
-        <v>5.25782775878906</v>
+        <v>5.2578272819519</v>
       </c>
       <c r="H878" t="n">
         <v>127179</v>
@@ -25860,7 +25860,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>5.2401237487793</v>
+        <v>5.24012422561646</v>
       </c>
       <c r="H879" t="n">
         <v>389442</v>
@@ -25889,7 +25889,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G880" t="n">
-        <v>5.26667833328247</v>
+        <v>5.26667881011963</v>
       </c>
       <c r="H880" t="n">
         <v>205395</v>
@@ -25918,7 +25918,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>5.2401237487793</v>
+        <v>5.24012422561646</v>
       </c>
       <c r="H881" t="n">
         <v>376959</v>
@@ -25947,7 +25947,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>5.22242069244385</v>
+        <v>5.22242164611816</v>
       </c>
       <c r="H882" t="n">
         <v>435477</v>
@@ -25976,7 +25976,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G883" t="n">
-        <v>5.1693115234375</v>
+        <v>5.16931247711182</v>
       </c>
       <c r="H883" t="n">
         <v>277530</v>
@@ -26005,7 +26005,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>5.12505435943604</v>
+        <v>5.12505388259888</v>
       </c>
       <c r="H884" t="n">
         <v>371113</v>
@@ -26092,7 +26092,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G887" t="n">
-        <v>5.0099835395813</v>
+        <v>5.00998401641846</v>
       </c>
       <c r="H887" t="n">
         <v>455302</v>
@@ -26208,7 +26208,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>5.1693115234375</v>
+        <v>5.16931247711182</v>
       </c>
       <c r="H891" t="n">
         <v>378106</v>
@@ -26237,7 +26237,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G892" t="n">
-        <v>5.14275646209717</v>
+        <v>5.14275693893433</v>
       </c>
       <c r="H892" t="n">
         <v>285915</v>
@@ -26266,7 +26266,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G893" t="n">
-        <v>5.09849882125854</v>
+        <v>5.0984992980957</v>
       </c>
       <c r="H893" t="n">
         <v>172844</v>
@@ -26295,7 +26295,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H894" t="n">
         <v>144694</v>
@@ -26324,7 +26324,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G895" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H895" t="n">
         <v>360106</v>
@@ -26382,7 +26382,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>5.12505435943604</v>
+        <v>5.12505388259888</v>
       </c>
       <c r="H897" t="n">
         <v>114135</v>
@@ -26440,7 +26440,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>5.14275646209717</v>
+        <v>5.14275693893433</v>
       </c>
       <c r="H899" t="n">
         <v>218405</v>
@@ -26498,7 +26498,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>5.12505435943604</v>
+        <v>5.12505388259888</v>
       </c>
       <c r="H901" t="n">
         <v>131304</v>
@@ -26527,7 +26527,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G902" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H902" t="n">
         <v>122768</v>
@@ -26556,7 +26556,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G903" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H903" t="n">
         <v>135564</v>
@@ -26585,7 +26585,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>5.12505435943604</v>
+        <v>5.12505388259888</v>
       </c>
       <c r="H904" t="n">
         <v>96058</v>
@@ -26643,7 +26643,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G906" t="n">
-        <v>5.21356868743896</v>
+        <v>5.21356916427612</v>
       </c>
       <c r="H906" t="n">
         <v>122715</v>
@@ -26701,7 +26701,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>5.25782775878906</v>
+        <v>5.2578272819519</v>
       </c>
       <c r="H908" t="n">
         <v>123611</v>
@@ -26730,7 +26730,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>5.2401237487793</v>
+        <v>5.24012422561646</v>
       </c>
       <c r="H909" t="n">
         <v>213504</v>
@@ -26759,7 +26759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H910" t="n">
         <v>240944</v>
@@ -26817,7 +26817,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G912" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H912" t="n">
         <v>245998</v>
@@ -26846,7 +26846,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>5.10735082626343</v>
+        <v>5.10735130310059</v>
       </c>
       <c r="H913" t="n">
         <v>186030</v>
@@ -26904,7 +26904,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H915" t="n">
         <v>94756</v>
@@ -26933,7 +26933,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H916" t="n">
         <v>146370</v>
@@ -26991,7 +26991,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G918" t="n">
-        <v>5.06309270858765</v>
+        <v>5.0630931854248</v>
       </c>
       <c r="H918" t="n">
         <v>125330</v>
@@ -27049,7 +27049,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>4.98342943191528</v>
+        <v>4.98342990875244</v>
       </c>
       <c r="H920" t="n">
         <v>140055</v>
@@ -27136,7 +27136,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G923" t="n">
-        <v>4.97457695007324</v>
+        <v>4.9745774269104</v>
       </c>
       <c r="H923" t="n">
         <v>78918</v>
@@ -27194,7 +27194,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>5.0453896522522</v>
+        <v>5.04538917541504</v>
       </c>
       <c r="H925" t="n">
         <v>49806</v>
@@ -27223,7 +27223,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G926" t="n">
-        <v>5.06309270858765</v>
+        <v>5.0630931854248</v>
       </c>
       <c r="H926" t="n">
         <v>42421</v>
@@ -27281,7 +27281,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.97457695007324</v>
+        <v>4.9745774269104</v>
       </c>
       <c r="H928" t="n">
         <v>47725</v>
@@ -27368,7 +27368,7 @@
         <v>5.75</v>
       </c>
       <c r="G931" t="n">
-        <v>5.08964729309082</v>
+        <v>5.08964776992798</v>
       </c>
       <c r="H931" t="n">
         <v>91374</v>
@@ -27397,7 +27397,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G932" t="n">
-        <v>5.0453896522522</v>
+        <v>5.04538917541504</v>
       </c>
       <c r="H932" t="n">
         <v>138686</v>
@@ -27513,7 +27513,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G936" t="n">
-        <v>5.14275646209717</v>
+        <v>5.14275693893433</v>
       </c>
       <c r="H936" t="n">
         <v>111596</v>
@@ -27542,7 +27542,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>5.10735082626343</v>
+        <v>5.10735130310059</v>
       </c>
       <c r="H937" t="n">
         <v>96102</v>
@@ -27716,7 +27716,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>5.18701553344727</v>
+        <v>5.18701505661011</v>
       </c>
       <c r="H943" t="n">
         <v>222015</v>
@@ -27745,7 +27745,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G944" t="n">
-        <v>5.18701553344727</v>
+        <v>5.18701505661011</v>
       </c>
       <c r="H944" t="n">
         <v>120119</v>
@@ -27832,7 +27832,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>5.2932333946228</v>
+        <v>5.29323434829712</v>
       </c>
       <c r="H947" t="n">
         <v>295674</v>
@@ -27861,7 +27861,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G948" t="n">
-        <v>5.3640456199646</v>
+        <v>5.36404609680176</v>
       </c>
       <c r="H948" t="n">
         <v>279533</v>
@@ -27890,7 +27890,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G949" t="n">
-        <v>5.452561378479</v>
+        <v>5.45256185531616</v>
       </c>
       <c r="H949" t="n">
         <v>366143</v>
@@ -27919,7 +27919,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>5.34634304046631</v>
+        <v>5.34634256362915</v>
       </c>
       <c r="H950" t="n">
         <v>408435</v>
@@ -27948,7 +27948,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>5.42600727081299</v>
+        <v>5.42600774765015</v>
       </c>
       <c r="H951" t="n">
         <v>165950</v>
@@ -27977,7 +27977,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G952" t="n">
-        <v>5.46141386032104</v>
+        <v>5.46141338348389</v>
       </c>
       <c r="H952" t="n">
         <v>522048</v>
@@ -28006,7 +28006,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G953" t="n">
-        <v>5.49681901931763</v>
+        <v>5.49681949615479</v>
       </c>
       <c r="H953" t="n">
         <v>217476</v>
@@ -28035,7 +28035,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G954" t="n">
-        <v>5.46141386032104</v>
+        <v>5.46141338348389</v>
       </c>
       <c r="H954" t="n">
         <v>197955</v>
@@ -28064,7 +28064,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G955" t="n">
-        <v>5.31978845596313</v>
+        <v>5.31978893280029</v>
       </c>
       <c r="H955" t="n">
         <v>187015</v>
@@ -28093,7 +28093,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>5.47911643981934</v>
+        <v>5.47911596298218</v>
       </c>
       <c r="H956" t="n">
         <v>697243</v>
@@ -28122,7 +28122,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G957" t="n">
-        <v>5.62074089050293</v>
+        <v>5.62074136734009</v>
       </c>
       <c r="H957" t="n">
         <v>651441</v>
@@ -28238,7 +28238,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>5.60303831100464</v>
+        <v>5.6030387878418</v>
       </c>
       <c r="H961" t="n">
         <v>224640</v>
@@ -28267,7 +28267,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>5.62074089050293</v>
+        <v>5.62074136734009</v>
       </c>
       <c r="H962" t="n">
         <v>122437</v>
@@ -28296,7 +28296,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G963" t="n">
-        <v>5.62959337234497</v>
+        <v>5.62959384918213</v>
       </c>
       <c r="H963" t="n">
         <v>90855</v>
@@ -28325,7 +28325,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G964" t="n">
-        <v>5.63844442367554</v>
+        <v>5.6384449005127</v>
       </c>
       <c r="H964" t="n">
         <v>342438</v>
@@ -28354,7 +28354,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G965" t="n">
-        <v>5.65614700317383</v>
+        <v>5.65614795684814</v>
       </c>
       <c r="H965" t="n">
         <v>328836</v>
@@ -28383,7 +28383,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G966" t="n">
-        <v>5.67385053634644</v>
+        <v>5.67385101318359</v>
       </c>
       <c r="H966" t="n">
         <v>88220</v>
@@ -28441,7 +28441,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G968" t="n">
-        <v>5.67385053634644</v>
+        <v>5.67385101318359</v>
       </c>
       <c r="H968" t="n">
         <v>188423</v>
@@ -28499,7 +28499,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G970" t="n">
-        <v>5.66499948501587</v>
+        <v>5.66499900817871</v>
       </c>
       <c r="H970" t="n">
         <v>168556</v>
@@ -28615,7 +28615,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G974" t="n">
-        <v>5.73581171035767</v>
+        <v>5.73581218719482</v>
       </c>
       <c r="H974" t="n">
         <v>138788</v>
@@ -28673,7 +28673,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G976" t="n">
-        <v>5.67385053634644</v>
+        <v>5.67385101318359</v>
       </c>
       <c r="H976" t="n">
         <v>237057</v>
@@ -28702,7 +28702,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G977" t="n">
-        <v>5.72695970535278</v>
+        <v>5.7269606590271</v>
       </c>
       <c r="H977" t="n">
         <v>86453</v>
@@ -28760,7 +28760,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G979" t="n">
-        <v>5.78006935119629</v>
+        <v>5.78006982803345</v>
       </c>
       <c r="H979" t="n">
         <v>267065</v>
@@ -28847,7 +28847,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>5.82432699203491</v>
+        <v>5.82432794570923</v>
       </c>
       <c r="H982" t="n">
         <v>2361841</v>
@@ -28876,7 +28876,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>5.80662441253662</v>
+        <v>5.80662393569946</v>
       </c>
       <c r="H983" t="n">
         <v>223147</v>
@@ -28905,7 +28905,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G984" t="n">
-        <v>5.86858558654785</v>
+        <v>5.86858510971069</v>
       </c>
       <c r="H984" t="n">
         <v>408525</v>
@@ -28963,7 +28963,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G986" t="n">
-        <v>5.87743616104126</v>
+        <v>5.87743663787842</v>
       </c>
       <c r="H986" t="n">
         <v>356270</v>
@@ -28992,7 +28992,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G987" t="n">
-        <v>5.85088157653809</v>
+        <v>5.8508825302124</v>
       </c>
       <c r="H987" t="n">
         <v>244819</v>
@@ -29021,7 +29021,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G988" t="n">
-        <v>5.89514017105103</v>
+        <v>5.89513969421387</v>
       </c>
       <c r="H988" t="n">
         <v>263333</v>
@@ -29050,7 +29050,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>5.90399122238159</v>
+        <v>5.90399074554443</v>
       </c>
       <c r="H989" t="n">
         <v>98735</v>
@@ -29079,7 +29079,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G990" t="n">
-        <v>5.89514017105103</v>
+        <v>5.89513969421387</v>
       </c>
       <c r="H990" t="n">
         <v>168371</v>
@@ -29108,7 +29108,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G991" t="n">
-        <v>5.87743616104126</v>
+        <v>5.87743663787842</v>
       </c>
       <c r="H991" t="n">
         <v>99395</v>
@@ -29137,7 +29137,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G992" t="n">
-        <v>5.88628816604614</v>
+        <v>5.8862886428833</v>
       </c>
       <c r="H992" t="n">
         <v>143166</v>
@@ -29195,7 +29195,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G994" t="n">
-        <v>5.94824886322021</v>
+        <v>5.94824981689453</v>
       </c>
       <c r="H994" t="n">
         <v>320883</v>
@@ -29224,7 +29224,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G995" t="n">
-        <v>6.05446767807007</v>
+        <v>6.05446863174438</v>
       </c>
       <c r="H995" t="n">
         <v>446369</v>
@@ -29253,7 +29253,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G996" t="n">
-        <v>6.09872579574585</v>
+        <v>6.09872531890869</v>
       </c>
       <c r="H996" t="n">
         <v>260536</v>
@@ -29282,7 +29282,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G997" t="n">
-        <v>6.05446767807007</v>
+        <v>6.05446863174438</v>
       </c>
       <c r="H997" t="n">
         <v>287676</v>
@@ -29398,7 +29398,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1001" t="n">
-        <v>6.08102226257324</v>
+        <v>6.0810227394104</v>
       </c>
       <c r="H1001" t="n">
         <v>488903</v>
@@ -29427,7 +29427,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1002" t="n">
-        <v>6.1518349647522</v>
+        <v>6.15183544158936</v>
       </c>
       <c r="H1002" t="n">
         <v>237720</v>
@@ -29456,7 +29456,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1003" t="n">
-        <v>6.13413143157959</v>
+        <v>6.13413238525391</v>
       </c>
       <c r="H1003" t="n">
         <v>205771</v>
@@ -29485,7 +29485,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.1518349647522</v>
+        <v>6.15183544158936</v>
       </c>
       <c r="H1004" t="n">
         <v>228192</v>
@@ -29514,7 +29514,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>6.14298295974731</v>
+        <v>6.14298343658447</v>
       </c>
       <c r="H1005" t="n">
         <v>151000</v>
@@ -29543,7 +29543,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>6.1518349647522</v>
+        <v>6.15183544158936</v>
       </c>
       <c r="H1006" t="n">
         <v>227841</v>
@@ -29572,7 +29572,7 @@
         <v>7</v>
       </c>
       <c r="G1007" t="n">
-        <v>6.19609260559082</v>
+        <v>6.19609308242798</v>
       </c>
       <c r="H1007" t="n">
         <v>456813</v>
@@ -29601,7 +29601,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1008" t="n">
-        <v>6.16953802108765</v>
+        <v>6.16953754425049</v>
       </c>
       <c r="H1008" t="n">
         <v>290496</v>
@@ -29688,7 +29688,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1011" t="n">
-        <v>6.09872579574585</v>
+        <v>6.09872531890869</v>
       </c>
       <c r="H1011" t="n">
         <v>142401</v>
@@ -29717,7 +29717,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1012" t="n">
-        <v>6.07217073440552</v>
+        <v>6.07217121124268</v>
       </c>
       <c r="H1012" t="n">
         <v>409550</v>
@@ -29862,7 +29862,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1017" t="n">
-        <v>6.07217073440552</v>
+        <v>6.07217121124268</v>
       </c>
       <c r="H1017" t="n">
         <v>100246</v>
@@ -29891,7 +29891,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1018" t="n">
-        <v>6.02791309356689</v>
+        <v>6.02791357040405</v>
       </c>
       <c r="H1018" t="n">
         <v>234450</v>
@@ -29920,7 +29920,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1019" t="n">
-        <v>6.01021003723145</v>
+        <v>6.0102105140686</v>
       </c>
       <c r="H1019" t="n">
         <v>124525</v>
@@ -29949,7 +29949,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1020" t="n">
-        <v>6.05446767807007</v>
+        <v>6.05446863174438</v>
       </c>
       <c r="H1020" t="n">
         <v>181556</v>
@@ -29978,7 +29978,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1021" t="n">
-        <v>6.16953802108765</v>
+        <v>6.16953754425049</v>
       </c>
       <c r="H1021" t="n">
         <v>195476</v>
@@ -30007,7 +30007,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>6.16068696975708</v>
+        <v>6.16068744659424</v>
       </c>
       <c r="H1022" t="n">
         <v>207900</v>
@@ -30065,7 +30065,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.16953802108765</v>
+        <v>6.16953754425049</v>
       </c>
       <c r="H1024" t="n">
         <v>130498</v>
@@ -30210,7 +30210,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.37312507629395</v>
+        <v>6.37312412261963</v>
       </c>
       <c r="H1029" t="n">
         <v>423303</v>
@@ -30239,7 +30239,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.28460884094238</v>
+        <v>6.28460836410522</v>
       </c>
       <c r="H1030" t="n">
         <v>250713</v>
@@ -30268,7 +30268,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.26690483093262</v>
+        <v>6.26690626144409</v>
       </c>
       <c r="H1031" t="n">
         <v>181592</v>
@@ -30355,7 +30355,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.16953802108765</v>
+        <v>6.16953754425049</v>
       </c>
       <c r="H1034" t="n">
         <v>319955</v>
@@ -30413,7 +30413,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.13413143157959</v>
+        <v>6.13413238525391</v>
       </c>
       <c r="H1036" t="n">
         <v>114464</v>
@@ -30442,7 +30442,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.01906204223633</v>
+        <v>6.01906156539917</v>
       </c>
       <c r="H1037" t="n">
         <v>222772</v>
@@ -30587,7 +30587,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.13413143157959</v>
+        <v>6.13413238525391</v>
       </c>
       <c r="H1042" t="n">
         <v>184207</v>
@@ -30616,7 +30616,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.14298295974731</v>
+        <v>6.14298343658447</v>
       </c>
       <c r="H1043" t="n">
         <v>201881</v>
@@ -30645,7 +30645,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.13413143157959</v>
+        <v>6.13413238525391</v>
       </c>
       <c r="H1044" t="n">
         <v>118248</v>
@@ -30674,7 +30674,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.1518349647522</v>
+        <v>6.15183544158936</v>
       </c>
       <c r="H1045" t="n">
         <v>153977</v>
@@ -30703,7 +30703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.16953802108765</v>
+        <v>6.16953754425049</v>
       </c>
       <c r="H1046" t="n">
         <v>120883</v>
@@ -30732,7 +30732,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.14298295974731</v>
+        <v>6.14298343658447</v>
       </c>
       <c r="H1047" t="n">
         <v>119304</v>
@@ -30761,7 +30761,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.28460884094238</v>
+        <v>6.28460836410522</v>
       </c>
       <c r="H1048" t="n">
         <v>201924</v>
@@ -30906,7 +30906,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1053" t="n">
-        <v>5.70040559768677</v>
+        <v>5.70040607452393</v>
       </c>
       <c r="H1053" t="n">
         <v>789210</v>
@@ -30935,7 +30935,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>5.69155406951904</v>
+        <v>5.69155359268188</v>
       </c>
       <c r="H1054" t="n">
         <v>386991</v>
@@ -30993,7 +30993,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1056" t="n">
-        <v>5.70040559768677</v>
+        <v>5.70040607452393</v>
       </c>
       <c r="H1056" t="n">
         <v>242688</v>
@@ -31051,7 +31051,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1058" t="n">
-        <v>5.54992914199829</v>
+        <v>5.54992866516113</v>
       </c>
       <c r="H1058" t="n">
         <v>532019</v>
@@ -31080,7 +31080,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1059" t="n">
-        <v>5.63844442367554</v>
+        <v>5.6384449005127</v>
       </c>
       <c r="H1059" t="n">
         <v>249090</v>
@@ -31109,7 +31109,7 @@
         <v>6.25</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.53222560882568</v>
+        <v>5.53222608566284</v>
       </c>
       <c r="H1060" t="n">
         <v>1238952</v>
@@ -31167,7 +31167,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H1062" t="n">
         <v>978086</v>
@@ -31225,7 +31225,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1064" t="n">
-        <v>4.68247556686401</v>
+        <v>4.68247652053833</v>
       </c>
       <c r="H1064" t="n">
         <v>795956</v>
@@ -31283,7 +31283,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.02303409576416</v>
+        <v>4.02303457260132</v>
       </c>
       <c r="H1066" t="n">
         <v>1206251</v>
@@ -31312,7 +31312,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1067" t="n">
-        <v>4.73558521270752</v>
+        <v>4.73558568954468</v>
       </c>
       <c r="H1067" t="n">
         <v>503455</v>
@@ -31370,7 +31370,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.50544404983521</v>
+        <v>4.50544452667236</v>
       </c>
       <c r="H1069" t="n">
         <v>603497</v>
@@ -31399,7 +31399,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.76213979721069</v>
+        <v>4.76214027404785</v>
       </c>
       <c r="H1070" t="n">
         <v>170996</v>
@@ -31457,7 +31457,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.20471811294556</v>
+        <v>5.20471858978271</v>
       </c>
       <c r="H1072" t="n">
         <v>305026</v>
@@ -31515,7 +31515,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.05424165725708</v>
+        <v>5.05424213409424</v>
       </c>
       <c r="H1074" t="n">
         <v>168755</v>
@@ -31602,7 +31602,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.06309270858765</v>
+        <v>5.0630931854248</v>
       </c>
       <c r="H1077" t="n">
         <v>277895</v>
@@ -31631,7 +31631,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1078" t="n">
-        <v>4.98342943191528</v>
+        <v>4.98342990875244</v>
       </c>
       <c r="H1078" t="n">
         <v>114376</v>
@@ -31660,7 +31660,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1079" t="n">
-        <v>4.98342943191528</v>
+        <v>4.98342990875244</v>
       </c>
       <c r="H1079" t="n">
         <v>253686</v>
@@ -31689,7 +31689,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1080" t="n">
-        <v>4.77099227905273</v>
+        <v>4.77099180221558</v>
       </c>
       <c r="H1080" t="n">
         <v>202976</v>
@@ -31747,7 +31747,7 @@
         <v>5.5</v>
       </c>
       <c r="G1082" t="n">
-        <v>4.86835861206055</v>
+        <v>4.86835956573486</v>
       </c>
       <c r="H1082" t="n">
         <v>104895</v>
@@ -31863,7 +31863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H1086" t="n">
         <v>115122</v>
@@ -31979,7 +31979,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.25782775878906</v>
+        <v>5.2578272819519</v>
       </c>
       <c r="H1090" t="n">
         <v>217878</v>
@@ -32037,7 +32037,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.22242069244385</v>
+        <v>5.22242164611816</v>
       </c>
       <c r="H1092" t="n">
         <v>76961</v>
@@ -32066,7 +32066,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.1693115234375</v>
+        <v>5.16931247711182</v>
       </c>
       <c r="H1093" t="n">
         <v>81621</v>
@@ -32095,7 +32095,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.21356868743896</v>
+        <v>5.21356916427612</v>
       </c>
       <c r="H1094" t="n">
         <v>61436</v>
@@ -32124,7 +32124,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.18701553344727</v>
+        <v>5.18701505661011</v>
       </c>
       <c r="H1095" t="n">
         <v>74819</v>
@@ -32182,7 +32182,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.31978845596313</v>
+        <v>5.31978893280029</v>
       </c>
       <c r="H1097" t="n">
         <v>130641</v>
@@ -32211,7 +32211,7 @@
         <v>6</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.31093692779541</v>
+        <v>5.31093645095825</v>
       </c>
       <c r="H1098" t="n">
         <v>102187</v>
@@ -32240,7 +32240,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.22242069244385</v>
+        <v>5.22242164611816</v>
       </c>
       <c r="H1099" t="n">
         <v>96506</v>
@@ -32298,7 +32298,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.10735082626343</v>
+        <v>5.10735130310059</v>
       </c>
       <c r="H1101" t="n">
         <v>74272</v>
@@ -32327,7 +32327,7 @@
         <v>5.75</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.08964729309082</v>
+        <v>5.08964776992798</v>
       </c>
       <c r="H1102" t="n">
         <v>40634</v>
@@ -32356,7 +32356,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.0453896522522</v>
+        <v>5.04538917541504</v>
       </c>
       <c r="H1103" t="n">
         <v>47634</v>
@@ -32385,7 +32385,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.06309270858765</v>
+        <v>5.0630931854248</v>
       </c>
       <c r="H1104" t="n">
         <v>35885</v>
@@ -32414,7 +32414,7 @@
         <v>5.75</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.08964729309082</v>
+        <v>5.08964776992798</v>
       </c>
       <c r="H1105" t="n">
         <v>55418</v>
@@ -32443,7 +32443,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.10735082626343</v>
+        <v>5.10735130310059</v>
       </c>
       <c r="H1106" t="n">
         <v>54444</v>
@@ -32472,7 +32472,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.11620283126831</v>
+        <v>5.11620330810547</v>
       </c>
       <c r="H1107" t="n">
         <v>62293</v>
@@ -32501,7 +32501,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1108" t="n">
-        <v>4.97457695007324</v>
+        <v>4.9745774269104</v>
       </c>
       <c r="H1108" t="n">
         <v>62073</v>
@@ -32530,7 +32530,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.06309270858765</v>
+        <v>5.0630931854248</v>
       </c>
       <c r="H1109" t="n">
         <v>56896</v>
@@ -32559,7 +32559,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.30590009689331</v>
+        <v>5.30590152740479</v>
       </c>
       <c r="H1110" t="n">
         <v>135600</v>
@@ -32588,7 +32588,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1111" t="n">
         <v>142983</v>
@@ -32617,7 +32617,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1112" t="n">
         <v>130989</v>
@@ -32646,7 +32646,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1113" t="n">
         <v>210319</v>
@@ -32704,7 +32704,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.25194263458252</v>
+        <v>5.25194311141968</v>
       </c>
       <c r="H1115" t="n">
         <v>165256</v>
@@ -32849,7 +32849,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.25194263458252</v>
+        <v>5.25194311141968</v>
       </c>
       <c r="H1120" t="n">
         <v>316966</v>
@@ -32878,7 +32878,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.26093530654907</v>
+        <v>5.26093578338623</v>
       </c>
       <c r="H1121" t="n">
         <v>214573</v>
@@ -32965,7 +32965,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.38683843612671</v>
+        <v>5.38683891296387</v>
       </c>
       <c r="H1124" t="n">
         <v>366092</v>
@@ -33081,7 +33081,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.30590009689331</v>
+        <v>5.30590152740479</v>
       </c>
       <c r="H1128" t="n">
         <v>312773</v>
@@ -33110,7 +33110,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.30590009689331</v>
+        <v>5.30590152740479</v>
       </c>
       <c r="H1129" t="n">
         <v>349978</v>
@@ -33197,7 +33197,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1132" t="n">
-        <v>5.28791475296021</v>
+        <v>5.28791522979736</v>
       </c>
       <c r="H1132" t="n">
         <v>331070</v>
@@ -33255,7 +33255,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1134" t="n">
         <v>509123</v>
@@ -33342,7 +33342,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1137" t="n">
         <v>634090</v>
@@ -33371,7 +33371,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.01812267303467</v>
+        <v>5.01812314987183</v>
       </c>
       <c r="H1138" t="n">
         <v>1021287</v>
@@ -33545,7 +33545,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1144" t="n">
         <v>89896</v>
@@ -33574,7 +33574,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.1889910697937</v>
+        <v>5.18899154663086</v>
       </c>
       <c r="H1145" t="n">
         <v>181224</v>
@@ -33603,7 +33603,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.1889910697937</v>
+        <v>5.18899154663086</v>
       </c>
       <c r="H1146" t="n">
         <v>83260</v>
@@ -33661,7 +33661,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.15301847457886</v>
+        <v>5.15301895141602</v>
       </c>
       <c r="H1148" t="n">
         <v>155032</v>
@@ -33719,7 +33719,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1150" t="n">
         <v>132468</v>
@@ -33748,7 +33748,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.06308841705322</v>
+        <v>5.06308937072754</v>
       </c>
       <c r="H1151" t="n">
         <v>162410</v>
@@ -33777,7 +33777,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>5.15301847457886</v>
+        <v>5.15301895141602</v>
       </c>
       <c r="H1152" t="n">
         <v>197161</v>
@@ -33806,7 +33806,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1153" t="n">
         <v>138603</v>
@@ -33951,7 +33951,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.26093530654907</v>
+        <v>5.26093578338623</v>
       </c>
       <c r="H1158" t="n">
         <v>131505</v>
@@ -33980,7 +33980,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.16201162338257</v>
+        <v>5.16201210021973</v>
       </c>
       <c r="H1159" t="n">
         <v>187803</v>
@@ -34009,7 +34009,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.16201162338257</v>
+        <v>5.16201210021973</v>
       </c>
       <c r="H1160" t="n">
         <v>121501</v>
@@ -34038,7 +34038,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.10805320739746</v>
+        <v>5.1080527305603</v>
       </c>
       <c r="H1161" t="n">
         <v>109055</v>
@@ -34067,7 +34067,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1162" t="n">
         <v>137327</v>
@@ -34154,7 +34154,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.06308841705322</v>
+        <v>5.06308937072754</v>
       </c>
       <c r="H1165" t="n">
         <v>165771</v>
@@ -34183,7 +34183,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.10805320739746</v>
+        <v>5.1080527305603</v>
       </c>
       <c r="H1166" t="n">
         <v>123669</v>
@@ -34212,7 +34212,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.15301847457886</v>
+        <v>5.15301895141602</v>
       </c>
       <c r="H1167" t="n">
         <v>110319</v>
@@ -34241,7 +34241,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1168" t="n">
         <v>64420</v>
@@ -34270,7 +34270,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.10805320739746</v>
+        <v>5.1080527305603</v>
       </c>
       <c r="H1169" t="n">
         <v>79024</v>
@@ -34299,7 +34299,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.14402627944946</v>
+        <v>5.1440258026123</v>
       </c>
       <c r="H1170" t="n">
         <v>63256</v>
@@ -34386,7 +34386,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.20697689056396</v>
+        <v>5.20697736740112</v>
       </c>
       <c r="H1173" t="n">
         <v>75937</v>
@@ -34415,7 +34415,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.1889910697937</v>
+        <v>5.18899154663086</v>
       </c>
       <c r="H1174" t="n">
         <v>63300</v>
@@ -34444,7 +34444,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1175" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1175" t="n">
         <v>59405</v>
@@ -34502,7 +34502,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1177" t="n">
         <v>41266</v>
@@ -34618,7 +34618,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.10805320739746</v>
+        <v>5.1080527305603</v>
       </c>
       <c r="H1181" t="n">
         <v>122065</v>
@@ -34705,7 +34705,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1184" t="n">
-        <v>5.14402627944946</v>
+        <v>5.1440258026123</v>
       </c>
       <c r="H1184" t="n">
         <v>108557</v>
@@ -34734,7 +34734,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.05409479141235</v>
+        <v>5.05409526824951</v>
       </c>
       <c r="H1185" t="n">
         <v>178424</v>
@@ -34763,7 +34763,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1186" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1186" t="n">
         <v>170757</v>
@@ -34792,7 +34792,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1187" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1187" t="n">
         <v>222279</v>
@@ -34821,7 +34821,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>5.13503313064575</v>
+        <v>5.13503360748291</v>
       </c>
       <c r="H1188" t="n">
         <v>74199</v>
@@ -34850,7 +34850,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1189" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1189" t="n">
         <v>130833</v>
@@ -34879,7 +34879,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1190" t="n">
-        <v>5.1889910697937</v>
+        <v>5.18899154663086</v>
       </c>
       <c r="H1190" t="n">
         <v>71658</v>
@@ -34908,7 +34908,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1191" t="n">
         <v>62940</v>
@@ -34937,7 +34937,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1192" t="n">
         <v>75415</v>
@@ -34995,7 +34995,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.20697689056396</v>
+        <v>5.20697736740112</v>
       </c>
       <c r="H1194" t="n">
         <v>100243</v>
@@ -35111,7 +35111,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.38683843612671</v>
+        <v>5.38683891296387</v>
       </c>
       <c r="H1198" t="n">
         <v>216110</v>
@@ -35169,7 +35169,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.25194263458252</v>
+        <v>5.25194311141968</v>
       </c>
       <c r="H1200" t="n">
         <v>301602</v>
@@ -35227,7 +35227,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1202" t="n">
-        <v>5.3328800201416</v>
+        <v>5.33287954330444</v>
       </c>
       <c r="H1202" t="n">
         <v>222993</v>
@@ -35256,7 +35256,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1203" t="n">
-        <v>5.19798469543457</v>
+        <v>5.19798517227173</v>
       </c>
       <c r="H1203" t="n">
         <v>260207</v>
@@ -35285,7 +35285,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1204" t="n">
-        <v>5.14402627944946</v>
+        <v>5.1440258026123</v>
       </c>
       <c r="H1204" t="n">
         <v>109271</v>
@@ -35343,7 +35343,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>5.1889910697937</v>
+        <v>5.18899154663086</v>
       </c>
       <c r="H1206" t="n">
         <v>130195</v>
@@ -35401,7 +35401,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.10805320739746</v>
+        <v>5.1080527305603</v>
       </c>
       <c r="H1208" t="n">
         <v>128709</v>
@@ -35459,7 +35459,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.16201162338257</v>
+        <v>5.16201210021973</v>
       </c>
       <c r="H1210" t="n">
         <v>89412</v>
@@ -35691,7 +35691,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.20697689056396</v>
+        <v>5.20697736740112</v>
       </c>
       <c r="H1218" t="n">
         <v>101647</v>
@@ -35778,7 +35778,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1221" t="n">
-        <v>5.14402627944946</v>
+        <v>5.1440258026123</v>
       </c>
       <c r="H1221" t="n">
         <v>84622</v>
@@ -35807,7 +35807,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1222" t="n">
-        <v>5.09906053543091</v>
+        <v>5.09906101226807</v>
       </c>
       <c r="H1222" t="n">
         <v>66113</v>
@@ -35836,7 +35836,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.07208108901978</v>
+        <v>5.07208156585693</v>
       </c>
       <c r="H1223" t="n">
         <v>89992</v>
@@ -35894,7 +35894,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1225" t="n">
-        <v>5.01812267303467</v>
+        <v>5.01812314987183</v>
       </c>
       <c r="H1225" t="n">
         <v>133178</v>
@@ -35952,7 +35952,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.83826208114624</v>
+        <v>4.8382625579834</v>
       </c>
       <c r="H1227" t="n">
         <v>252966</v>
@@ -35981,7 +35981,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.8022894859314</v>
+        <v>4.80228996276855</v>
       </c>
       <c r="H1228" t="n">
         <v>271057</v>
@@ -36126,7 +36126,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1233" t="n">
-        <v>5.14402627944946</v>
+        <v>5.1440258026123</v>
       </c>
       <c r="H1233" t="n">
         <v>125127</v>
@@ -36184,7 +36184,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.26093530654907</v>
+        <v>5.26093578338623</v>
       </c>
       <c r="H1235" t="n">
         <v>238197</v>
@@ -36242,7 +36242,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.30590009689331</v>
+        <v>5.30590152740479</v>
       </c>
       <c r="H1237" t="n">
         <v>144615</v>
@@ -36300,7 +36300,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.48576211929321</v>
+        <v>5.48576164245605</v>
       </c>
       <c r="H1239" t="n">
         <v>227623</v>
@@ -36329,7 +36329,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1240" t="n">
-        <v>5.52173328399658</v>
+        <v>5.5217342376709</v>
       </c>
       <c r="H1240" t="n">
         <v>192244</v>
@@ -36358,7 +36358,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>5.46777534484863</v>
+        <v>5.46777582168579</v>
       </c>
       <c r="H1241" t="n">
         <v>132165</v>
@@ -36387,7 +36387,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1242" t="n">
-        <v>5.70159530639648</v>
+        <v>5.70159578323364</v>
       </c>
       <c r="H1242" t="n">
         <v>642197</v>
@@ -36445,7 +36445,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1244" t="n">
-        <v>5.80051851272583</v>
+        <v>5.80051898956299</v>
       </c>
       <c r="H1244" t="n">
         <v>264950</v>
@@ -36561,7 +36561,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1248" t="n">
-        <v>5.7285737991333</v>
+        <v>5.72857475280762</v>
       </c>
       <c r="H1248" t="n">
         <v>141476</v>
@@ -36590,7 +36590,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.7285737991333</v>
+        <v>5.72857475280762</v>
       </c>
       <c r="H1249" t="n">
         <v>122193</v>
@@ -36735,7 +36735,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1254" t="n">
-        <v>5.76454639434814</v>
+        <v>5.7645468711853</v>
       </c>
       <c r="H1254" t="n">
         <v>84005</v>
@@ -36764,7 +36764,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1255" t="n">
-        <v>5.8274974822998</v>
+        <v>5.82749843597412</v>
       </c>
       <c r="H1255" t="n">
         <v>108217</v>
@@ -36851,7 +36851,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1258" t="n">
-        <v>5.81850433349609</v>
+        <v>5.81850528717041</v>
       </c>
       <c r="H1258" t="n">
         <v>79450</v>
@@ -36880,7 +36880,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1259" t="n">
-        <v>5.83649063110352</v>
+        <v>5.83649110794067</v>
       </c>
       <c r="H1259" t="n">
         <v>98434</v>
@@ -36909,7 +36909,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>5.86347007751465</v>
+        <v>5.86346960067749</v>
       </c>
       <c r="H1260" t="n">
         <v>98981</v>
@@ -36967,7 +36967,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1262" t="n">
-        <v>5.94440698623657</v>
+        <v>5.94440793991089</v>
       </c>
       <c r="H1262" t="n">
         <v>131098</v>
@@ -36996,7 +36996,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1263" t="n">
-        <v>6.04333066940308</v>
+        <v>6.04333162307739</v>
       </c>
       <c r="H1263" t="n">
         <v>220988</v>
@@ -37054,7 +37054,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.10628223419189</v>
+        <v>6.10628271102905</v>
       </c>
       <c r="H1265" t="n">
         <v>335164</v>
@@ -37112,7 +37112,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.19621324539185</v>
+        <v>6.19621276855469</v>
       </c>
       <c r="H1267" t="n">
         <v>184506</v>
@@ -37141,7 +37141,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.19621324539185</v>
+        <v>6.19621276855469</v>
       </c>
       <c r="H1268" t="n">
         <v>203729</v>
@@ -37170,7 +37170,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1269" t="n">
-        <v>6.25916433334351</v>
+        <v>6.25916528701782</v>
       </c>
       <c r="H1269" t="n">
         <v>172917</v>
@@ -37199,7 +37199,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1270" t="n">
-        <v>6.19621324539185</v>
+        <v>6.19621276855469</v>
       </c>
       <c r="H1270" t="n">
         <v>62577</v>
@@ -37228,7 +37228,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1271" t="n">
-        <v>6.23218488693237</v>
+        <v>6.23218584060669</v>
       </c>
       <c r="H1271" t="n">
         <v>100579</v>
@@ -37257,7 +37257,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1272" t="n">
-        <v>6.22319173812866</v>
+        <v>6.22319221496582</v>
       </c>
       <c r="H1272" t="n">
         <v>78648</v>
@@ -37286,7 +37286,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1273" t="n">
-        <v>6.22319173812866</v>
+        <v>6.22319221496582</v>
       </c>
       <c r="H1273" t="n">
         <v>71839</v>
@@ -37344,7 +37344,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1275" t="n">
-        <v>6.24117851257324</v>
+        <v>6.24117803573608</v>
       </c>
       <c r="H1275" t="n">
         <v>72408</v>
@@ -37489,7 +37489,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1280" t="n">
-        <v>6.17822647094727</v>
+        <v>6.17822694778442</v>
       </c>
       <c r="H1280" t="n">
         <v>140674</v>
@@ -37576,7 +37576,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>6.25916433334351</v>
+        <v>6.25916528701782</v>
       </c>
       <c r="H1283" t="n">
         <v>86316</v>
@@ -37605,7 +37605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.16923332214355</v>
+        <v>6.16923379898071</v>
       </c>
       <c r="H1284" t="n">
         <v>81473</v>
@@ -37634,7 +37634,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.15124750137329</v>
+        <v>6.15124845504761</v>
       </c>
       <c r="H1285" t="n">
         <v>122620</v>
@@ -37663,7 +37663,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.06131649017334</v>
+        <v>6.0613169670105</v>
       </c>
       <c r="H1286" t="n">
         <v>150874</v>
@@ -37750,7 +37750,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.06131649017334</v>
+        <v>6.0613169670105</v>
       </c>
       <c r="H1289" t="n">
         <v>66895</v>
@@ -37866,7 +37866,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1293" t="n">
-        <v>6.19621324539185</v>
+        <v>6.19621276855469</v>
       </c>
       <c r="H1293" t="n">
         <v>283793</v>
@@ -37895,7 +37895,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.32211542129517</v>
+        <v>6.32211589813232</v>
       </c>
       <c r="H1294" t="n">
         <v>194875</v>
@@ -37982,7 +37982,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1297" t="n">
-        <v>6.56492853164673</v>
+        <v>6.56492900848389</v>
       </c>
       <c r="H1297" t="n">
         <v>143744</v>
@@ -38011,7 +38011,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.57392120361328</v>
+        <v>6.57392168045044</v>
       </c>
       <c r="H1298" t="n">
         <v>156779</v>
@@ -38069,7 +38069,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1300" t="n">
-        <v>6.60090112686157</v>
+        <v>6.60090017318726</v>
       </c>
       <c r="H1300" t="n">
         <v>113566</v>
@@ -38098,7 +38098,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1301" t="n">
-        <v>6.57392120361328</v>
+        <v>6.57392168045044</v>
       </c>
       <c r="H1301" t="n">
         <v>172732</v>
@@ -38127,7 +38127,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>6.5379490852356</v>
+        <v>6.53794956207275</v>
       </c>
       <c r="H1302" t="n">
         <v>33018</v>
@@ -38156,7 +38156,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1303" t="n">
-        <v>6.45701217651367</v>
+        <v>6.45701169967651</v>
       </c>
       <c r="H1303" t="n">
         <v>68220</v>
@@ -38185,7 +38185,7 @@
         <v>7</v>
       </c>
       <c r="G1304" t="n">
-        <v>6.29513645172119</v>
+        <v>6.29513692855835</v>
       </c>
       <c r="H1304" t="n">
         <v>112068</v>
@@ -38243,7 +38243,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1306" t="n">
-        <v>6.19621324539185</v>
+        <v>6.19621276855469</v>
       </c>
       <c r="H1306" t="n">
         <v>135113</v>
@@ -38272,7 +38272,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.12426853179932</v>
+        <v>6.12426900863647</v>
       </c>
       <c r="H1307" t="n">
         <v>127841</v>
@@ -38301,7 +38301,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1308" t="n">
-        <v>6.31312227249146</v>
+        <v>6.31312274932861</v>
       </c>
       <c r="H1308" t="n">
         <v>122732</v>
@@ -38330,7 +38330,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1309" t="n">
-        <v>6.32211542129517</v>
+        <v>6.32211589813232</v>
       </c>
       <c r="H1309" t="n">
         <v>133289</v>
@@ -38359,7 +38359,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1310" t="n">
-        <v>6.31312227249146</v>
+        <v>6.31312274932861</v>
       </c>
       <c r="H1310" t="n">
         <v>217995</v>
@@ -38388,7 +38388,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.40305376052856</v>
+        <v>6.40305280685425</v>
       </c>
       <c r="H1311" t="n">
         <v>301099</v>
@@ -38504,7 +38504,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1315" t="n">
-        <v>6.47499799728394</v>
+        <v>6.47499752044678</v>
       </c>
       <c r="H1315" t="n">
         <v>258518</v>
@@ -38533,7 +38533,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.51097011566162</v>
+        <v>6.51096963882446</v>
       </c>
       <c r="H1316" t="n">
         <v>114486</v>
@@ -38562,7 +38562,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1317" t="n">
-        <v>6.65485954284668</v>
+        <v>6.65485858917236</v>
       </c>
       <c r="H1317" t="n">
         <v>181693</v>
@@ -38591,7 +38591,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G1318" t="n">
-        <v>6.64586591720581</v>
+        <v>6.64586544036865</v>
       </c>
       <c r="H1318" t="n">
         <v>136662</v>
@@ -38649,7 +38649,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>6.71781015396118</v>
+        <v>6.71780967712402</v>
       </c>
       <c r="H1320" t="n">
         <v>103160</v>
@@ -38678,7 +38678,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.71781015396118</v>
+        <v>6.71780967712402</v>
       </c>
       <c r="H1321" t="n">
         <v>207077</v>
@@ -38765,7 +38765,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1324" t="n">
-        <v>6.65485954284668</v>
+        <v>6.65485858917236</v>
       </c>
       <c r="H1324" t="n">
         <v>112806</v>
@@ -38823,7 +38823,7 @@
         <v>7.5</v>
       </c>
       <c r="G1326" t="n">
-        <v>6.74478960037231</v>
+        <v>6.74478912353516</v>
       </c>
       <c r="H1326" t="n">
         <v>281213</v>
@@ -38852,7 +38852,7 @@
         <v>7.5</v>
       </c>
       <c r="G1327" t="n">
-        <v>6.74478960037231</v>
+        <v>6.74478912353516</v>
       </c>
       <c r="H1327" t="n">
         <v>110510</v>
@@ -38881,7 +38881,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.72680377960205</v>
+        <v>6.72680330276489</v>
       </c>
       <c r="H1328" t="n">
         <v>149348</v>
@@ -38939,7 +38939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1330" t="n">
-        <v>6.87069177627563</v>
+        <v>6.87069129943848</v>
       </c>
       <c r="H1330" t="n">
         <v>216187</v>
@@ -38997,7 +38997,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1332" t="n">
-        <v>6.82572746276855</v>
+        <v>6.8257269859314</v>
       </c>
       <c r="H1332" t="n">
         <v>100607</v>
@@ -39084,7 +39084,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.91565704345703</v>
+        <v>6.91565752029419</v>
       </c>
       <c r="H1335" t="n">
         <v>97238</v>
@@ -39142,7 +39142,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1337" t="n">
-        <v>6.95163011550903</v>
+        <v>6.95162963867188</v>
       </c>
       <c r="H1337" t="n">
         <v>155514</v>
@@ -39171,7 +39171,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1338" t="n">
-        <v>6.87069177627563</v>
+        <v>6.87069129943848</v>
       </c>
       <c r="H1338" t="n">
         <v>85560</v>
@@ -39200,7 +39200,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.89767169952393</v>
+        <v>6.89767074584961</v>
       </c>
       <c r="H1339" t="n">
         <v>99309</v>
@@ -39229,7 +39229,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.91565704345703</v>
+        <v>6.91565752029419</v>
       </c>
       <c r="H1340" t="n">
         <v>96905</v>
@@ -39287,7 +39287,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>6.93364381790161</v>
+        <v>6.93364334106445</v>
       </c>
       <c r="H1342" t="n">
         <v>82963</v>
@@ -39316,7 +39316,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.00558853149414</v>
+        <v>7.00558757781982</v>
       </c>
       <c r="H1343" t="n">
         <v>99337</v>
@@ -39374,7 +39374,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G1345" t="n">
-        <v>7.00558853149414</v>
+        <v>7.00558757781982</v>
       </c>
       <c r="H1345" t="n">
         <v>291998</v>
@@ -39635,7 +39635,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1354" t="n">
-        <v>7.09551858901978</v>
+        <v>7.09551811218262</v>
       </c>
       <c r="H1354" t="n">
         <v>61297</v>
@@ -39693,7 +39693,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1356" t="n">
-        <v>7.14947700500488</v>
+        <v>7.14947652816772</v>
       </c>
       <c r="H1356" t="n">
         <v>136062</v>
@@ -39722,7 +39722,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1357" t="n">
-        <v>7.14947700500488</v>
+        <v>7.14947652816772</v>
       </c>
       <c r="H1357" t="n">
         <v>137419</v>
@@ -39780,7 +39780,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1359" t="n">
-        <v>7.10451173782349</v>
+        <v>7.10451126098633</v>
       </c>
       <c r="H1359" t="n">
         <v>99010</v>
@@ -39838,7 +39838,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1361" t="n">
-        <v>7.05954647064209</v>
+        <v>7.05954551696777</v>
       </c>
       <c r="H1361" t="n">
         <v>135413</v>
@@ -39896,7 +39896,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1363" t="n">
-        <v>7.10451173782349</v>
+        <v>7.10451126098633</v>
       </c>
       <c r="H1363" t="n">
         <v>118984</v>
@@ -39983,7 +39983,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1366" t="n">
-        <v>6.91565704345703</v>
+        <v>6.91565752029419</v>
       </c>
       <c r="H1366" t="n">
         <v>165000</v>
@@ -40041,7 +40041,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.95163011550903</v>
+        <v>6.95162963867188</v>
       </c>
       <c r="H1368" t="n">
         <v>240781</v>
@@ -40070,7 +40070,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1369" t="n">
-        <v>7.24317407608032</v>
+        <v>7.24317359924316</v>
       </c>
       <c r="H1369" t="n">
         <v>199433</v>
@@ -40157,7 +40157,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1372" t="n">
-        <v>7.04273414611816</v>
+        <v>7.04273319244385</v>
       </c>
       <c r="H1372" t="n">
         <v>599104</v>
@@ -40215,7 +40215,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1374" t="n">
-        <v>7.1885085105896</v>
+        <v>7.18850803375244</v>
       </c>
       <c r="H1374" t="n">
         <v>125062</v>
@@ -40244,7 +40244,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1375" t="n">
-        <v>7.2613959312439</v>
+        <v>7.26139545440674</v>
       </c>
       <c r="H1375" t="n">
         <v>171562</v>
@@ -40273,7 +40273,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1376" t="n">
-        <v>7.35250473022461</v>
+        <v>7.35250425338745</v>
       </c>
       <c r="H1376" t="n">
         <v>269738</v>
@@ -40302,7 +40302,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1377" t="n">
-        <v>7.34339475631714</v>
+        <v>7.34339427947998</v>
       </c>
       <c r="H1377" t="n">
         <v>157404</v>
@@ -40360,7 +40360,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1379" t="n">
-        <v>7.37072706222534</v>
+        <v>7.37072658538818</v>
       </c>
       <c r="H1379" t="n">
         <v>149156</v>
@@ -40418,7 +40418,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1381" t="n">
-        <v>7.43450260162354</v>
+        <v>7.43450307846069</v>
       </c>
       <c r="H1381" t="n">
         <v>464308</v>
@@ -40447,7 +40447,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1382" t="n">
-        <v>7.35250473022461</v>
+        <v>7.35250425338745</v>
       </c>
       <c r="H1382" t="n">
         <v>80102</v>
@@ -40505,7 +40505,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1384" t="n">
-        <v>7.37072706222534</v>
+        <v>7.37072658538818</v>
       </c>
       <c r="H1384" t="n">
         <v>151071</v>
@@ -40534,7 +40534,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1385" t="n">
-        <v>7.30695056915283</v>
+        <v>7.30695104598999</v>
       </c>
       <c r="H1385" t="n">
         <v>75350</v>
@@ -40563,7 +40563,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1386" t="n">
-        <v>7.30695056915283</v>
+        <v>7.30695104598999</v>
       </c>
       <c r="H1386" t="n">
         <v>117150</v>
@@ -40592,7 +40592,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1387" t="n">
-        <v>7.30695056915283</v>
+        <v>7.30695104598999</v>
       </c>
       <c r="H1387" t="n">
         <v>64676</v>
@@ -40621,7 +40621,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1388" t="n">
-        <v>7.22495222091675</v>
+        <v>7.22495174407959</v>
       </c>
       <c r="H1388" t="n">
         <v>286037</v>
@@ -40650,7 +40650,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1389" t="n">
-        <v>7.37983798980713</v>
+        <v>7.37983846664429</v>
       </c>
       <c r="H1389" t="n">
         <v>377221</v>
@@ -40679,7 +40679,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1390" t="n">
-        <v>7.42539215087891</v>
+        <v>7.42539167404175</v>
       </c>
       <c r="H1390" t="n">
         <v>416005</v>
@@ -40766,7 +40766,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1393" t="n">
-        <v>7.3980598449707</v>
+        <v>7.39805936813354</v>
       </c>
       <c r="H1393" t="n">
         <v>102035</v>
@@ -40795,7 +40795,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1394" t="n">
-        <v>7.3980598449707</v>
+        <v>7.39805936813354</v>
       </c>
       <c r="H1394" t="n">
         <v>418203</v>
@@ -40824,7 +40824,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>7.55294466018677</v>
+        <v>7.55294418334961</v>
       </c>
       <c r="H1395" t="n">
         <v>363699</v>
@@ -40853,7 +40853,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1396" t="n">
-        <v>7.53472328186035</v>
+        <v>7.53472375869751</v>
       </c>
       <c r="H1396" t="n">
         <v>531591</v>
@@ -40940,7 +40940,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1399" t="n">
-        <v>7.8444938659668</v>
+        <v>7.84449338912964</v>
       </c>
       <c r="H1399" t="n">
         <v>158638</v>
@@ -40998,7 +40998,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1401" t="n">
-        <v>7.81716012954712</v>
+        <v>7.81716060638428</v>
       </c>
       <c r="H1401" t="n">
         <v>228667</v>
@@ -41027,7 +41027,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.58027696609497</v>
+        <v>7.58027648925781</v>
       </c>
       <c r="H1402" t="n">
         <v>348715</v>
@@ -41056,7 +41056,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.66227579116821</v>
+        <v>7.66227531433105</v>
       </c>
       <c r="H1403" t="n">
         <v>229263</v>
@@ -41114,7 +41114,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.88093757629395</v>
+        <v>7.88093709945679</v>
       </c>
       <c r="H1405" t="n">
         <v>470672</v>
@@ -41201,7 +41201,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.54383373260498</v>
+        <v>7.54383325576782</v>
       </c>
       <c r="H1408" t="n">
         <v>300708</v>
@@ -41259,7 +41259,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1410" t="n">
-        <v>7.24317407608032</v>
+        <v>7.24317359924316</v>
       </c>
       <c r="H1410" t="n">
         <v>426768</v>
@@ -41288,7 +41288,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1411" t="n">
-        <v>7.41628170013428</v>
+        <v>7.41628122329712</v>
       </c>
       <c r="H1411" t="n">
         <v>604867</v>
@@ -41317,7 +41317,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1412" t="n">
-        <v>7.53472328186035</v>
+        <v>7.53472375869751</v>
       </c>
       <c r="H1412" t="n">
         <v>241976</v>
@@ -41346,7 +41346,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1413" t="n">
-        <v>7.58027696609497</v>
+        <v>7.58027648925781</v>
       </c>
       <c r="H1413" t="n">
         <v>162204</v>
@@ -41375,7 +41375,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>7.63494300842285</v>
+        <v>7.63494348526001</v>
       </c>
       <c r="H1414" t="n">
         <v>305244</v>
@@ -41520,7 +41520,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1419" t="n">
-        <v>7.63494300842285</v>
+        <v>7.63494348526001</v>
       </c>
       <c r="H1419" t="n">
         <v>67360</v>
@@ -41549,7 +41549,7 @@
         <v>8.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>7.74427366256714</v>
+        <v>7.7442741394043</v>
       </c>
       <c r="H1420" t="n">
         <v>237413</v>
@@ -41578,7 +41578,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1421" t="n">
-        <v>7.85360479354858</v>
+        <v>7.85360527038574</v>
       </c>
       <c r="H1421" t="n">
         <v>316352</v>
@@ -41607,7 +41607,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>7.81716012954712</v>
+        <v>7.81716060638428</v>
       </c>
       <c r="H1422" t="n">
         <v>171338</v>
@@ -41636,7 +41636,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1423" t="n">
-        <v>7.68049764633179</v>
+        <v>7.68049716949463</v>
       </c>
       <c r="H1423" t="n">
         <v>114881</v>
@@ -41694,7 +41694,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1425" t="n">
-        <v>7.68049764633179</v>
+        <v>7.68049716949463</v>
       </c>
       <c r="H1425" t="n">
         <v>32512</v>
@@ -41752,7 +41752,7 @@
         <v>8.5</v>
       </c>
       <c r="G1427" t="n">
-        <v>7.74427366256714</v>
+        <v>7.7442741394043</v>
       </c>
       <c r="H1427" t="n">
         <v>186699</v>
@@ -41781,7 +41781,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1428" t="n">
-        <v>7.70783042907715</v>
+        <v>7.70783185958862</v>
       </c>
       <c r="H1428" t="n">
         <v>149387</v>
@@ -41810,7 +41810,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1429" t="n">
-        <v>7.62583255767822</v>
+        <v>7.62583208084106</v>
       </c>
       <c r="H1429" t="n">
         <v>53420</v>
@@ -41839,7 +41839,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.63494300842285</v>
+        <v>7.63494348526001</v>
       </c>
       <c r="H1430" t="n">
         <v>156377</v>
@@ -41868,7 +41868,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1431" t="n">
-        <v>7.82627296447754</v>
+        <v>7.82627201080322</v>
       </c>
       <c r="H1431" t="n">
         <v>241833</v>
@@ -41897,7 +41897,7 @@
         <v>8.5</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.74427366256714</v>
+        <v>7.7442741394043</v>
       </c>
       <c r="H1432" t="n">
         <v>159312</v>
@@ -42013,7 +42013,7 @@
         <v>8.75</v>
       </c>
       <c r="G1436" t="n">
-        <v>7.97204685211182</v>
+        <v>7.9720458984375</v>
       </c>
       <c r="H1436" t="n">
         <v>122437</v>
@@ -42042,7 +42042,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1437" t="n">
-        <v>7.99937868118286</v>
+        <v>7.9993782043457</v>
       </c>
       <c r="H1437" t="n">
         <v>124301</v>
@@ -42129,7 +42129,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1440" t="n">
-        <v>8.4093713760376</v>
+        <v>8.40937042236328</v>
       </c>
       <c r="H1440" t="n">
         <v>524582</v>
@@ -42187,7 +42187,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1442" t="n">
-        <v>8.60069942474365</v>
+        <v>8.60069751739502</v>
       </c>
       <c r="H1442" t="n">
         <v>459922</v>
@@ -42303,7 +42303,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1446" t="n">
-        <v>8.51870250701904</v>
+        <v>8.51870155334473</v>
       </c>
       <c r="H1446" t="n">
         <v>724510</v>
@@ -42361,7 +42361,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1448" t="n">
-        <v>8.30915069580078</v>
+        <v>8.30914974212646</v>
       </c>
       <c r="H1448" t="n">
         <v>406269</v>
@@ -42506,7 +42506,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.25448513031006</v>
+        <v>8.25448608398438</v>
       </c>
       <c r="H1453" t="n">
         <v>341657</v>
@@ -42593,7 +42593,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.51870250701904</v>
+        <v>8.51870155334473</v>
       </c>
       <c r="H1456" t="n">
         <v>358638</v>
@@ -42622,7 +42622,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1457" t="n">
-        <v>8.51870250701904</v>
+        <v>8.51870155334473</v>
       </c>
       <c r="H1457" t="n">
         <v>136998</v>
@@ -42680,7 +42680,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1459" t="n">
-        <v>8.43670272827148</v>
+        <v>8.4367036819458</v>
       </c>
       <c r="H1459" t="n">
         <v>113847</v>
@@ -42767,7 +42767,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1462" t="n">
-        <v>8.34559345245361</v>
+        <v>8.34559440612793</v>
       </c>
       <c r="H1462" t="n">
         <v>146931</v>
@@ -42883,7 +42883,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.30004024505615</v>
+        <v>8.30003929138184</v>
       </c>
       <c r="H1466" t="n">
         <v>251320</v>
@@ -42941,7 +42941,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.30915069580078</v>
+        <v>8.30914974212646</v>
       </c>
       <c r="H1468" t="n">
         <v>377007</v>
@@ -42970,7 +42970,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1469" t="n">
-        <v>8.30004024505615</v>
+        <v>8.30003929138184</v>
       </c>
       <c r="H1469" t="n">
         <v>137492</v>
@@ -43086,7 +43086,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.70092010498047</v>
+        <v>8.70091915130615</v>
       </c>
       <c r="H1473" t="n">
         <v>154366</v>
@@ -43115,7 +43115,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.92869281768799</v>
+        <v>8.9286937713623</v>
       </c>
       <c r="H1474" t="n">
         <v>227042</v>
@@ -43144,7 +43144,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.14735317230225</v>
+        <v>9.14735412597656</v>
       </c>
       <c r="H1475" t="n">
         <v>457237</v>
@@ -43202,7 +43202,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1477" t="n">
-        <v>9.14735317230225</v>
+        <v>9.14735412597656</v>
       </c>
       <c r="H1477" t="n">
         <v>93142</v>
@@ -43289,7 +43289,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1480" t="n">
-        <v>9.06535625457764</v>
+        <v>9.06535530090332</v>
       </c>
       <c r="H1480" t="n">
         <v>100398</v>
@@ -43318,7 +43318,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G1481" t="n">
-        <v>8.93780326843262</v>
+        <v>8.93780422210693</v>
       </c>
       <c r="H1481" t="n">
         <v>133807</v>
@@ -43347,7 +43347,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.94691276550293</v>
+        <v>8.94691371917725</v>
       </c>
       <c r="H1482" t="n">
         <v>90887</v>
@@ -43376,7 +43376,7 @@
         <v>9.75</v>
       </c>
       <c r="G1483" t="n">
-        <v>8.88313770294189</v>
+        <v>8.88313865661621</v>
       </c>
       <c r="H1483" t="n">
         <v>119483</v>
@@ -43550,7 +43550,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.54823398590088</v>
+        <v>9.54823303222656</v>
       </c>
       <c r="H1489" t="n">
         <v>390865</v>
@@ -43579,7 +43579,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.38423728942871</v>
+        <v>9.38423919677734</v>
       </c>
       <c r="H1490" t="n">
         <v>121808</v>
@@ -43608,7 +43608,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.27490615844727</v>
+        <v>9.27490711212158</v>
       </c>
       <c r="H1491" t="n">
         <v>139683</v>
@@ -43637,7 +43637,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1492" t="n">
-        <v>9.29312801361084</v>
+        <v>9.29312896728516</v>
       </c>
       <c r="H1492" t="n">
         <v>126265</v>
@@ -43753,7 +43753,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.06535625457764</v>
+        <v>9.06535530090332</v>
       </c>
       <c r="H1496" t="n">
         <v>183051</v>
@@ -43782,7 +43782,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1497" t="n">
-        <v>8.94691276550293</v>
+        <v>8.94691371917725</v>
       </c>
       <c r="H1497" t="n">
         <v>368861</v>
@@ -43840,7 +43840,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.90136051177979</v>
+        <v>8.90135955810547</v>
       </c>
       <c r="H1499" t="n">
         <v>239947</v>
@@ -43898,7 +43898,7 @@
         <v>9.5</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.65536499023438</v>
+        <v>8.65536594390869</v>
       </c>
       <c r="H1501" t="n">
         <v>210224</v>
@@ -43927,7 +43927,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1502" t="n">
-        <v>8.71003150939941</v>
+        <v>8.7100305557251</v>
       </c>
       <c r="H1502" t="n">
         <v>2119767</v>
@@ -43956,7 +43956,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>8.54603385925293</v>
+        <v>8.54603481292725</v>
       </c>
       <c r="H1503" t="n">
         <v>173808</v>
@@ -43985,7 +43985,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1504" t="n">
-        <v>8.68269729614258</v>
+        <v>8.68269824981689</v>
       </c>
       <c r="H1504" t="n">
         <v>180080</v>
@@ -44014,7 +44014,7 @@
         <v>9.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.65536499023438</v>
+        <v>8.65536594390869</v>
       </c>
       <c r="H1505" t="n">
         <v>369388</v>
@@ -44072,7 +44072,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.68269729614258</v>
+        <v>8.68269824981689</v>
       </c>
       <c r="H1507" t="n">
         <v>172046</v>
@@ -44101,7 +44101,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>8.71003150939941</v>
+        <v>8.7100305557251</v>
       </c>
       <c r="H1508" t="n">
         <v>151592</v>
@@ -44159,7 +44159,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>8.95602512359619</v>
+        <v>8.95602607727051</v>
       </c>
       <c r="H1510" t="n">
         <v>137951</v>
@@ -44275,7 +44275,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.72825145721436</v>
+        <v>8.72825241088867</v>
       </c>
       <c r="H1514" t="n">
         <v>339786</v>
@@ -44304,7 +44304,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.75558471679688</v>
+        <v>8.75558376312256</v>
       </c>
       <c r="H1515" t="n">
         <v>144392</v>
@@ -44333,7 +44333,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.80113983154297</v>
+        <v>8.80113887786865</v>
       </c>
       <c r="H1516" t="n">
         <v>69606</v>
@@ -44362,7 +44362,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1517" t="n">
-        <v>8.80113983154297</v>
+        <v>8.80113887786865</v>
       </c>
       <c r="H1517" t="n">
         <v>104432</v>
@@ -44391,7 +44391,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>8.54603385925293</v>
+        <v>8.54603481292725</v>
       </c>
       <c r="H1518" t="n">
         <v>394587</v>
@@ -44449,7 +44449,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>8.6098108291626</v>
+        <v>8.60980987548828</v>
       </c>
       <c r="H1520" t="n">
         <v>129698</v>
@@ -44507,7 +44507,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>8.84669399261475</v>
+        <v>8.84669303894043</v>
       </c>
       <c r="H1522" t="n">
         <v>72417</v>
@@ -44565,7 +44565,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1524" t="n">
-        <v>8.95602512359619</v>
+        <v>8.95602607727051</v>
       </c>
       <c r="H1524" t="n">
         <v>165323</v>
@@ -44594,7 +44594,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1525" t="n">
-        <v>9.01980209350586</v>
+        <v>9.01980113983154</v>
       </c>
       <c r="H1525" t="n">
         <v>64850</v>
@@ -44739,7 +44739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1530" t="n">
-        <v>9.01980209350586</v>
+        <v>9.01980113983154</v>
       </c>
       <c r="H1530" t="n">
         <v>85340</v>
@@ -44884,7 +44884,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1535" t="n">
-        <v>8.72825145721436</v>
+        <v>8.72825241088867</v>
       </c>
       <c r="H1535" t="n">
         <v>89162</v>
@@ -44942,7 +44942,7 @@
         <v>9.5</v>
       </c>
       <c r="G1537" t="n">
-        <v>8.65536499023438</v>
+        <v>8.65536594390869</v>
       </c>
       <c r="H1537" t="n">
         <v>124510</v>
@@ -44971,7 +44971,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1538" t="n">
-        <v>8.51870250701904</v>
+        <v>8.51870155334473</v>
       </c>
       <c r="H1538" t="n">
         <v>169636</v>
@@ -45000,7 +45000,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1539" t="n">
-        <v>8.51870250701904</v>
+        <v>8.51870155334473</v>
       </c>
       <c r="H1539" t="n">
         <v>118856</v>
@@ -45029,7 +45029,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G1540" t="n">
-        <v>8.68269729614258</v>
+        <v>8.68269824981689</v>
       </c>
       <c r="H1540" t="n">
         <v>257143</v>
@@ -45087,7 +45087,7 @@
         <v>8.75</v>
       </c>
       <c r="G1542" t="n">
-        <v>7.97204685211182</v>
+        <v>7.9720458984375</v>
       </c>
       <c r="H1542" t="n">
         <v>354452</v>
@@ -45145,7 +45145,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1544" t="n">
-        <v>8.13604259490967</v>
+        <v>8.13604354858398</v>
       </c>
       <c r="H1544" t="n">
         <v>455133</v>
@@ -45261,7 +45261,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1548" t="n">
-        <v>8.30915069580078</v>
+        <v>8.30914974212646</v>
       </c>
       <c r="H1548" t="n">
         <v>215436</v>
@@ -45290,7 +45290,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1549" t="n">
-        <v>8.41848182678223</v>
+        <v>8.41848087310791</v>
       </c>
       <c r="H1549" t="n">
         <v>136664</v>
@@ -45319,7 +45319,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G1550" t="n">
-        <v>8.22715187072754</v>
+        <v>8.22715282440186</v>
       </c>
       <c r="H1550" t="n">
         <v>105616</v>
@@ -45348,7 +45348,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G1551" t="n">
-        <v>8.22715187072754</v>
+        <v>8.22715282440186</v>
       </c>
       <c r="H1551" t="n">
         <v>154939</v>
@@ -45435,7 +45435,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1554" t="n">
-        <v>8.00849151611328</v>
+        <v>8.00849056243896</v>
       </c>
       <c r="H1554" t="n">
         <v>209054</v>
@@ -45551,7 +45551,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1558" t="n">
-        <v>8.26359558105469</v>
+        <v>8.26359462738037</v>
       </c>
       <c r="H1558" t="n">
         <v>242442</v>
@@ -45638,7 +45638,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1561" t="n">
-        <v>7.94471454620361</v>
+        <v>7.94471406936646</v>
       </c>
       <c r="H1561" t="n">
         <v>195649</v>
@@ -45696,7 +45696,7 @@
         <v>8.5</v>
       </c>
       <c r="G1563" t="n">
-        <v>7.74427366256714</v>
+        <v>7.7442741394043</v>
       </c>
       <c r="H1563" t="n">
         <v>394984</v>
@@ -45754,7 +45754,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1565" t="n">
-        <v>7.54383373260498</v>
+        <v>7.54383325576782</v>
       </c>
       <c r="H1565" t="n">
         <v>318120</v>
@@ -45783,7 +45783,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>7.81716012954712</v>
+        <v>7.81716060638428</v>
       </c>
       <c r="H1566" t="n">
         <v>269154</v>
@@ -45812,7 +45812,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1567" t="n">
-        <v>7.89915990829468</v>
+        <v>7.89915895462036</v>
       </c>
       <c r="H1567" t="n">
         <v>216820</v>
@@ -45899,7 +45899,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.54383373260498</v>
+        <v>7.54383325576782</v>
       </c>
       <c r="H1570" t="n">
         <v>223901</v>
@@ -45928,7 +45928,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.2978401184082</v>
+        <v>7.29783964157104</v>
       </c>
       <c r="H1571" t="n">
         <v>248691</v>
@@ -45957,7 +45957,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1572" t="n">
-        <v>7.17939758300781</v>
+        <v>7.17939710617065</v>
       </c>
       <c r="H1572" t="n">
         <v>442094</v>
@@ -45986,7 +45986,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1573" t="n">
-        <v>7.07917737960815</v>
+        <v>7.079176902771</v>
       </c>
       <c r="H1573" t="n">
         <v>236825</v>
@@ -46015,7 +46015,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.53472328186035</v>
+        <v>7.53472375869751</v>
       </c>
       <c r="H1574" t="n">
         <v>211307</v>
@@ -46131,7 +46131,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1578" t="n">
-        <v>7.54383373260498</v>
+        <v>7.54383325576782</v>
       </c>
       <c r="H1578" t="n">
         <v>226208</v>
@@ -46160,7 +46160,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G1579" t="n">
-        <v>8.03582191467285</v>
+        <v>8.03582286834717</v>
       </c>
       <c r="H1579" t="n">
         <v>302583</v>
@@ -46218,7 +46218,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>7.89004802703857</v>
+        <v>7.89004850387573</v>
       </c>
       <c r="H1581" t="n">
         <v>380805</v>
@@ -46247,7 +46247,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>8.1451530456543</v>
+        <v>8.14515209197998</v>
       </c>
       <c r="H1582" t="n">
         <v>256482</v>
@@ -46363,7 +46363,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1586" t="n">
-        <v>8.13604259490967</v>
+        <v>8.13604354858398</v>
       </c>
       <c r="H1586" t="n">
         <v>108019</v>
@@ -46421,7 +46421,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1588" t="n">
-        <v>8.30915069580078</v>
+        <v>8.30914974212646</v>
       </c>
       <c r="H1588" t="n">
         <v>115304</v>
@@ -46479,7 +46479,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1590" t="n">
-        <v>8.19070911407471</v>
+        <v>8.19070816040039</v>
       </c>
       <c r="H1590" t="n">
         <v>147536</v>
@@ -46537,7 +46537,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1592" t="n">
-        <v>8.26359558105469</v>
+        <v>8.26359462738037</v>
       </c>
       <c r="H1592" t="n">
         <v>117641</v>
@@ -46595,7 +46595,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1594" t="n">
-        <v>8.1451530456543</v>
+        <v>8.14515209197998</v>
       </c>
       <c r="H1594" t="n">
         <v>354494</v>
@@ -46682,7 +46682,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1597" t="n">
-        <v>8.26359558105469</v>
+        <v>8.26359462738037</v>
       </c>
       <c r="H1597" t="n">
         <v>303357</v>
@@ -46740,7 +46740,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1599" t="n">
-        <v>8.09960079193115</v>
+        <v>8.09959888458252</v>
       </c>
       <c r="H1599" t="n">
         <v>144591</v>
@@ -46769,7 +46769,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1600" t="n">
-        <v>8.18159770965576</v>
+        <v>8.18159866333008</v>
       </c>
       <c r="H1600" t="n">
         <v>68515</v>
@@ -46798,7 +46798,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1601" t="n">
-        <v>8.09960079193115</v>
+        <v>8.09959888458252</v>
       </c>
       <c r="H1601" t="n">
         <v>213713</v>
@@ -46856,7 +46856,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1603" t="n">
-        <v>8.19070911407471</v>
+        <v>8.19070816040039</v>
       </c>
       <c r="H1603" t="n">
         <v>152256</v>
@@ -46885,7 +46885,7 @@
         <v>8.75</v>
       </c>
       <c r="G1604" t="n">
-        <v>7.97204685211182</v>
+        <v>7.9720458984375</v>
       </c>
       <c r="H1604" t="n">
         <v>140310</v>
@@ -46914,7 +46914,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1605" t="n">
-        <v>7.88093757629395</v>
+        <v>7.88093709945679</v>
       </c>
       <c r="H1605" t="n">
         <v>98280</v>
@@ -47001,7 +47001,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1608" t="n">
-        <v>7.81716012954712</v>
+        <v>7.81716060638428</v>
       </c>
       <c r="H1608" t="n">
         <v>70123</v>
@@ -47030,7 +47030,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1609" t="n">
-        <v>7.94471454620361</v>
+        <v>7.94471406936646</v>
       </c>
       <c r="H1609" t="n">
         <v>161749</v>
@@ -47059,7 +47059,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>7.89915990829468</v>
+        <v>7.89915895462036</v>
       </c>
       <c r="H1610" t="n">
         <v>135913</v>
@@ -47088,7 +47088,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G1611" t="n">
-        <v>7.90827035903931</v>
+        <v>7.90827083587646</v>
       </c>
       <c r="H1611" t="n">
         <v>100520</v>
@@ -47117,7 +47117,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1612" t="n">
-        <v>7.81716012954712</v>
+        <v>7.81716060638428</v>
       </c>
       <c r="H1612" t="n">
         <v>82555</v>
@@ -47146,7 +47146,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1613" t="n">
-        <v>7.75338506698608</v>
+        <v>7.75338554382324</v>
       </c>
       <c r="H1613" t="n">
         <v>94135</v>
@@ -47175,7 +47175,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1614" t="n">
-        <v>7.54383373260498</v>
+        <v>7.54383325576782</v>
       </c>
       <c r="H1614" t="n">
         <v>251105</v>
@@ -47204,7 +47204,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1615" t="n">
-        <v>7.2613959312439</v>
+        <v>7.26139545440674</v>
       </c>
       <c r="H1615" t="n">
         <v>212295</v>
@@ -47233,7 +47233,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1616" t="n">
-        <v>7.41628170013428</v>
+        <v>7.41628122329712</v>
       </c>
       <c r="H1616" t="n">
         <v>99243</v>
@@ -47320,7 +47320,7 @@
         <v>8.5</v>
       </c>
       <c r="G1619" t="n">
-        <v>7.74427366256714</v>
+        <v>7.7442741394043</v>
       </c>
       <c r="H1619" t="n">
         <v>165705</v>
@@ -47407,7 +47407,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1622" t="n">
-        <v>7.55294466018677</v>
+        <v>7.55294418334961</v>
       </c>
       <c r="H1622" t="n">
         <v>122793</v>
@@ -47436,7 +47436,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1623" t="n">
-        <v>7.58027696609497</v>
+        <v>7.58027648925781</v>
       </c>
       <c r="H1623" t="n">
         <v>101999</v>
@@ -47871,7 +47871,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1638" t="n">
-        <v>7.48782157897949</v>
+        <v>7.48782205581665</v>
       </c>
       <c r="H1638" t="n">
         <v>152037</v>
@@ -47929,7 +47929,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1640" t="n">
-        <v>6.96155071258545</v>
+        <v>6.96155118942261</v>
       </c>
       <c r="H1640" t="n">
         <v>378161</v>
@@ -47958,7 +47958,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1641" t="n">
-        <v>6.94308567047119</v>
+        <v>6.94308519363403</v>
       </c>
       <c r="H1641" t="n">
         <v>189606</v>
@@ -48103,7 +48103,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1646" t="n">
-        <v>6.76766204833984</v>
+        <v>6.76766157150269</v>
       </c>
       <c r="H1646" t="n">
         <v>118308</v>
@@ -48132,7 +48132,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1647" t="n">
-        <v>6.70303201675415</v>
+        <v>6.70303249359131</v>
       </c>
       <c r="H1647" t="n">
         <v>146436</v>
@@ -48248,7 +48248,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1651" t="n">
-        <v>6.91538715362549</v>
+        <v>6.91538667678833</v>
       </c>
       <c r="H1651" t="n">
         <v>117299</v>
@@ -48306,7 +48306,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1653" t="n">
-        <v>6.76766204833984</v>
+        <v>6.76766157150269</v>
       </c>
       <c r="H1653" t="n">
         <v>161842</v>
@@ -48538,7 +48538,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1661" t="n">
-        <v>6.97078418731689</v>
+        <v>6.97078371047974</v>
       </c>
       <c r="H1661" t="n">
         <v>70754</v>
@@ -48828,7 +48828,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1671" t="n">
-        <v>7.0261812210083</v>
+        <v>7.02618074417114</v>
       </c>
       <c r="H1671" t="n">
         <v>108606</v>
@@ -48915,7 +48915,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1674" t="n">
-        <v>7.47858953475952</v>
+        <v>7.47859001159668</v>
       </c>
       <c r="H1674" t="n">
         <v>118159</v>
@@ -48944,7 +48944,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1675" t="n">
-        <v>7.45089054107666</v>
+        <v>7.4508900642395</v>
       </c>
       <c r="H1675" t="n">
         <v>59742</v>
@@ -48973,7 +48973,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1676" t="n">
-        <v>7.37702751159668</v>
+        <v>7.37702798843384</v>
       </c>
       <c r="H1676" t="n">
         <v>84329</v>
@@ -49060,7 +49060,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1679" t="n">
-        <v>7.45089054107666</v>
+        <v>7.4508900642395</v>
       </c>
       <c r="H1679" t="n">
         <v>40451</v>
@@ -49263,7 +49263,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1686" t="n">
-        <v>7.59861516952515</v>
+        <v>7.5986156463623</v>
       </c>
       <c r="H1686" t="n">
         <v>42598</v>
@@ -49321,7 +49321,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1688" t="n">
-        <v>7.50628805160522</v>
+        <v>7.50628757476807</v>
       </c>
       <c r="H1688" t="n">
         <v>40884</v>
@@ -49553,7 +49553,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1696" t="n">
-        <v>7.12774181365967</v>
+        <v>7.12774133682251</v>
       </c>
       <c r="H1696" t="n">
         <v>100644</v>
@@ -49640,7 +49640,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1699" t="n">
-        <v>7.00771522521973</v>
+        <v>7.00771570205688</v>
       </c>
       <c r="H1699" t="n">
         <v>57616</v>
@@ -49698,7 +49698,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1701" t="n">
-        <v>6.87845516204834</v>
+        <v>6.87845468521118</v>
       </c>
       <c r="H1701" t="n">
         <v>62696</v>
@@ -49988,7 +49988,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1711" t="n">
-        <v>6.52760791778564</v>
+        <v>6.5276083946228</v>
       </c>
       <c r="H1711" t="n">
         <v>200602</v>
@@ -50104,7 +50104,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1715" t="n">
-        <v>6.13982915878296</v>
+        <v>6.13982963562012</v>
       </c>
       <c r="H1715" t="n">
         <v>201572</v>
@@ -50133,7 +50133,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>6.13982915878296</v>
+        <v>6.13982963562012</v>
       </c>
       <c r="H1716" t="n">
         <v>271324</v>
@@ -50220,7 +50220,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1719" t="n">
-        <v>6.1213641166687</v>
+        <v>6.12136363983154</v>
       </c>
       <c r="H1719" t="n">
         <v>169308</v>
@@ -50278,7 +50278,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1721" t="n">
-        <v>6.2413911819458</v>
+        <v>6.24139070510864</v>
       </c>
       <c r="H1721" t="n">
         <v>196636</v>
@@ -50336,7 +50336,7 @@
         <v>6.5</v>
       </c>
       <c r="G1723" t="n">
-        <v>6.0013370513916</v>
+        <v>6.00133752822876</v>
       </c>
       <c r="H1723" t="n">
         <v>100094</v>
@@ -50394,7 +50394,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1725" t="n">
-        <v>5.95517253875732</v>
+        <v>5.95517301559448</v>
       </c>
       <c r="H1725" t="n">
         <v>163630</v>
@@ -50568,7 +50568,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1731" t="n">
-        <v>6.37064981460571</v>
+        <v>6.37065029144287</v>
       </c>
       <c r="H1731" t="n">
         <v>105594</v>
@@ -50597,7 +50597,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>6.50914239883423</v>
+        <v>6.50914192199707</v>
       </c>
       <c r="H1732" t="n">
         <v>181809</v>
@@ -50916,7 +50916,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>6.65686798095703</v>
+        <v>6.65686750411987</v>
       </c>
       <c r="H1743" t="n">
         <v>76047</v>
@@ -51032,7 +51032,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1747" t="n">
-        <v>6.98924922943115</v>
+        <v>6.98924875259399</v>
       </c>
       <c r="H1747" t="n">
         <v>307572</v>
@@ -51061,7 +51061,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1748" t="n">
-        <v>6.97078418731689</v>
+        <v>6.97078371047974</v>
       </c>
       <c r="H1748" t="n">
         <v>128306</v>
@@ -51119,7 +51119,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.94308567047119</v>
+        <v>6.94308519363403</v>
       </c>
       <c r="H1750" t="n">
         <v>109553</v>
@@ -51148,7 +51148,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1751" t="n">
-        <v>6.89692068099976</v>
+        <v>6.89692115783691</v>
       </c>
       <c r="H1751" t="n">
         <v>271323</v>
@@ -51177,7 +51177,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1752" t="n">
-        <v>6.83229160308838</v>
+        <v>6.83229112625122</v>
       </c>
       <c r="H1752" t="n">
         <v>80568</v>
@@ -51206,7 +51206,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>6.89692068099976</v>
+        <v>6.89692115783691</v>
       </c>
       <c r="H1753" t="n">
         <v>50210</v>
@@ -51264,7 +51264,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1755" t="n">
-        <v>6.97078418731689</v>
+        <v>6.97078371047974</v>
       </c>
       <c r="H1755" t="n">
         <v>90992</v>
@@ -51293,7 +51293,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1756" t="n">
-        <v>7.12774181365967</v>
+        <v>7.12774133682251</v>
       </c>
       <c r="H1756" t="n">
         <v>99125</v>
@@ -51409,7 +51409,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1760" t="n">
-        <v>6.96155071258545</v>
+        <v>6.96155118942261</v>
       </c>
       <c r="H1760" t="n">
         <v>43861</v>
@@ -51641,7 +51641,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1768" t="n">
-        <v>6.83229160308838</v>
+        <v>6.83229112625122</v>
       </c>
       <c r="H1768" t="n">
         <v>56524</v>
@@ -51699,7 +51699,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1770" t="n">
-        <v>6.94308567047119</v>
+        <v>6.94308519363403</v>
       </c>
       <c r="H1770" t="n">
         <v>79152</v>
@@ -51902,7 +51902,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1777" t="n">
-        <v>6.60147094726562</v>
+        <v>6.60147047042847</v>
       </c>
       <c r="H1777" t="n">
         <v>61533</v>
@@ -51931,7 +51931,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>6.6384015083313</v>
+        <v>6.63840198516846</v>
       </c>
       <c r="H1778" t="n">
         <v>36191</v>
@@ -52134,7 +52134,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1785" t="n">
-        <v>6.91538715362549</v>
+        <v>6.91538667678833</v>
       </c>
       <c r="H1785" t="n">
         <v>87234</v>
@@ -52163,7 +52163,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1786" t="n">
-        <v>6.85075712203979</v>
+        <v>6.85075759887695</v>
       </c>
       <c r="H1786" t="n">
         <v>58991</v>
@@ -52308,7 +52308,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1791" t="n">
-        <v>7.00771522521973</v>
+        <v>7.00771570205688</v>
       </c>
       <c r="H1791" t="n">
         <v>287905</v>
@@ -52366,7 +52366,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1793" t="n">
-        <v>7.12774181365967</v>
+        <v>7.12774133682251</v>
       </c>
       <c r="H1793" t="n">
         <v>112165</v>
@@ -52511,7 +52511,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1798" t="n">
-        <v>7.35856246948242</v>
+        <v>7.35856199264526</v>
       </c>
       <c r="H1798" t="n">
         <v>277638</v>
@@ -52772,7 +52772,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1807" t="n">
-        <v>7.45089054107666</v>
+        <v>7.4508900642395</v>
       </c>
       <c r="H1807" t="n">
         <v>212037</v>
@@ -52801,7 +52801,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1808" t="n">
-        <v>7.45089054107666</v>
+        <v>7.4508900642395</v>
       </c>
       <c r="H1808" t="n">
         <v>156912</v>
@@ -52830,7 +52830,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1809" t="n">
-        <v>7.35856246948242</v>
+        <v>7.35856199264526</v>
       </c>
       <c r="H1809" t="n">
         <v>152706</v>
@@ -52917,7 +52917,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>7.24776887893677</v>
+        <v>7.24776840209961</v>
       </c>
       <c r="H1812" t="n">
         <v>161690</v>
@@ -52975,7 +52975,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1814" t="n">
-        <v>7.35856246948242</v>
+        <v>7.35856199264526</v>
       </c>
       <c r="H1814" t="n">
         <v>118127</v>
@@ -53033,7 +53033,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1816" t="n">
-        <v>7.33086395263672</v>
+        <v>7.33086442947388</v>
       </c>
       <c r="H1816" t="n">
         <v>126757</v>
@@ -53178,7 +53178,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1821" t="n">
-        <v>7.0261812210083</v>
+        <v>7.02618074417114</v>
       </c>
       <c r="H1821" t="n">
         <v>137990</v>
@@ -53265,7 +53265,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1824" t="n">
-        <v>7.08157825469971</v>
+        <v>7.08157777786255</v>
       </c>
       <c r="H1824" t="n">
         <v>208764</v>
@@ -53294,7 +53294,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1825" t="n">
-        <v>7.11850881576538</v>
+        <v>7.11850929260254</v>
       </c>
       <c r="H1825" t="n">
         <v>164778</v>
@@ -53468,7 +53468,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1831" t="n">
-        <v>7.08157825469971</v>
+        <v>7.08157777786255</v>
       </c>
       <c r="H1831" t="n">
         <v>123418</v>
@@ -53526,7 +53526,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1833" t="n">
-        <v>6.6384015083313</v>
+        <v>6.63840198516846</v>
       </c>
       <c r="H1833" t="n">
         <v>318516</v>
@@ -53584,7 +53584,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1835" t="n">
-        <v>6.59223747253418</v>
+        <v>6.59223794937134</v>
       </c>
       <c r="H1835" t="n">
         <v>304088</v>
@@ -53671,7 +53671,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1838" t="n">
-        <v>7.11850881576538</v>
+        <v>7.11850929260254</v>
       </c>
       <c r="H1838" t="n">
         <v>418614</v>
@@ -53700,7 +53700,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1839" t="n">
-        <v>7.47858953475952</v>
+        <v>7.47859001159668</v>
       </c>
       <c r="H1839" t="n">
         <v>4013310</v>
@@ -53758,7 +53758,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1841" t="n">
-        <v>7.81097173690796</v>
+        <v>7.81097221374512</v>
       </c>
       <c r="H1841" t="n">
         <v>260403</v>
@@ -53874,7 +53874,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1845" t="n">
-        <v>7.62631464004517</v>
+        <v>7.62631511688232</v>
       </c>
       <c r="H1845" t="n">
         <v>131031</v>
@@ -53903,7 +53903,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1846" t="n">
-        <v>7.81097173690796</v>
+        <v>7.81097221374512</v>
       </c>
       <c r="H1846" t="n">
         <v>168597</v>
@@ -53961,7 +53961,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1848" t="n">
-        <v>7.73710823059082</v>
+        <v>7.73710870742798</v>
       </c>
       <c r="H1848" t="n">
         <v>196060</v>
@@ -54048,7 +54048,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1851" t="n">
-        <v>7.73710823059082</v>
+        <v>7.73710870742798</v>
       </c>
       <c r="H1851" t="n">
         <v>174373</v>
@@ -54077,7 +54077,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1852" t="n">
-        <v>7.73710823059082</v>
+        <v>7.73710870742798</v>
       </c>
       <c r="H1852" t="n">
         <v>188336</v>
@@ -54135,7 +54135,7 @@
         <v>8.5</v>
       </c>
       <c r="G1854" t="n">
-        <v>7.84790229797363</v>
+        <v>7.84790277481079</v>
       </c>
       <c r="H1854" t="n">
         <v>101123</v>
@@ -54164,7 +54164,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1855" t="n">
-        <v>7.8386697769165</v>
+        <v>7.83866930007935</v>
       </c>
       <c r="H1855" t="n">
         <v>262205</v>
@@ -54222,7 +54222,7 @@
         <v>8.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>7.84790229797363</v>
+        <v>7.84790277481079</v>
       </c>
       <c r="H1857" t="n">
         <v>115325</v>
@@ -54251,7 +54251,7 @@
         <v>8.5</v>
       </c>
       <c r="G1858" t="n">
-        <v>7.84790229797363</v>
+        <v>7.84790277481079</v>
       </c>
       <c r="H1858" t="n">
         <v>103601</v>
@@ -54280,7 +54280,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1859" t="n">
-        <v>7.73710823059082</v>
+        <v>7.73710870742798</v>
       </c>
       <c r="H1859" t="n">
         <v>109492</v>
@@ -54338,7 +54338,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1861" t="n">
-        <v>7.8386697769165</v>
+        <v>7.83866930007935</v>
       </c>
       <c r="H1861" t="n">
         <v>63582</v>
@@ -54396,7 +54396,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1863" t="n">
-        <v>7.73710823059082</v>
+        <v>7.73710870742798</v>
       </c>
       <c r="H1863" t="n">
         <v>106998</v>
@@ -54425,7 +54425,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1864" t="n">
-        <v>7.90329933166504</v>
+        <v>7.9032998085022</v>
       </c>
       <c r="H1864" t="n">
         <v>204199</v>
@@ -54483,7 +54483,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1866" t="n">
-        <v>8.12488746643066</v>
+        <v>8.12488651275635</v>
       </c>
       <c r="H1866" t="n">
         <v>325771</v>
@@ -54512,7 +54512,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G1867" t="n">
-        <v>8.10642147064209</v>
+        <v>8.10642051696777</v>
       </c>
       <c r="H1867" t="n">
         <v>203208</v>
@@ -54657,7 +54657,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1872" t="n">
-        <v>7.90329933166504</v>
+        <v>7.9032998085022</v>
       </c>
       <c r="H1872" t="n">
         <v>103381</v>
@@ -54715,7 +54715,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1874" t="n">
-        <v>8.06948947906494</v>
+        <v>8.06949043273926</v>
       </c>
       <c r="H1874" t="n">
         <v>94946</v>
@@ -54744,7 +54744,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1875" t="n">
-        <v>8.11565399169922</v>
+        <v>8.11565494537354</v>
       </c>
       <c r="H1875" t="n">
         <v>147475</v>
@@ -54773,7 +54773,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1876" t="n">
-        <v>8.11565399169922</v>
+        <v>8.11565494537354</v>
       </c>
       <c r="H1876" t="n">
         <v>210340</v>
@@ -54802,7 +54802,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1877" t="n">
-        <v>8.11565399169922</v>
+        <v>8.11565494537354</v>
       </c>
       <c r="H1877" t="n">
         <v>118139</v>
@@ -54831,7 +54831,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1878" t="n">
-        <v>8.12488746643066</v>
+        <v>8.12488651275635</v>
       </c>
       <c r="H1878" t="n">
         <v>133688</v>
@@ -55121,7 +55121,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1888" t="n">
-        <v>8.2172155380249</v>
+        <v>8.21721458435059</v>
       </c>
       <c r="H1888" t="n">
         <v>123441</v>
@@ -55150,7 +55150,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1889" t="n">
-        <v>8.32801055908203</v>
+        <v>8.32800960540771</v>
       </c>
       <c r="H1889" t="n">
         <v>102836</v>
@@ -55208,7 +55208,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1891" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H1891" t="n">
         <v>98296</v>
@@ -55295,7 +55295,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1894" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H1894" t="n">
         <v>65526</v>
@@ -55411,7 +55411,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1898" t="n">
-        <v>8.50343322753906</v>
+        <v>8.50343227386475</v>
       </c>
       <c r="H1898" t="n">
         <v>73748</v>
@@ -80096,6 +80096,35 @@
         <v>214345</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>8.89000034332275</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>8.89000034332275</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>208814</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>
